--- a/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7885C7-CCCD-4128-B180-8EC301D7EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C1FB02-ABD3-4FE2-A116-A7C1140F0C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="227">
   <si>
     <t>TOTAL</t>
   </si>
@@ -601,43 +606,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Casa Ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
-    <t>Transf 13/07</t>
-  </si>
-  <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
-    <t>Transf 06/07</t>
-  </si>
-  <si>
-    <t>Transf 22/07</t>
-  </si>
-  <si>
-    <t>Debito 13/07</t>
-  </si>
-  <si>
-    <t>Transf 15/07</t>
-  </si>
-  <si>
-    <t>Cuota 16/24</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Transf 27/07</t>
-  </si>
-  <si>
-    <t>Rescate 27/07</t>
-  </si>
-  <si>
     <t>Rescate FCI</t>
-  </si>
-  <si>
-    <t>Transf 30/07</t>
   </si>
   <si>
     <t>Articulos de limpieza</t>
@@ -677,27 +646,9 @@
     <t>PERÍODO: AGOSTO</t>
   </si>
   <si>
-    <t>Doartero AGOSTO - Conectado de trifasica en gabinete porta NH - Traslado de medidor trifasico - Extraccion de cableado intero - Extraccion de tablero trifasico interior</t>
-  </si>
-  <si>
-    <t>Doartero AGOSTO - Cambio de canilla y complra de 2 - Coneccion rapida para manguera 3/4</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Se adeuda Mitad de MAYO Y AGOSTO (ENTERO)</t>
-  </si>
-  <si>
-    <t>Gustavo Padron -  Sr. Contador - Se adeuda Mayo y JULIO</t>
-  </si>
-  <si>
     <t>Transf 17/8</t>
   </si>
   <si>
-    <t>Abono ascensor - ADS - Se abona el mes 7</t>
-  </si>
-  <si>
-    <t>Abono ascensor - ADS - Se abona el mes 6, se adeuda mes 8</t>
-  </si>
-  <si>
     <t>Palazzo Andres - Reparacion de camaras (fuente, cajas, conectores)</t>
   </si>
   <si>
@@ -710,13 +661,70 @@
     <t>Casa Fernandez - Motorrag SM INOX 150</t>
   </si>
   <si>
-    <t>Galvam Zaffalon - Visita de guardia por saltado de termica baja</t>
-  </si>
-  <si>
     <t>Transf 10/08</t>
   </si>
   <si>
-    <t>Galvam Zaffalon - Instalacion de pedrollo de su propiedad</t>
+    <t>Transf 06/08</t>
+  </si>
+  <si>
+    <t>Gabriel Chiantori - Se realizó el retiro de la bomba sumergible quemada, instalación de una nueva bomba con rejilla protectora anti-sedimentos y reacondicionamiento integral de la instalación eléctrica, incluyendo nuevo cableado y conexión hasta la caja del techo del subsuelo.</t>
+  </si>
+  <si>
+    <t>Galvan Zaffalon - Visita de guardia por saltado de termica baja</t>
+  </si>
+  <si>
+    <t>Galvan Zaffalon - Instalacion de pedrollo de su propiedad</t>
+  </si>
+  <si>
+    <t>Debito 10/08</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Transf 12/08</t>
+  </si>
+  <si>
+    <t>Gustavo Padron -  Sr. Contador - Mes 5 , 6  y 7</t>
+  </si>
+  <si>
+    <t>Transf 13/08</t>
+  </si>
+  <si>
+    <t>Abono ascensor - ADS - Se abona mes de mayo</t>
+  </si>
+  <si>
+    <t>Duplicacion de pago</t>
+  </si>
+  <si>
+    <t>Transf 18/08</t>
+  </si>
+  <si>
+    <t>Abono ascensor - ADS - Se abona el mes de junio</t>
+  </si>
+  <si>
+    <t>Cuota 17/24</t>
+  </si>
+  <si>
+    <t>Debito 18/08</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mitad de MAYO adeudada</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se debe Julio y Agosto ($420.000 c/u)</t>
+  </si>
+  <si>
+    <t>Transf 26/08</t>
+  </si>
+  <si>
+    <t>Transf 28/08</t>
+  </si>
+  <si>
+    <t>Rescate 12/08</t>
+  </si>
+  <si>
+    <t>Deposito ya identificad 29/6</t>
   </si>
 </sst>
 </file>
@@ -733,7 +741,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -889,6 +897,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="19">
     <fill>
@@ -983,12 +1005,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -999,8 +1015,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="41">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1497,21 +1519,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1654,9 +1667,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="17" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="20" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1713,7 +1723,6 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1824,54 +1833,44 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="8" fontId="12" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1896,20 +1895,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1956,12 +1973,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1995,33 +2006,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2040,8 +2024,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="18" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="18" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="18" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="21" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="18" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="18" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2125,9 +2131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2165,9 +2171,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2200,9 +2206,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2235,9 +2258,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2411,32 +2451,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M122"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M124"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="220" t="s">
+      <c r="B1" s="210" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="221"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="211"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>45</v>
@@ -2445,16 +2485,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="212" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="223"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="213"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2465,12 +2505,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2478,7 +2518,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>185</v>
       </c>
@@ -2489,62 +2529,62 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="224" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="224"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="224"/>
-      <c r="C9" s="224"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="224"/>
-      <c r="C10" s="224"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="214" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="214"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="214"/>
+      <c r="C9" s="214"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="214"/>
+      <c r="C10" s="214"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="225" t="s">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="215" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="225"/>
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="225"/>
-      <c r="B15" s="225"/>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="225"/>
-      <c r="B16" s="225"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="215"/>
+      <c r="C13" s="215"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="215"/>
+      <c r="B14" s="215"/>
+      <c r="C14" s="215"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="215"/>
+      <c r="B15" s="215"/>
+      <c r="C15" s="215"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="215"/>
+      <c r="B16" s="215"/>
+      <c r="C16" s="215"/>
+      <c r="D16" s="215"/>
+      <c r="E16" s="215"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2553,205 +2593,205 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="81"/>
-      <c r="E21" s="97"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="226" t="s">
+      <c r="E21" s="96"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="216" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="227"/>
+      <c r="B22" s="217"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="196">
-        <v>1369114.12</v>
-      </c>
-      <c r="E22" s="98"/>
+      <c r="D22" s="266">
+        <v>1460357.72</v>
+      </c>
+      <c r="E22" s="97"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="216" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="217"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="196">
-        <v>-297782.12</v>
+      <c r="B23" s="207"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="266">
+        <v>-317627.71999999997</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="38"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="216" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="217"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="197"/>
+      <c r="B24" s="207"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="194"/>
       <c r="E24" s="21"/>
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="153" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="22"/>
-      <c r="E25" s="99">
+      <c r="E25" s="98">
         <f>SUM(D22:D24)</f>
-        <v>1071332</v>
+        <v>1142730</v>
       </c>
       <c r="F25" s="38"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="153" t="s">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="153"/>
-      <c r="C26" s="153"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="151"/>
       <c r="D26" s="22"/>
-      <c r="E26" s="100"/>
+      <c r="E26" s="99"/>
       <c r="F26" s="38"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="152"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="150"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="150"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="111"/>
+      <c r="E27" s="110"/>
       <c r="F27" s="38"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="152"/>
-      <c r="B28" s="152"/>
-      <c r="C28" s="152"/>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="150"/>
+      <c r="B28" s="150"/>
+      <c r="C28" s="150"/>
       <c r="D28" s="28"/>
-      <c r="E28" s="111"/>
+      <c r="E28" s="110"/>
       <c r="F28" s="38"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="152"/>
-      <c r="B29" s="152"/>
-      <c r="C29" s="152"/>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="150"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="150"/>
       <c r="D29" s="28"/>
-      <c r="E29" s="111"/>
+      <c r="E29" s="110"/>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="153" t="s">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="152"/>
       <c r="D30" s="71"/>
-      <c r="E30" s="102">
+      <c r="E30" s="101">
         <f>SUM(D27:D29)</f>
         <v>0</v>
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="153"/>
-      <c r="C31" s="153"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="151"/>
       <c r="D31" s="22"/>
-      <c r="E31" s="100"/>
+      <c r="E31" s="99"/>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="152" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="155"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="28">
+      <c r="B32" s="153"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="263">
         <v>673382.02</v>
       </c>
-      <c r="E32" s="101" t="s">
-        <v>192</v>
+      <c r="E32" s="100" t="s">
+        <v>210</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="152" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="150" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="152" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="155"/>
-      <c r="D33" s="277">
+      <c r="B33" s="150" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="153"/>
+      <c r="D33" s="263">
         <v>182823.01</v>
       </c>
-      <c r="E33" s="101" t="s">
-        <v>195</v>
+      <c r="E33" s="100" t="s">
+        <v>220</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="152" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="155"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="277">
+      <c r="B34" s="153"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="263">
         <v>61610.09</v>
       </c>
-      <c r="E34" s="101" t="s">
-        <v>192</v>
+      <c r="E34" s="100" t="s">
+        <v>211</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="152" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="150" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="155"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="277">
+      <c r="B35" s="153"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="263">
         <v>6845.57</v>
       </c>
-      <c r="E35" s="101" t="str">
+      <c r="E35" s="100" t="str">
         <f>E34</f>
-        <v>Debito 13/07</v>
+        <v>Debito 12/08</v>
       </c>
       <c r="F35" s="38"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="152" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="150" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="155"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="277">
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="263">
         <v>110477.88</v>
       </c>
-      <c r="E36" s="101" t="str">
+      <c r="E36" s="100" t="str">
         <f>E34</f>
-        <v>Debito 13/07</v>
+        <v>Debito 12/08</v>
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="153" t="s">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="153"/>
-      <c r="C37" s="153"/>
+      <c r="B37" s="151"/>
+      <c r="C37" s="151"/>
       <c r="D37" s="22"/>
       <c r="E37" s="32">
         <f>SUM(D32:D36)</f>
@@ -2759,23 +2799,23 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="153"/>
-      <c r="C38" s="153"/>
+      <c r="B38" s="151"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="23"/>
-      <c r="E38" s="102"/>
+      <c r="E38" s="101"/>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="228" t="s">
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="229"/>
-      <c r="C39" s="156"/>
-      <c r="D39" s="198">
+      <c r="B39" s="202"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="261">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2783,13 +2823,13 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="228" t="s">
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="201" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="229"/>
-      <c r="C40" s="156"/>
-      <c r="D40" s="198">
+      <c r="B40" s="202"/>
+      <c r="C40" s="154"/>
+      <c r="D40" s="195">
         <f>1285.32+12020</f>
         <v>13305.32</v>
       </c>
@@ -2799,12 +2839,12 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="153" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="153"/>
-      <c r="C41" s="153"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
@@ -2812,556 +2852,557 @@
       </c>
       <c r="F41" s="38"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
+      <c r="B42" s="152"/>
+      <c r="C42" s="152"/>
       <c r="D42" s="25"/>
-      <c r="E42" s="103"/>
+      <c r="E42" s="102"/>
       <c r="F42" s="38"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>145</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="276">
-        <v>1712788.09</v>
+      <c r="D43" s="262">
+        <v>1726596.39</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F43" s="38"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="157"/>
+      <c r="B44" s="155"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="133">
+      <c r="D44" s="262">
         <v>6637.89</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="F44" s="38"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="228" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="155" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" s="33"/>
+      <c r="D45" s="262">
+        <v>6637.89</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="201" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="229"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="276">
+      <c r="B46" s="202"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="262">
         <v>542877.21</v>
       </c>
-      <c r="E45" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" s="38"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="158" t="s">
+      <c r="E46" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="38"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="156" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="159" t="s">
+      <c r="B47" s="157" t="s">
         <v>174</v>
       </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="276">
+      <c r="C47" s="33"/>
+      <c r="D47" s="262">
         <v>40810.79</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E47" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F47" s="38"/>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="151"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="103">
+        <f>SUM(D43:D47)</f>
+        <v>2323560.17</v>
+      </c>
+      <c r="F48" s="38"/>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="151"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="38"/>
+    </row>
+    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="206" t="s">
+        <v>215</v>
+      </c>
+      <c r="B50" s="207"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="262">
+        <v>250600</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="38"/>
+    </row>
+    <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="206" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" s="207"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="262">
+        <v>298200</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F51" s="38"/>
+    </row>
+    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="201" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="202"/>
+      <c r="C52" s="150"/>
+      <c r="D52" s="262">
+        <v>300000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="F52" s="132"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="204" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="205"/>
+      <c r="C53" s="150"/>
+      <c r="D53" s="262">
+        <v>150000</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F53" s="132"/>
+    </row>
+    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="204" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="205"/>
+      <c r="C54" s="150"/>
+      <c r="D54" s="262">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="132"/>
+    </row>
+    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" s="205"/>
+      <c r="C55" s="150"/>
+      <c r="D55" s="262">
+        <v>202973</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="F55" s="132"/>
+    </row>
+    <row r="56" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="201" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="202"/>
+      <c r="C56" s="150"/>
+      <c r="D56" s="262">
+        <v>180000</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="38"/>
+    </row>
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="207"/>
+      <c r="C57" s="150"/>
+      <c r="D57" s="262">
+        <v>265200</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" s="38"/>
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="193" t="s">
         <v>188</v>
       </c>
-      <c r="F46" s="38"/>
-    </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="153" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="153"/>
-      <c r="C47" s="153"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="104">
-        <f>SUM(D43:D46)</f>
-        <v>2303113.98</v>
-      </c>
-      <c r="F47" s="38"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="153"/>
-      <c r="C48" s="153"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="105"/>
-      <c r="F48" s="38"/>
-    </row>
-    <row r="49" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="216" t="s">
-        <v>218</v>
-      </c>
-      <c r="B49" s="217"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="276">
-        <v>298200</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="F49" s="38"/>
-    </row>
-    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="216" t="s">
-        <v>217</v>
-      </c>
-      <c r="B50" s="217"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="276">
-        <v>298200</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="F50" s="38"/>
-    </row>
-    <row r="51" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="232" t="s">
-        <v>212</v>
-      </c>
-      <c r="B51" s="219"/>
-      <c r="C51" s="152"/>
-      <c r="D51" s="133">
-        <v>290000</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="134"/>
-    </row>
-    <row r="52" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="228" t="s">
-        <v>213</v>
-      </c>
-      <c r="B52" s="229"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="133">
-        <v>110000</v>
-      </c>
-      <c r="E52" s="27" t="s">
+      <c r="B58" s="158"/>
+      <c r="C58" s="150"/>
+      <c r="D58" s="262">
+        <v>130500</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" s="38"/>
+    </row>
+    <row r="59" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="200" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="134"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="230" t="s">
-        <v>223</v>
-      </c>
-      <c r="B53" s="231"/>
-      <c r="C53" s="152"/>
-      <c r="D53" s="276">
-        <v>150000</v>
-      </c>
-      <c r="E53" s="27" t="s">
+      <c r="B59" s="158"/>
+      <c r="C59" s="150"/>
+      <c r="D59" s="262">
+        <v>118800</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="F53" s="134"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="230" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" s="231"/>
-      <c r="C54" s="152"/>
-      <c r="D54" s="276">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="F54" s="134"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="230" t="s">
-        <v>222</v>
-      </c>
-      <c r="B55" s="231"/>
-      <c r="C55" s="152"/>
-      <c r="D55" s="276">
-        <v>202973</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F55" s="134"/>
-    </row>
-    <row r="56" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="228" t="s">
-        <v>221</v>
-      </c>
-      <c r="B56" s="229"/>
-      <c r="C56" s="152"/>
-      <c r="D56" s="276">
-        <v>180000</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F56" s="38"/>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="216" t="s">
-        <v>219</v>
-      </c>
-      <c r="B57" s="217"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="276">
-        <v>265200</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="F57" s="38"/>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="195" t="s">
-        <v>200</v>
-      </c>
-      <c r="B58" s="160"/>
-      <c r="C58" s="152"/>
-      <c r="D58" s="133">
-        <v>123200</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F58" s="38"/>
-    </row>
-    <row r="59" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="161" t="s">
-        <v>187</v>
-      </c>
-      <c r="B59" s="160"/>
-      <c r="C59" s="152"/>
-      <c r="D59" s="133">
-        <v>261000</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="F59" s="134"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="153" t="s">
+      <c r="F59" s="132"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="151" t="s">
         <v>0</v>
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="29"/>
       <c r="D60" s="29"/>
       <c r="E60" s="32">
-        <f>SUM(D49:D59)</f>
-        <v>2528773</v>
+        <f>SUM(D50:D59)</f>
+        <v>2246273</v>
       </c>
       <c r="F60" s="38"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
       <c r="D61" s="18"/>
-      <c r="E61" s="97"/>
+      <c r="E61" s="96"/>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="216" t="s">
-        <v>214</v>
-      </c>
-      <c r="B62" s="217"/>
-      <c r="C62" s="152"/>
-      <c r="D62" s="199">
-        <v>420000</v>
-      </c>
-      <c r="E62" s="98"/>
+    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="206" t="s">
+        <v>221</v>
+      </c>
+      <c r="B62" s="207"/>
+      <c r="C62" s="150"/>
+      <c r="D62" s="265">
+        <v>210000</v>
+      </c>
+      <c r="E62" s="97"/>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="161" t="s">
-        <v>215</v>
-      </c>
-      <c r="B63" s="160"/>
-      <c r="C63" s="152"/>
-      <c r="D63" s="200">
-        <v>50000</v>
-      </c>
-      <c r="E63" s="98"/>
+    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="206" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="207"/>
+      <c r="C63" s="150"/>
+      <c r="D63" s="264">
+        <v>0</v>
+      </c>
+      <c r="E63" s="97"/>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="153" t="s">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="159" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="158"/>
+      <c r="C64" s="150"/>
+      <c r="D64" s="264">
+        <v>150000</v>
+      </c>
+      <c r="E64" s="97"/>
+      <c r="F64" s="38"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="153"/>
-      <c r="C64" s="153"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="99">
-        <f>SUM(D62:D63)</f>
-        <v>470000</v>
-      </c>
-      <c r="F64" s="38"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="29" t="s">
+      <c r="B65" s="151"/>
+      <c r="C65" s="151"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="98">
+        <f>SUM(D62:D64)</f>
+        <v>360000</v>
+      </c>
+      <c r="F65" s="38"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="162"/>
-      <c r="C65" s="153"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="38"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="33" t="s">
+      <c r="B66" s="160"/>
+      <c r="C66" s="151"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="38"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B66" s="163"/>
-      <c r="C66" s="163"/>
-      <c r="D66" s="164">
+      <c r="B67" s="161"/>
+      <c r="C67" s="161"/>
+      <c r="D67" s="267">
         <v>69000</v>
       </c>
-      <c r="E66" s="106"/>
-      <c r="F66" s="38"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="33" t="s">
+      <c r="E67" s="105"/>
+      <c r="F67" s="38"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B67" s="163"/>
-      <c r="C67" s="163"/>
-      <c r="D67" s="164">
+      <c r="B68" s="161"/>
+      <c r="C68" s="161"/>
+      <c r="D68" s="162">
         <v>110424.89</v>
       </c>
-      <c r="E67" s="106"/>
-      <c r="F67" s="38"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="165" t="s">
+      <c r="E68" s="105"/>
+      <c r="F68" s="38"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B68" s="165"/>
-      <c r="C68" s="165"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="32">
-        <f>SUM(D66:D67)</f>
+      <c r="B69" s="163"/>
+      <c r="C69" s="163"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="32">
+        <f>SUM(D67:D68)</f>
         <v>179424.89</v>
       </c>
-      <c r="F68" s="38"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="34"/>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="166" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="33"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="38"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="B70" s="166"/>
-      <c r="C70" s="166"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="38"/>
-    </row>
-    <row r="71" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="167"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="134"/>
-    </row>
-    <row r="72" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="168" t="s">
+      <c r="B71" s="164"/>
+      <c r="C71" s="164"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="38"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="165"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="132"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="169"/>
-      <c r="C72" s="41"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="42">
-        <f>(SUM(E21:E70))</f>
-        <v>7806121.4699999997</v>
-      </c>
-      <c r="F72" s="170"/>
-      <c r="G72" s="40"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="38"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-    </row>
-    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="167"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="42">
+        <f>(SUM(E21:E71))</f>
+        <v>7505465.6599999992</v>
+      </c>
+      <c r="F73" s="168"/>
+      <c r="G73" s="40"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="38"/>
       <c r="B74" s="38"/>
       <c r="C74" s="38"/>
       <c r="D74" s="38"/>
       <c r="E74" s="38"/>
       <c r="F74" s="38"/>
-      <c r="H74" s="44"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="171" t="s">
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="38"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="H75" s="44"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="172"/>
-      <c r="C75" s="173"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="38"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="218"/>
-      <c r="B76" s="219"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="174"/>
-      <c r="E76" s="120"/>
+      <c r="B76" s="170"/>
+      <c r="C76" s="171"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="46"/>
       <c r="F76" s="38"/>
     </row>
-    <row r="77" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="38"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="209"/>
+      <c r="B77" s="203"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="172"/>
+      <c r="E77" s="119"/>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="175"/>
-      <c r="B78" s="176"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="47"/>
+    <row r="78" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="177" t="s">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="173"/>
+      <c r="B79" s="174"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="38"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="B79" s="178"/>
-      <c r="C79" s="178"/>
-      <c r="D79" s="80"/>
-      <c r="E79" s="107">
-        <f>SUM(D76:D78)</f>
-        <v>0</v>
-      </c>
-      <c r="F79" s="38"/>
-    </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
+      <c r="B80" s="176"/>
+      <c r="C80" s="176"/>
+      <c r="D80" s="80"/>
+      <c r="E80" s="106">
+        <f>SUM(D77:D79)</f>
+        <v>0</v>
+      </c>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="166" t="s">
+    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="38"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="166"/>
-      <c r="C81" s="166"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="110">
-        <v>0</v>
-      </c>
-      <c r="F81" s="38"/>
-    </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="38"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
+      <c r="B82" s="164"/>
+      <c r="C82" s="164"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="109">
+        <v>0</v>
+      </c>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="168" t="s">
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="38"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="169"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="42">
-        <f>E79+E81</f>
-        <v>0</v>
-      </c>
-      <c r="F83" s="38"/>
-    </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="38"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="38"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="38"/>
+      <c r="B84" s="167"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="42">
+        <f>E80+E82</f>
+        <v>0</v>
+      </c>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="179" t="s">
-        <v>20</v>
-      </c>
-      <c r="B85" s="180">
-        <f>E72</f>
-        <v>7806121.4699999997</v>
-      </c>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="38"/>
+      <c r="B85" s="38"/>
       <c r="C85" s="38"/>
       <c r="D85" s="38"/>
       <c r="E85" s="38"/>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="179" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" s="180">
-        <f>E72-E70</f>
-        <v>7806121.4699999997</v>
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="177" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" s="178">
+        <f>E73</f>
+        <v>7505465.6599999992</v>
       </c>
       <c r="C86" s="38"/>
       <c r="D86" s="38"/>
       <c r="E86" s="38"/>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="179" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="180">
-        <f>E83-E81</f>
-        <v>0</v>
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="177" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="178">
+        <f>E73-E71</f>
+        <v>7505465.6599999992</v>
       </c>
       <c r="C87" s="38"/>
       <c r="D87" s="38"/>
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="179" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="180">
-        <f>E83</f>
+    <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="177" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="178">
+        <f>E84-E82</f>
         <v>0</v>
       </c>
       <c r="C88" s="38"/>
@@ -3369,15 +3410,20 @@
       <c r="E88" s="38"/>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="38"/>
-      <c r="B89" s="38"/>
+    <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="177" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" s="178">
+        <f>E84</f>
+        <v>0</v>
+      </c>
       <c r="C89" s="38"/>
       <c r="D89" s="38"/>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="38"/>
       <c r="B90" s="38"/>
       <c r="C90" s="38"/>
@@ -3385,168 +3431,164 @@
       <c r="E90" s="38"/>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="112" t="s">
-        <v>182</v>
-      </c>
-      <c r="B91" s="181">
-        <v>0</v>
-      </c>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="38"/>
+      <c r="B91" s="38"/>
       <c r="C91" s="38"/>
       <c r="D91" s="38"/>
       <c r="E91" s="38"/>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="156" t="s">
-        <v>202</v>
-      </c>
-      <c r="B92" s="182">
-        <v>6500000</v>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="111" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="179">
+        <v>0</v>
       </c>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="156" t="s">
-        <v>197</v>
-      </c>
-      <c r="B93" s="135">
-        <v>-1501954.93</v>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="154" t="s">
+        <v>190</v>
+      </c>
+      <c r="B93" s="180">
+        <v>6500000</v>
       </c>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="156" t="s">
-        <v>201</v>
-      </c>
-      <c r="B94" s="135">
-        <f>5125397.67-4998045.07</f>
-        <v>127352.59999999963</v>
+    <row r="94" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="154" t="s">
+        <v>225</v>
+      </c>
+      <c r="B94" s="268">
+        <v>-2000574.76</v>
       </c>
       <c r="C94" s="38"/>
       <c r="D94" s="38"/>
       <c r="E94" s="38"/>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="183" t="s">
-        <v>178</v>
-      </c>
-      <c r="B95" s="184">
-        <f>SUM(B91:B94)</f>
-        <v>5125397.67</v>
+    <row r="95" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="154" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" s="133">
+        <f>5125397.67-4998045.07</f>
+        <v>127352.59999999963</v>
       </c>
       <c r="C95" s="38"/>
       <c r="D95" s="38"/>
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="185"/>
-      <c r="B96" s="186"/>
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="181" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" s="182">
+        <f>SUM(B92:B95)</f>
+        <v>4626777.84</v>
+      </c>
       <c r="C96" s="38"/>
       <c r="D96" s="38"/>
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="185"/>
-      <c r="B97" s="186"/>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="183"/>
+      <c r="B97" s="184"/>
       <c r="C97" s="38"/>
       <c r="D97" s="38"/>
       <c r="E97" s="38"/>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="112" t="s">
-        <v>160</v>
-      </c>
-      <c r="B98" s="51">
-        <v>231400</v>
-      </c>
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="183"/>
+      <c r="B98" s="184"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B99" s="182">
-        <v>0</v>
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="B99" s="51">
+        <v>231400</v>
       </c>
       <c r="C99" s="38"/>
       <c r="D99" s="38"/>
       <c r="E99" s="38"/>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="156" t="s">
-        <v>162</v>
-      </c>
-      <c r="B100" s="135"/>
+    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" s="180">
+        <v>0</v>
+      </c>
       <c r="C100" s="38"/>
       <c r="D100" s="38"/>
       <c r="E100" s="38"/>
       <c r="F100" s="38"/>
     </row>
-    <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="183" t="s">
-        <v>178</v>
-      </c>
-      <c r="B101" s="184">
-        <f>SUM(B98:B100)</f>
-        <v>231400</v>
-      </c>
+    <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="154" t="s">
+        <v>162</v>
+      </c>
+      <c r="B101" s="133"/>
       <c r="C101" s="38"/>
       <c r="D101" s="38"/>
       <c r="E101" s="38"/>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="185"/>
-      <c r="B102" s="186"/>
+    <row r="102" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="181" t="s">
+        <v>178</v>
+      </c>
+      <c r="B102" s="182">
+        <f>SUM(B99:B101)</f>
+        <v>231400</v>
+      </c>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
       <c r="F102" s="38"/>
     </row>
-    <row r="103" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="112" t="s">
-        <v>163</v>
-      </c>
-      <c r="B103" s="51">
-        <v>58418</v>
-      </c>
+    <row r="103" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="183"/>
+      <c r="B103" s="184"/>
       <c r="C103" s="38"/>
       <c r="D103" s="38"/>
       <c r="E103" s="38"/>
       <c r="F103" s="38"/>
     </row>
-    <row r="104" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B104" s="182">
-        <v>0</v>
+    <row r="104" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="B104" s="51">
+        <v>58418</v>
       </c>
       <c r="C104" s="38"/>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
       <c r="F104" s="38"/>
     </row>
-    <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="156" t="s">
-        <v>183</v>
-      </c>
-      <c r="B105" s="135">
+    <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B105" s="180">
         <v>0</v>
       </c>
       <c r="C105" s="38"/>
@@ -3554,165 +3596,183 @@
       <c r="E105" s="38"/>
       <c r="F105" s="38"/>
     </row>
-    <row r="106" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="183" t="s">
-        <v>178</v>
-      </c>
-      <c r="B106" s="184">
-        <f>SUM(B103:B105)</f>
-        <v>58418</v>
+    <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="154" t="s">
+        <v>183</v>
+      </c>
+      <c r="B106" s="133">
+        <v>0</v>
       </c>
       <c r="C106" s="38"/>
       <c r="D106" s="38"/>
       <c r="E106" s="38"/>
       <c r="F106" s="38"/>
     </row>
-    <row r="107" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107"/>
-      <c r="B107" s="48"/>
-      <c r="C107" s="49"/>
-      <c r="D107" s="108"/>
-      <c r="E107" s="108"/>
-    </row>
-    <row r="108" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="112" t="s">
+    <row r="107" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="181" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="182">
+        <f>SUM(B104:B106)</f>
+        <v>58418</v>
+      </c>
+      <c r="C107" s="38"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="38"/>
+      <c r="F107" s="38"/>
+    </row>
+    <row r="108" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+      <c r="B108" s="48"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="107"/>
+      <c r="E108" s="107"/>
+    </row>
+    <row r="109" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="111" t="s">
         <v>177</v>
       </c>
-      <c r="B108" s="51">
+      <c r="B109" s="51">
         <v>281967.3499999987</v>
       </c>
-      <c r="C108" s="49"/>
-      <c r="D108" s="109"/>
-      <c r="E108" s="109"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="24" t="s">
+      <c r="C109" s="49"/>
+      <c r="D109" s="108"/>
+      <c r="E109" s="108"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B109" s="136">
-        <f>-B86-B87</f>
-        <v>-7806121.4699999997</v>
-      </c>
-      <c r="D109" s="38"/>
-      <c r="E109" s="38"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B110" s="52">
-        <f>B121</f>
-        <v>0</v>
+      <c r="B110" s="134">
+        <f>-B87-B88</f>
+        <v>-7505465.6599999992</v>
       </c>
       <c r="D110" s="38"/>
       <c r="E110" s="38"/>
-      <c r="F110" s="48"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B111" s="53">
-        <f>PRORRATEO!G61</f>
-        <v>5479535.0300000003</v>
+        <v>24</v>
+      </c>
+      <c r="B111" s="52">
+        <f>B123</f>
+        <v>0</v>
       </c>
       <c r="D111" s="38"/>
       <c r="E111" s="38"/>
       <c r="F111" s="48"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B112" s="96">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="B112" s="53">
+        <f>PRORRATEO!G61</f>
+        <v>6230781.8999999994</v>
       </c>
       <c r="D112" s="38"/>
       <c r="E112" s="38"/>
       <c r="F112" s="48"/>
     </row>
-    <row r="113" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="B113" s="135">
-        <f>-B93</f>
-        <v>1501954.93</v>
-      </c>
-      <c r="D113" s="134"/>
+        <v>226</v>
+      </c>
+      <c r="B113" s="268">
+        <v>-160000</v>
+      </c>
+      <c r="D113" s="38"/>
       <c r="E113" s="38"/>
       <c r="F113" s="48"/>
     </row>
-    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="54" t="s">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" s="268">
+        <v>-16162</v>
+      </c>
+      <c r="D114" s="38"/>
+      <c r="E114" s="38"/>
+      <c r="F114" s="48"/>
+    </row>
+    <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B115" s="268">
+        <f>-B94</f>
+        <v>2000574.76</v>
+      </c>
+      <c r="D115" s="132"/>
+      <c r="E115" s="38"/>
+      <c r="F115" s="48"/>
+    </row>
+    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="B114" s="55">
-        <f>SUM(B108:C113)</f>
-        <v>-542664.16000000085</v>
-      </c>
-      <c r="D114" s="48"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
-    </row>
-    <row r="115" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="116" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="137" t="s">
+      <c r="B116" s="55">
+        <f>SUM(B109:C115)</f>
+        <v>831696.34999999893</v>
+      </c>
+      <c r="D116" s="48"/>
+      <c r="E116" s="40"/>
+      <c r="F116" s="40"/>
+    </row>
+    <row r="117" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="118" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="135" t="s">
         <v>164</v>
       </c>
-      <c r="B116" s="138">
-        <f>B114+B101</f>
-        <v>-311264.16000000085</v>
-      </c>
-      <c r="D116" s="40"/>
-      <c r="E116" s="40"/>
-      <c r="H116" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="215" t="s">
+      <c r="B118" s="136">
+        <f>B116+B102</f>
+        <v>1063096.3499999989</v>
+      </c>
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="H118" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="B118" s="215"/>
-      <c r="C118" s="215"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="215"/>
-      <c r="B119" s="215"/>
-      <c r="C119" s="215"/>
-    </row>
-    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="56"/>
-      <c r="B120" s="79"/>
-      <c r="C120" s="57"/>
-      <c r="D120" s="43"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B121" s="59">
-        <f>SUM(B120:B120)</f>
-        <v>0</v>
-      </c>
-      <c r="C121" s="60"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M122" s="61"/>
+      <c r="B120" s="208"/>
+      <c r="C120" s="208"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="208"/>
+      <c r="B121" s="208"/>
+      <c r="C121" s="208"/>
+    </row>
+    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="56"/>
+      <c r="B122" s="79"/>
+      <c r="C122" s="57"/>
+      <c r="D122" s="43"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="59">
+        <f>SUM(B122:B122)</f>
+        <v>0</v>
+      </c>
+      <c r="C123" s="60"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M124" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A120:C121"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A118:C119"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
@@ -3722,10 +3782,15 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3736,129 +3801,129 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="66"/>
-      <c r="B1" s="127"/>
+      <c r="B1" s="126"/>
       <c r="C1" s="67"/>
       <c r="D1" s="67"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="261" t="str">
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="218" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="261"/>
-      <c r="O1" s="261"/>
-      <c r="P1" s="262"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="219"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="128"/>
-      <c r="C2" s="140">
+      <c r="B2" s="127"/>
+      <c r="C2" s="138">
         <f>7325605.04-C5-305000.04-15405.58</f>
         <v>5300000</v>
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
-      <c r="F2" s="269"/>
-      <c r="G2" s="269"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="263"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="263"/>
-      <c r="P2" s="264"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="220"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="221"/>
       <c r="Q2" s="62"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="128"/>
-      <c r="C3" s="140">
+      <c r="B3" s="127"/>
+      <c r="C3" s="138">
         <v>0</v>
       </c>
       <c r="D3" s="68"/>
       <c r="E3" s="68"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="263"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
-      <c r="P3" s="264"/>
+      <c r="J3" s="220"/>
+      <c r="K3" s="220"/>
+      <c r="L3" s="220"/>
+      <c r="M3" s="220"/>
+      <c r="N3" s="220"/>
+      <c r="O3" s="220"/>
+      <c r="P3" s="221"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="128"/>
-      <c r="C4" s="140">
+      <c r="B4" s="127"/>
+      <c r="C4" s="138">
         <v>182823.01</v>
       </c>
       <c r="D4" s="68"/>
       <c r="E4" s="68"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="263"/>
-      <c r="K4" s="263"/>
-      <c r="L4" s="263"/>
-      <c r="M4" s="263"/>
-      <c r="N4" s="263"/>
-      <c r="O4" s="263"/>
-      <c r="P4" s="264"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="221"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="139" t="s">
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="137" t="s">
         <v>166</v>
       </c>
-      <c r="B5" s="129"/>
-      <c r="C5" s="141">
+      <c r="B5" s="128"/>
+      <c r="C5" s="139">
         <v>1705199.42</v>
       </c>
       <c r="D5" s="69"/>
@@ -3867,207 +3932,207 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
-      <c r="M5" s="265"/>
-      <c r="N5" s="265"/>
-      <c r="O5" s="265"/>
-      <c r="P5" s="266"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
+      <c r="P5" s="223"/>
       <c r="Q5" s="62"/>
     </row>
-    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="234" t="s">
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="230" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="235"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="236"/>
-      <c r="O6" s="236"/>
-      <c r="P6" s="237"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="232"/>
+      <c r="N6" s="232"/>
+      <c r="O6" s="232"/>
+      <c r="P6" s="233"/>
       <c r="Q6" s="62"/>
     </row>
-    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="238"/>
-      <c r="B7" s="239"/>
-      <c r="C7" s="239"/>
-      <c r="D7" s="239"/>
-      <c r="E7" s="239"/>
-      <c r="F7" s="239"/>
-      <c r="G7" s="239"/>
-      <c r="H7" s="239"/>
-      <c r="I7" s="239"/>
-      <c r="J7" s="239"/>
-      <c r="K7" s="239"/>
-      <c r="L7" s="239"/>
-      <c r="M7" s="239"/>
-      <c r="N7" s="239"/>
-      <c r="O7" s="239"/>
-      <c r="P7" s="240"/>
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="234"/>
+      <c r="B7" s="235"/>
+      <c r="C7" s="235"/>
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235"/>
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="235"/>
+      <c r="K7" s="235"/>
+      <c r="L7" s="235"/>
+      <c r="M7" s="235"/>
+      <c r="N7" s="235"/>
+      <c r="O7" s="235"/>
+      <c r="P7" s="236"/>
       <c r="Q7" s="62"/>
     </row>
-    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="238"/>
-      <c r="B8" s="239"/>
-      <c r="C8" s="239"/>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="239"/>
-      <c r="G8" s="239"/>
-      <c r="H8" s="239"/>
-      <c r="I8" s="239"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
-      <c r="N8" s="239"/>
-      <c r="O8" s="239"/>
-      <c r="P8" s="240"/>
+    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="234"/>
+      <c r="B8" s="235"/>
+      <c r="C8" s="235"/>
+      <c r="D8" s="235"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="235"/>
+      <c r="N8" s="235"/>
+      <c r="O8" s="235"/>
+      <c r="P8" s="236"/>
       <c r="Q8" s="62"/>
     </row>
-    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="238"/>
-      <c r="B9" s="239"/>
-      <c r="C9" s="239"/>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
-      <c r="M9" s="239"/>
-      <c r="N9" s="239"/>
-      <c r="O9" s="239"/>
-      <c r="P9" s="240"/>
+    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="234"/>
+      <c r="B9" s="235"/>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
+      <c r="N9" s="235"/>
+      <c r="O9" s="235"/>
+      <c r="P9" s="236"/>
       <c r="Q9" s="62"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="241"/>
-      <c r="B10" s="242"/>
-      <c r="C10" s="242"/>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
-      <c r="M10" s="242"/>
-      <c r="N10" s="242"/>
-      <c r="O10" s="242"/>
-      <c r="P10" s="243"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="254" t="s">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="237"/>
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="239"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="248" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="255"/>
-      <c r="C11" s="255"/>
-      <c r="D11" s="255"/>
-      <c r="E11" s="255"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
-      <c r="H11" s="255"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="255"/>
-      <c r="K11" s="255"/>
-      <c r="L11" s="255"/>
-      <c r="M11" s="255"/>
-      <c r="N11" s="255"/>
-      <c r="O11" s="255"/>
-      <c r="P11" s="256"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="244" t="s">
+      <c r="B11" s="249"/>
+      <c r="C11" s="249"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
+      <c r="M11" s="249"/>
+      <c r="N11" s="249"/>
+      <c r="O11" s="249"/>
+      <c r="P11" s="250"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="240" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="259" t="s">
+      <c r="B12" s="253" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="246" t="s">
+      <c r="C12" s="242" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="246" t="s">
+      <c r="D12" s="242" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="246" t="s">
+      <c r="E12" s="242" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="248" t="s">
+      <c r="F12" s="224" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="250" t="s">
+      <c r="G12" s="244" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="252" t="s">
+      <c r="H12" s="246" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="248" t="s">
+      <c r="I12" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="248" t="s">
+      <c r="J12" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="248" t="s">
+      <c r="K12" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="259" t="s">
+      <c r="L12" s="253" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="248" t="s">
+      <c r="M12" s="224" t="s">
         <v>167</v>
       </c>
-      <c r="N12" s="257" t="s">
+      <c r="N12" s="251" t="s">
         <v>184</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="267" t="s">
+      <c r="P12" s="226" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="245"/>
-      <c r="B13" s="260"/>
-      <c r="C13" s="247"/>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="253"/>
-      <c r="I13" s="249"/>
-      <c r="J13" s="249"/>
-      <c r="K13" s="249"/>
-      <c r="L13" s="260"/>
-      <c r="M13" s="249"/>
-      <c r="N13" s="258"/>
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="241"/>
+      <c r="B13" s="254"/>
+      <c r="C13" s="243"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="254"/>
+      <c r="M13" s="225"/>
+      <c r="N13" s="252"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P13" s="268"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="227"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
         <v>1</v>
       </c>
-      <c r="B14" s="130" t="s">
+      <c r="B14" s="129" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="72" t="s">
@@ -4078,11 +4143,11 @@
         <v>5.22</v>
       </c>
       <c r="F14" s="63">
-        <v>322564.01</v>
-      </c>
-      <c r="G14" s="63">
+        <v>375215.01</v>
+      </c>
+      <c r="G14" s="269">
         <f t="shared" ref="G14" si="0">F14</f>
-        <v>322564.01</v>
+        <v>375215.01</v>
       </c>
       <c r="H14" s="75">
         <f t="shared" ref="H14:H59" si="1">F14-G14</f>
@@ -4121,11 +4186,11 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="83">
         <v>2</v>
       </c>
-      <c r="B15" s="130" t="s">
+      <c r="B15" s="129" t="s">
         <v>74</v>
       </c>
       <c r="C15" s="72" t="s">
@@ -4138,16 +4203,16 @@
         <v>3.4</v>
       </c>
       <c r="F15" s="63">
-        <v>33276.019999999997</v>
+        <v>278667.02</v>
       </c>
       <c r="G15" s="63"/>
       <c r="H15" s="75">
         <f t="shared" si="1"/>
-        <v>33276.019999999997</v>
+        <v>278667.02</v>
       </c>
       <c r="I15" s="75">
         <f t="shared" ref="I15:I59" si="4">IF(H15&gt;0,H15*3%,0)</f>
-        <v>998.28059999999982</v>
+        <v>8360.0105999999996</v>
       </c>
       <c r="J15" s="82">
         <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
@@ -4168,22 +4233,22 @@
       <c r="N15" s="82"/>
       <c r="O15" s="76">
         <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>278667.02</v>
+        <v>531420.02</v>
       </c>
       <c r="P15" s="91">
         <f t="shared" si="3"/>
-        <v>287027.02</v>
+        <v>547363.02</v>
       </c>
       <c r="Q15" s="40">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="83">
         <v>3</v>
       </c>
-      <c r="B16" s="130" t="s">
+      <c r="B16" s="129" t="s">
         <v>75</v>
       </c>
       <c r="C16" s="72" t="s">
@@ -4196,15 +4261,14 @@
         <v>2.54</v>
       </c>
       <c r="F16" s="63">
-        <v>160932.03</v>
-      </c>
-      <c r="G16" s="63">
-        <f>F16</f>
-        <v>160932.03</v>
+        <v>182576.03</v>
+      </c>
+      <c r="G16" s="269">
+        <v>183000</v>
       </c>
       <c r="H16" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-423.97000000000116</v>
       </c>
       <c r="I16" s="75">
         <f t="shared" si="4"/>
@@ -4229,11 +4293,11 @@
       <c r="N16" s="82"/>
       <c r="O16" s="76">
         <f t="shared" si="8"/>
-        <v>182576.03</v>
+        <v>182152.03</v>
       </c>
       <c r="P16" s="91">
         <f t="shared" si="3"/>
-        <v>188053.03</v>
+        <v>187617.03</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
@@ -4243,11 +4307,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="83">
         <v>4</v>
       </c>
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="129" t="s">
         <v>76</v>
       </c>
       <c r="C17" s="72" t="s">
@@ -4260,15 +4324,15 @@
         <v>5.19</v>
       </c>
       <c r="F17" s="63">
-        <v>337083.04</v>
-      </c>
-      <c r="G17" s="63">
-        <f>403280-G55-G44</f>
-        <v>348856.27</v>
+        <v>361285.04</v>
+      </c>
+      <c r="G17" s="269">
+        <f>435125-G55-G44</f>
+        <v>374026.27</v>
       </c>
       <c r="H17" s="75">
         <f t="shared" si="1"/>
-        <v>-11773.23000000004</v>
+        <v>-12741.23000000004</v>
       </c>
       <c r="I17" s="75">
         <f t="shared" si="4"/>
@@ -4293,11 +4357,11 @@
       <c r="N17" s="82"/>
       <c r="O17" s="76">
         <f t="shared" si="8"/>
-        <v>361285.04</v>
+        <v>360317.04</v>
       </c>
       <c r="P17" s="91">
         <f t="shared" si="3"/>
-        <v>372124.04</v>
+        <v>371127.03999999998</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="9"/>
@@ -4307,11 +4371,11 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="83">
         <v>5</v>
       </c>
-      <c r="B18" s="130" t="s">
+      <c r="B18" s="129" t="s">
         <v>72</v>
       </c>
       <c r="C18" s="72" t="s">
@@ -4324,7 +4388,7 @@
         <v>3.4</v>
       </c>
       <c r="F18" s="63">
-        <v>217691.05</v>
+        <v>244044.05</v>
       </c>
       <c r="G18" s="63">
         <f>77540+140500</f>
@@ -4332,11 +4396,11 @@
       </c>
       <c r="H18" s="75">
         <f t="shared" si="1"/>
-        <v>-348.95000000001164</v>
+        <v>26004.049999999988</v>
       </c>
       <c r="I18" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>780.12149999999963</v>
       </c>
       <c r="J18" s="82">
         <f t="shared" si="5"/>
@@ -4357,22 +4421,22 @@
       <c r="N18" s="82"/>
       <c r="O18" s="76">
         <f t="shared" si="8"/>
-        <v>244044.05</v>
+        <v>271177.05</v>
       </c>
       <c r="P18" s="91">
         <f t="shared" si="3"/>
-        <v>251365.05</v>
+        <v>279312.05</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="83">
         <v>6</v>
       </c>
-      <c r="B19" s="130" t="s">
+      <c r="B19" s="129" t="s">
         <v>77</v>
       </c>
       <c r="C19" s="72" t="s">
@@ -4385,11 +4449,11 @@
         <v>2.54</v>
       </c>
       <c r="F19" s="63">
-        <v>162628.06</v>
-      </c>
-      <c r="G19" s="63">
+        <v>182576.06</v>
+      </c>
+      <c r="G19" s="269">
         <f>F19</f>
-        <v>162628.06</v>
+        <v>182576.06</v>
       </c>
       <c r="H19" s="75">
         <f t="shared" si="1"/>
@@ -4429,11 +4493,11 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="83">
         <v>7</v>
       </c>
-      <c r="B20" s="130" t="s">
+      <c r="B20" s="129" t="s">
         <v>78</v>
       </c>
       <c r="C20" s="72" t="s">
@@ -4444,11 +4508,11 @@
         <v>5.19</v>
       </c>
       <c r="F20" s="63">
-        <v>332298.07</v>
-      </c>
-      <c r="G20" s="63">
+        <v>373058.07</v>
+      </c>
+      <c r="G20" s="269">
         <f t="shared" ref="G20:G25" si="10">F20</f>
-        <v>332298.07</v>
+        <v>373058.07</v>
       </c>
       <c r="H20" s="75">
         <f t="shared" si="1"/>
@@ -4488,11 +4552,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="83">
         <v>8</v>
       </c>
-      <c r="B21" s="130" t="s">
+      <c r="B21" s="129" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="72" t="s">
@@ -4503,11 +4567,11 @@
         <v>3.4</v>
       </c>
       <c r="F21" s="63">
-        <v>217691.08</v>
-      </c>
-      <c r="G21" s="63">
+        <v>244393.08</v>
+      </c>
+      <c r="G21" s="269">
         <f t="shared" si="10"/>
-        <v>217691.08</v>
+        <v>244393.08</v>
       </c>
       <c r="H21" s="75">
         <f t="shared" si="1"/>
@@ -4547,11 +4611,11 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="83">
         <v>9</v>
       </c>
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="129" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="72" t="s">
@@ -4564,11 +4628,11 @@
         <v>2.54</v>
       </c>
       <c r="F22" s="63">
-        <v>162628.09</v>
-      </c>
-      <c r="G22" s="63">
+        <v>182576.09</v>
+      </c>
+      <c r="G22" s="269">
         <f t="shared" si="10"/>
-        <v>162628.09</v>
+        <v>182576.09</v>
       </c>
       <c r="H22" s="75">
         <f t="shared" si="1"/>
@@ -4608,11 +4672,11 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="83">
         <v>10</v>
       </c>
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="129" t="s">
         <v>80</v>
       </c>
       <c r="C23" s="72" t="s">
@@ -4623,11 +4687,11 @@
         <v>5.19</v>
       </c>
       <c r="F23" s="63">
-        <v>332298.09999999998</v>
-      </c>
-      <c r="G23" s="63">
+        <v>373058.1</v>
+      </c>
+      <c r="G23" s="269">
         <f t="shared" si="10"/>
-        <v>332298.09999999998</v>
+        <v>373058.1</v>
       </c>
       <c r="H23" s="75">
         <f t="shared" si="1"/>
@@ -4667,11 +4731,11 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="83">
         <v>11</v>
       </c>
-      <c r="B24" s="130" t="s">
+      <c r="B24" s="129" t="s">
         <v>81</v>
       </c>
       <c r="C24" s="72" t="s">
@@ -4684,11 +4748,11 @@
         <v>3.4</v>
       </c>
       <c r="F24" s="63">
-        <v>217691.11</v>
-      </c>
-      <c r="G24" s="63">
+        <v>244393.11</v>
+      </c>
+      <c r="G24" s="269">
         <f t="shared" si="10"/>
-        <v>217691.11</v>
+        <v>244393.11</v>
       </c>
       <c r="H24" s="75">
         <f t="shared" si="1"/>
@@ -4728,11 +4792,11 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83">
         <v>12</v>
       </c>
-      <c r="B25" s="130" t="s">
+      <c r="B25" s="129" t="s">
         <v>82</v>
       </c>
       <c r="C25" s="72" t="s">
@@ -4745,11 +4809,11 @@
         <v>2.54</v>
       </c>
       <c r="F25" s="63">
-        <v>162628.12</v>
-      </c>
-      <c r="G25" s="63">
+        <v>182576.12</v>
+      </c>
+      <c r="G25" s="269">
         <f t="shared" si="10"/>
-        <v>162628.12</v>
+        <v>182576.12</v>
       </c>
       <c r="H25" s="75">
         <f t="shared" si="1"/>
@@ -4789,129 +4853,129 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="142">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="83">
         <v>13</v>
       </c>
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="72" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="145"/>
-      <c r="E26" s="146">
+      <c r="D26" s="77"/>
+      <c r="E26" s="74">
         <v>5.19</v>
       </c>
-      <c r="F26" s="147">
-        <v>320441.13</v>
-      </c>
-      <c r="G26" s="147">
-        <f>335330.44-G45</f>
-        <v>330208.12</v>
-      </c>
-      <c r="H26" s="148">
+      <c r="F26" s="63">
+        <v>363291.13</v>
+      </c>
+      <c r="G26" s="269">
+        <f>F26</f>
+        <v>363291.13</v>
+      </c>
+      <c r="H26" s="75">
         <f t="shared" si="1"/>
-        <v>-9766.9899999999907</v>
-      </c>
-      <c r="I26" s="148">
+        <v>0</v>
+      </c>
+      <c r="I26" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="149">
+      <c r="J26" s="82">
         <f t="shared" si="5"/>
         <v>275070.00000000006</v>
       </c>
-      <c r="K26" s="149">
+      <c r="K26" s="82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="149">
+      <c r="L26" s="82">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="149">
+      <c r="M26" s="82">
         <f t="shared" si="7"/>
         <v>88499.849898</v>
       </c>
-      <c r="N26" s="149"/>
-      <c r="O26" s="150">
+      <c r="N26" s="82"/>
+      <c r="O26" s="76">
         <f t="shared" si="8"/>
-        <v>363291.13</v>
-      </c>
-      <c r="P26" s="151">
+        <v>373058.13</v>
+      </c>
+      <c r="P26" s="91">
         <f t="shared" si="3"/>
-        <v>374190.13</v>
+        <v>384250.13</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="142">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="140">
         <v>14</v>
       </c>
-      <c r="B27" s="143" t="s">
+      <c r="B27" s="141" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="142" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="145"/>
-      <c r="E27" s="146">
+      <c r="D27" s="143"/>
+      <c r="E27" s="144">
         <v>3.4</v>
       </c>
-      <c r="F27" s="147">
-        <v>217691.14</v>
-      </c>
-      <c r="G27" s="147">
-        <f>288191.52-G51</f>
-        <v>226085.14</v>
-      </c>
-      <c r="H27" s="148">
+      <c r="F27" s="145">
+        <v>235999.14</v>
+      </c>
+      <c r="G27" s="270">
+        <f>314895.52-G51</f>
+        <v>245171.14</v>
+      </c>
+      <c r="H27" s="146">
         <f t="shared" si="1"/>
-        <v>-8394</v>
-      </c>
-      <c r="I27" s="148">
+        <v>-9172</v>
+      </c>
+      <c r="I27" s="146">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="149">
+      <c r="J27" s="147">
         <f t="shared" si="5"/>
         <v>180200</v>
       </c>
-      <c r="K27" s="149">
+      <c r="K27" s="147">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="149">
+      <c r="L27" s="147">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="149">
+      <c r="M27" s="147">
         <f t="shared" si="7"/>
         <v>57976.780279999999</v>
       </c>
-      <c r="N27" s="149"/>
-      <c r="O27" s="150">
+      <c r="N27" s="147"/>
+      <c r="O27" s="148">
         <f t="shared" si="8"/>
-        <v>235999.14</v>
-      </c>
-      <c r="P27" s="151">
+        <v>235221.14</v>
+      </c>
+      <c r="P27" s="149">
         <f t="shared" si="3"/>
-        <v>243079.14</v>
+        <v>242278.14</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="83">
         <v>15</v>
       </c>
-      <c r="B28" s="130" t="s">
+      <c r="B28" s="129" t="s">
         <v>85</v>
       </c>
       <c r="C28" s="72" t="s">
@@ -4924,11 +4988,11 @@
         <v>2.54</v>
       </c>
       <c r="F28" s="63">
-        <v>162628.15</v>
-      </c>
-      <c r="G28" s="63">
-        <f>F28</f>
-        <v>162628.15</v>
+        <v>182576.15</v>
+      </c>
+      <c r="G28" s="269">
+        <f t="shared" ref="G28" si="11">F28</f>
+        <v>182576.15</v>
       </c>
       <c r="H28" s="75">
         <f t="shared" si="1"/>
@@ -4968,11 +5032,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="83">
         <v>16</v>
       </c>
-      <c r="B29" s="130" t="s">
+      <c r="B29" s="129" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="72" t="s">
@@ -4983,11 +5047,11 @@
         <v>5.19</v>
       </c>
       <c r="F29" s="63">
-        <v>332298.15999999997</v>
-      </c>
-      <c r="G29" s="63">
+        <v>373058.16</v>
+      </c>
+      <c r="G29" s="269">
         <f>F29</f>
-        <v>332298.15999999997</v>
+        <v>373058.16</v>
       </c>
       <c r="H29" s="75">
         <f t="shared" si="1"/>
@@ -5027,11 +5091,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="83">
         <v>17</v>
       </c>
-      <c r="B30" s="130" t="s">
+      <c r="B30" s="129" t="s">
         <v>87</v>
       </c>
       <c r="C30" s="72" t="s">
@@ -5044,15 +5108,15 @@
         <v>3.4</v>
       </c>
       <c r="F30" s="63">
-        <v>217688.17</v>
-      </c>
-      <c r="G30" s="63">
-        <f>268481-G53</f>
-        <v>219179.6</v>
+        <v>242901.17</v>
+      </c>
+      <c r="G30" s="269">
+        <f>243901.17</f>
+        <v>243901.17</v>
       </c>
       <c r="H30" s="75">
         <f t="shared" si="1"/>
-        <v>-1491.429999999993</v>
+        <v>-1000</v>
       </c>
       <c r="I30" s="75">
         <f t="shared" si="4"/>
@@ -5077,22 +5141,22 @@
       <c r="N30" s="82"/>
       <c r="O30" s="76">
         <f t="shared" si="8"/>
-        <v>242901.17</v>
+        <v>243393.17</v>
       </c>
       <c r="P30" s="91">
         <f t="shared" si="3"/>
-        <v>250188.17</v>
+        <v>250695.17</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="83">
         <v>18</v>
       </c>
-      <c r="B31" s="130" t="s">
+      <c r="B31" s="129" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="72" t="s">
@@ -5103,16 +5167,16 @@
         <v>2.54</v>
       </c>
       <c r="F31" s="63">
-        <v>1615606.18</v>
+        <v>1846650.18</v>
       </c>
       <c r="G31" s="63"/>
       <c r="H31" s="75">
         <f t="shared" si="1"/>
-        <v>1615606.18</v>
+        <v>1846650.18</v>
       </c>
       <c r="I31" s="75">
         <f t="shared" si="4"/>
-        <v>48468.185399999995</v>
+        <v>55399.505399999995</v>
       </c>
       <c r="J31" s="82">
         <f t="shared" si="5"/>
@@ -5133,22 +5197,22 @@
       <c r="N31" s="82"/>
       <c r="O31" s="76">
         <f t="shared" si="8"/>
-        <v>1846650.18</v>
+        <v>2084625.18</v>
       </c>
       <c r="P31" s="91">
         <f t="shared" si="3"/>
-        <v>1902050.18</v>
+        <v>2147164.1799999997</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="83">
         <v>19</v>
       </c>
-      <c r="B32" s="130" t="s">
+      <c r="B32" s="129" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="72" t="s">
@@ -5159,18 +5223,18 @@
         <v>5.19</v>
       </c>
       <c r="F32" s="63">
-        <v>1143639.19</v>
+        <v>1594507.19</v>
       </c>
       <c r="G32" s="63">
         <v>0</v>
       </c>
       <c r="H32" s="75">
         <f t="shared" si="1"/>
-        <v>1143639.19</v>
+        <v>1594507.19</v>
       </c>
       <c r="I32" s="75">
         <f t="shared" si="4"/>
-        <v>34309.1757</v>
+        <v>47835.215699999993</v>
       </c>
       <c r="J32" s="82">
         <f t="shared" si="5"/>
@@ -5193,78 +5257,78 @@
       </c>
       <c r="O32" s="76">
         <f t="shared" si="8"/>
-        <v>1594507.19</v>
+        <v>2058901.19</v>
       </c>
       <c r="P32" s="91">
         <f t="shared" si="3"/>
-        <v>1642342.19</v>
+        <v>2120668.19</v>
       </c>
       <c r="Q32" s="40">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="201">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="140">
         <v>20</v>
       </c>
-      <c r="B33" s="202" t="s">
+      <c r="B33" s="141" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="203" t="s">
+      <c r="C33" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="188"/>
-      <c r="E33" s="189">
+      <c r="D33" s="186"/>
+      <c r="E33" s="187">
         <v>3.4</v>
       </c>
-      <c r="F33" s="190">
-        <v>217691.2</v>
-      </c>
-      <c r="G33" s="190">
-        <f>229946.49-G47</f>
-        <v>224824.15</v>
-      </c>
-      <c r="H33" s="191">
+      <c r="F33" s="188">
+        <v>237260.2</v>
+      </c>
+      <c r="G33" s="271">
+        <f>249002-G47</f>
+        <v>243251.66</v>
+      </c>
+      <c r="H33" s="189">
         <f t="shared" si="1"/>
-        <v>-7132.9499999999825</v>
-      </c>
-      <c r="I33" s="191"/>
-      <c r="J33" s="192">
+        <v>-5991.4599999999919</v>
+      </c>
+      <c r="I33" s="189"/>
+      <c r="J33" s="190">
         <f t="shared" si="5"/>
         <v>180200</v>
       </c>
-      <c r="K33" s="192">
+      <c r="K33" s="190">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="192">
+      <c r="L33" s="190">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="192">
+      <c r="M33" s="190">
         <f t="shared" si="7"/>
         <v>57976.780279999999</v>
       </c>
-      <c r="N33" s="192"/>
-      <c r="O33" s="193">
+      <c r="N33" s="190"/>
+      <c r="O33" s="191">
         <f t="shared" si="8"/>
-        <v>237260.2</v>
-      </c>
-      <c r="P33" s="194">
+        <v>238401.2</v>
+      </c>
+      <c r="P33" s="192">
         <f t="shared" si="3"/>
-        <v>244378.2</v>
+        <v>245553.2</v>
       </c>
       <c r="Q33" s="40">
-        <f t="shared" ref="Q33:Q59" si="11">Q32+0.01</f>
+        <f t="shared" ref="Q33:Q59" si="12">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="83">
         <v>21</v>
       </c>
-      <c r="B34" s="130" t="s">
+      <c r="B34" s="129" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="78" t="s">
@@ -5277,11 +5341,11 @@
         <v>2.54</v>
       </c>
       <c r="F34" s="63">
-        <v>162628.21</v>
-      </c>
-      <c r="G34" s="63">
-        <f t="shared" ref="G34:G35" si="12">F34</f>
-        <v>162628.21</v>
+        <v>182576.21</v>
+      </c>
+      <c r="G34" s="269">
+        <f t="shared" ref="G34:G35" si="13">F34</f>
+        <v>182576.21</v>
       </c>
       <c r="H34" s="75">
         <f t="shared" si="1"/>
@@ -5317,16 +5381,16 @@
         <v>188053.21</v>
       </c>
       <c r="Q34" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="83">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="130" t="s">
+      <c r="B35" s="129" t="s">
         <v>92</v>
       </c>
       <c r="C35" s="78" t="s">
@@ -5339,11 +5403,11 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="F35" s="63">
-        <v>316292.21999999997</v>
-      </c>
-      <c r="G35" s="63">
-        <f t="shared" si="12"/>
-        <v>316292.21999999997</v>
+        <v>355088.22</v>
+      </c>
+      <c r="G35" s="269">
+        <f t="shared" si="13"/>
+        <v>355088.22</v>
       </c>
       <c r="H35" s="75">
         <f t="shared" si="1"/>
@@ -5375,40 +5439,41 @@
         <v>355088.22</v>
       </c>
       <c r="P35" s="91">
-        <f t="shared" ref="P35:P59" si="13">ROUND(O35*3%,0) + O35</f>
+        <f t="shared" ref="P35:P59" si="14">ROUND(O35*3%,0) + O35</f>
         <v>365741.22</v>
       </c>
       <c r="Q35" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="206">
-        <f t="shared" ref="A36:A59" si="14">A35+1</f>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="83">
+        <f t="shared" ref="A36:A59" si="15">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="207" t="s">
+      <c r="B36" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="208" t="s">
+      <c r="C36" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="209" t="s">
+      <c r="D36" s="77" t="s">
         <v>156</v>
       </c>
       <c r="E36" s="74">
         <v>3.28</v>
       </c>
       <c r="F36" s="63">
-        <v>210877.23</v>
-      </c>
-      <c r="G36" s="63">
-        <v>217223</v>
+        <v>229421.23</v>
+      </c>
+      <c r="G36" s="269">
+        <f>229441</f>
+        <v>229441</v>
       </c>
       <c r="H36" s="75">
         <f t="shared" si="1"/>
-        <v>-6345.7699999999895</v>
+        <v>-19.769999999989523</v>
       </c>
       <c r="I36" s="75">
         <f t="shared" si="4"/>
@@ -5433,23 +5498,23 @@
       <c r="N36" s="82"/>
       <c r="O36" s="76">
         <f t="shared" si="8"/>
-        <v>229421.23</v>
+        <v>235747.23</v>
       </c>
       <c r="P36" s="91">
-        <f t="shared" si="13"/>
-        <v>236304.23</v>
+        <f t="shared" si="14"/>
+        <v>242819.23</v>
       </c>
       <c r="Q36" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="B37" s="130" t="s">
+      <c r="B37" s="129" t="s">
         <v>94</v>
       </c>
       <c r="C37" s="78" t="s">
@@ -5460,18 +5525,18 @@
         <v>2.41</v>
       </c>
       <c r="F37" s="63">
-        <v>154304.24</v>
+        <v>168602.23999999999</v>
       </c>
       <c r="G37" s="63">
         <v>158933.24</v>
       </c>
       <c r="H37" s="75">
         <f t="shared" si="1"/>
-        <v>-4629</v>
+        <v>9669</v>
       </c>
       <c r="I37" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>290.07</v>
       </c>
       <c r="J37" s="82">
         <f t="shared" si="5"/>
@@ -5492,26 +5557,26 @@
       <c r="N37" s="82"/>
       <c r="O37" s="76">
         <f t="shared" si="8"/>
-        <v>168602.23999999999</v>
+        <v>183190.24</v>
       </c>
       <c r="P37" s="91">
-        <f t="shared" si="13"/>
-        <v>173660.24</v>
+        <f t="shared" si="14"/>
+        <v>188686.24</v>
       </c>
       <c r="Q37" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="212">
-        <f t="shared" si="14"/>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="83">
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="B38" s="213" t="s">
+      <c r="B38" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="214" t="s">
+      <c r="C38" s="78" t="s">
         <v>136</v>
       </c>
       <c r="D38" s="77"/>
@@ -5519,16 +5584,19 @@
         <v>0.44</v>
       </c>
       <c r="F38" s="63">
-        <v>53808.25</v>
-      </c>
-      <c r="G38" s="63"/>
+        <v>87050.25</v>
+      </c>
+      <c r="G38" s="269">
+        <f>16162+70888</f>
+        <v>87050</v>
+      </c>
       <c r="H38" s="75">
         <f t="shared" si="1"/>
-        <v>53808.25</v>
+        <v>0.25</v>
       </c>
       <c r="I38" s="75">
         <f t="shared" si="4"/>
-        <v>1614.2474999999999</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="J38" s="82">
         <f t="shared" si="5"/>
@@ -5549,26 +5617,26 @@
       <c r="N38" s="82"/>
       <c r="O38" s="76">
         <f t="shared" si="8"/>
-        <v>87050.25</v>
+        <v>31628.25</v>
       </c>
       <c r="P38" s="91">
-        <f t="shared" si="13"/>
-        <v>89662.25</v>
+        <f t="shared" si="14"/>
+        <v>32577.25</v>
       </c>
       <c r="Q38" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>26</v>
       </c>
-      <c r="B39" s="130" t="s">
+      <c r="B39" s="129" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="78" t="s">
@@ -5579,11 +5647,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F39" s="63">
-        <v>35215.26</v>
+        <v>39534.26</v>
       </c>
       <c r="G39" s="63">
-        <f t="shared" ref="G39:G40" si="15">F39</f>
-        <v>35215.26</v>
+        <f t="shared" ref="G39:G40" si="16">F39</f>
+        <v>39534.26</v>
       </c>
       <c r="H39" s="75">
         <f t="shared" si="1"/>
@@ -5615,20 +5683,20 @@
         <v>39534.26</v>
       </c>
       <c r="P39" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>40720.26</v>
       </c>
       <c r="Q39" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>27</v>
       </c>
-      <c r="B40" s="130" t="s">
+      <c r="B40" s="129" t="s">
         <v>96</v>
       </c>
       <c r="C40" s="78" t="s">
@@ -5639,11 +5707,11 @@
         <v>0.53</v>
       </c>
       <c r="F40" s="63">
-        <v>32741.27</v>
-      </c>
-      <c r="G40" s="63">
-        <f t="shared" si="15"/>
-        <v>32741.27</v>
+        <v>38097.269999999997</v>
+      </c>
+      <c r="G40" s="269">
+        <f t="shared" si="16"/>
+        <v>38097.269999999997</v>
       </c>
       <c r="H40" s="75">
         <f t="shared" si="1"/>
@@ -5675,20 +5743,20 @@
         <v>38097.269999999997</v>
       </c>
       <c r="P40" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>39240.269999999997</v>
       </c>
       <c r="Q40" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
-      <c r="B41" s="130" t="s">
+      <c r="B41" s="129" t="s">
         <v>98</v>
       </c>
       <c r="C41" s="78" t="s">
@@ -5701,16 +5769,16 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="F41" s="63">
-        <v>18568.28</v>
+        <v>39971.279999999999</v>
       </c>
       <c r="G41" s="63"/>
       <c r="H41" s="75">
         <f t="shared" si="1"/>
-        <v>18568.28</v>
+        <v>39971.279999999999</v>
       </c>
       <c r="I41" s="75">
         <f t="shared" si="4"/>
-        <v>557.0483999999999</v>
+        <v>1199.1383999999998</v>
       </c>
       <c r="J41" s="82">
         <f t="shared" si="5"/>
@@ -5731,23 +5799,23 @@
       <c r="N41" s="82"/>
       <c r="O41" s="76">
         <f t="shared" si="8"/>
-        <v>39971.279999999999</v>
+        <v>62016.28</v>
       </c>
       <c r="P41" s="91">
-        <f t="shared" si="13"/>
-        <v>41170.28</v>
+        <f t="shared" si="14"/>
+        <v>63876.28</v>
       </c>
       <c r="Q41" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29</v>
       </c>
-      <c r="B42" s="130" t="s">
+      <c r="B42" s="129" t="s">
         <v>99</v>
       </c>
       <c r="C42" s="78" t="s">
@@ -5760,11 +5828,11 @@
         <v>0.08</v>
       </c>
       <c r="F42" s="63">
-        <v>5122.29</v>
-      </c>
-      <c r="G42" s="63">
-        <f t="shared" ref="G42:G43" si="16">F42</f>
-        <v>5122.29</v>
+        <v>5750.29</v>
+      </c>
+      <c r="G42" s="269">
+        <f t="shared" ref="G42:G43" si="17">F42</f>
+        <v>5750.29</v>
       </c>
       <c r="H42" s="75">
         <f t="shared" si="1"/>
@@ -5796,20 +5864,20 @@
         <v>5750.29</v>
       </c>
       <c r="P42" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5923.29</v>
       </c>
       <c r="Q42" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="B43" s="130" t="s">
+      <c r="B43" s="129" t="s">
         <v>100</v>
       </c>
       <c r="C43" s="78" t="s">
@@ -5820,11 +5888,11 @@
         <v>0.08</v>
       </c>
       <c r="F43" s="63">
-        <v>4942.3</v>
-      </c>
-      <c r="G43" s="63">
-        <f t="shared" si="16"/>
-        <v>4942.3</v>
+        <v>5750.3</v>
+      </c>
+      <c r="G43" s="269">
+        <f t="shared" si="17"/>
+        <v>5750.3</v>
       </c>
       <c r="H43" s="75">
         <f t="shared" si="1"/>
@@ -5856,20 +5924,20 @@
         <v>5750.3</v>
       </c>
       <c r="P43" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5923.3</v>
       </c>
       <c r="Q43" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
-      <c r="B44" s="130" t="s">
+      <c r="B44" s="129" t="s">
         <v>101</v>
       </c>
       <c r="C44" s="78" t="s">
@@ -5882,11 +5950,11 @@
         <v>0.08</v>
       </c>
       <c r="F44" s="63">
-        <v>5122.3100000000004</v>
-      </c>
-      <c r="G44" s="63">
+        <v>5750.31</v>
+      </c>
+      <c r="G44" s="269">
         <f>F44</f>
-        <v>5122.3100000000004</v>
+        <v>5750.31</v>
       </c>
       <c r="H44" s="75">
         <f t="shared" si="1"/>
@@ -5918,23 +5986,23 @@
         <v>5750.31</v>
       </c>
       <c r="P44" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5923.31</v>
       </c>
       <c r="Q44" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>32</v>
       </c>
-      <c r="B45" s="130" t="s">
+      <c r="B45" s="129" t="s">
         <v>102</v>
       </c>
       <c r="C45" s="78" t="s">
@@ -5945,11 +6013,11 @@
         <v>0.08</v>
       </c>
       <c r="F45" s="63">
-        <v>5122.32</v>
-      </c>
-      <c r="G45" s="63">
+        <v>5750.32</v>
+      </c>
+      <c r="G45" s="269">
         <f>F45</f>
-        <v>5122.32</v>
+        <v>5750.32</v>
       </c>
       <c r="H45" s="75">
         <f t="shared" si="1"/>
@@ -5981,20 +6049,20 @@
         <v>5750.32</v>
       </c>
       <c r="P45" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5923.32</v>
       </c>
       <c r="Q45" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="B46" s="130" t="s">
+      <c r="B46" s="129" t="s">
         <v>103</v>
       </c>
       <c r="C46" s="78" t="s">
@@ -6005,12 +6073,12 @@
         <v>0.08</v>
       </c>
       <c r="F46" s="63">
-        <v>23434.33</v>
+        <v>29185.33</v>
       </c>
       <c r="G46" s="63"/>
       <c r="H46" s="75">
         <f t="shared" si="1"/>
-        <v>23434.33</v>
+        <v>29185.33</v>
       </c>
       <c r="I46" s="75"/>
       <c r="J46" s="82">
@@ -6018,7 +6086,7 @@
         <v>4240</v>
       </c>
       <c r="K46" s="82">
-        <f t="shared" ref="K46:K59" si="17">F$2*E46/100</f>
+        <f t="shared" ref="K46:K59" si="18">F$2*E46/100</f>
         <v>0</v>
       </c>
       <c r="L46" s="82">
@@ -6032,23 +6100,23 @@
       <c r="N46" s="82"/>
       <c r="O46" s="76">
         <f t="shared" si="8"/>
-        <v>29185.33</v>
+        <v>34936.33</v>
       </c>
       <c r="P46" s="91">
-        <f t="shared" si="13"/>
-        <v>30061.33</v>
+        <f t="shared" si="14"/>
+        <v>35984.33</v>
       </c>
       <c r="Q46" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="B47" s="130" t="s">
+      <c r="B47" s="129" t="s">
         <v>104</v>
       </c>
       <c r="C47" s="78" t="s">
@@ -6059,11 +6127,11 @@
         <v>0.08</v>
       </c>
       <c r="F47" s="63">
-        <v>5122.34</v>
-      </c>
-      <c r="G47" s="63">
+        <v>5750.34</v>
+      </c>
+      <c r="G47" s="269">
         <f>F47</f>
-        <v>5122.34</v>
+        <v>5750.34</v>
       </c>
       <c r="H47" s="75">
         <f t="shared" si="1"/>
@@ -6078,7 +6146,7 @@
         <v>4240</v>
       </c>
       <c r="K47" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L47" s="82">
@@ -6095,47 +6163,50 @@
         <v>5750.34</v>
       </c>
       <c r="P47" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5923.34</v>
       </c>
       <c r="Q47" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="121">
-        <f t="shared" si="14"/>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="120">
+        <f t="shared" si="15"/>
         <v>35</v>
       </c>
-      <c r="B48" s="130" t="s">
+      <c r="B48" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="122" t="s">
+      <c r="C48" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="123"/>
-      <c r="E48" s="124">
+      <c r="D48" s="122"/>
+      <c r="E48" s="123">
         <v>0.09</v>
       </c>
       <c r="F48" s="63">
-        <v>5762.35</v>
-      </c>
-      <c r="G48" s="63"/>
-      <c r="H48" s="125">
+        <v>12404.35</v>
+      </c>
+      <c r="G48" s="269">
+        <f>12776.35</f>
+        <v>12776.35</v>
+      </c>
+      <c r="H48" s="124">
         <f t="shared" si="1"/>
-        <v>5762.35</v>
-      </c>
-      <c r="I48" s="125">
+        <v>-372</v>
+      </c>
+      <c r="I48" s="124">
         <f t="shared" si="4"/>
-        <v>172.87049999999999</v>
+        <v>0</v>
       </c>
       <c r="J48" s="82">
         <f t="shared" si="5"/>
         <v>4770</v>
       </c>
-      <c r="K48" s="126">
-        <f t="shared" si="17"/>
+      <c r="K48" s="125">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L48" s="82">
@@ -6146,26 +6217,26 @@
         <f t="shared" si="7"/>
         <v>1534.679478</v>
       </c>
-      <c r="N48" s="126"/>
+      <c r="N48" s="125"/>
       <c r="O48" s="76">
         <f t="shared" si="8"/>
-        <v>12404.35</v>
+        <v>6097.35</v>
       </c>
       <c r="P48" s="91">
-        <f t="shared" si="13"/>
-        <v>12776.35</v>
+        <f t="shared" si="14"/>
+        <v>6280.35</v>
       </c>
       <c r="Q48" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
-      <c r="B49" s="130" t="s">
+      <c r="B49" s="129" t="s">
         <v>106</v>
       </c>
       <c r="C49" s="78" t="s">
@@ -6176,11 +6247,11 @@
         <v>0.79</v>
       </c>
       <c r="F49" s="63">
-        <v>50581.36</v>
-      </c>
-      <c r="G49" s="63">
+        <v>56785.36</v>
+      </c>
+      <c r="G49" s="269">
         <f>F49</f>
-        <v>50581.36</v>
+        <v>56785.36</v>
       </c>
       <c r="H49" s="75">
         <f t="shared" si="1"/>
@@ -6195,7 +6266,7 @@
         <v>41870</v>
       </c>
       <c r="K49" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L49" s="82">
@@ -6212,20 +6283,20 @@
         <v>56785.36</v>
       </c>
       <c r="P49" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>58489.36</v>
       </c>
       <c r="Q49" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>37</v>
       </c>
-      <c r="B50" s="130" t="s">
+      <c r="B50" s="129" t="s">
         <v>107</v>
       </c>
       <c r="C50" s="78" t="s">
@@ -6236,23 +6307,23 @@
         <v>1</v>
       </c>
       <c r="F50" s="63">
-        <v>304541.37</v>
+        <v>385558.37</v>
       </c>
       <c r="G50" s="63"/>
       <c r="H50" s="75">
         <f t="shared" si="1"/>
-        <v>304541.37</v>
+        <v>385558.37</v>
       </c>
       <c r="I50" s="75">
         <f t="shared" si="4"/>
-        <v>9136.2410999999993</v>
+        <v>11566.751099999999</v>
       </c>
       <c r="J50" s="82">
         <f t="shared" si="5"/>
         <v>53000</v>
       </c>
       <c r="K50" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L50" s="82">
@@ -6266,23 +6337,23 @@
       <c r="N50" s="82"/>
       <c r="O50" s="76">
         <f t="shared" si="8"/>
-        <v>385558.37</v>
+        <v>469005.37</v>
       </c>
       <c r="P50" s="91">
-        <f t="shared" si="13"/>
-        <v>397125.37</v>
+        <f t="shared" si="14"/>
+        <v>483075.37</v>
       </c>
       <c r="Q50" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>38</v>
       </c>
-      <c r="B51" s="130" t="s">
+      <c r="B51" s="129" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -6293,11 +6364,11 @@
         <v>0.97</v>
       </c>
       <c r="F51" s="63">
-        <v>62106.38</v>
-      </c>
-      <c r="G51" s="63">
+        <v>69724.38</v>
+      </c>
+      <c r="G51" s="269">
         <f>F51</f>
-        <v>62106.38</v>
+        <v>69724.38</v>
       </c>
       <c r="H51" s="75">
         <f t="shared" si="1"/>
@@ -6312,7 +6383,7 @@
         <v>51410</v>
       </c>
       <c r="K51" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L51" s="82">
@@ -6329,20 +6400,20 @@
         <v>69724.38</v>
       </c>
       <c r="P51" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>71816.38</v>
       </c>
       <c r="Q51" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>39</v>
       </c>
-      <c r="B52" s="130" t="s">
+      <c r="B52" s="129" t="s">
         <v>109</v>
       </c>
       <c r="C52" s="78" t="s">
@@ -6353,25 +6424,25 @@
         <v>0.77</v>
       </c>
       <c r="F52" s="63">
-        <v>109279.39</v>
-      </c>
-      <c r="G52" s="63">
-        <v>8160</v>
+        <v>159501.39000000001</v>
+      </c>
+      <c r="G52" s="269">
+        <v>160000</v>
       </c>
       <c r="H52" s="75">
         <f t="shared" si="1"/>
-        <v>101119.39</v>
+        <v>-498.60999999998603</v>
       </c>
       <c r="I52" s="75">
         <f t="shared" si="4"/>
-        <v>3033.5816999999997</v>
+        <v>0</v>
       </c>
       <c r="J52" s="82">
         <f t="shared" si="5"/>
         <v>40810</v>
       </c>
       <c r="K52" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L52" s="82">
@@ -6385,88 +6456,88 @@
       <c r="N52" s="82"/>
       <c r="O52" s="76">
         <f t="shared" si="8"/>
-        <v>159501.39000000001</v>
+        <v>54849.39</v>
       </c>
       <c r="P52" s="91">
-        <f t="shared" si="13"/>
-        <v>164286.39000000001</v>
+        <f t="shared" si="14"/>
+        <v>56494.39</v>
       </c>
       <c r="Q52" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="83">
-        <f t="shared" si="14"/>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="140">
+        <f t="shared" si="15"/>
         <v>40</v>
       </c>
-      <c r="B53" s="130" t="s">
+      <c r="B53" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="78" t="s">
+      <c r="C53" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="77" t="s">
+      <c r="D53" s="143" t="s">
         <v>169</v>
       </c>
-      <c r="E53" s="74">
+      <c r="E53" s="144">
         <v>0.77</v>
       </c>
-      <c r="F53" s="63">
-        <v>49301.4</v>
-      </c>
-      <c r="G53" s="63">
+      <c r="F53" s="145">
+        <v>55348.4</v>
+      </c>
+      <c r="G53" s="270">
         <f>F53</f>
-        <v>49301.4</v>
-      </c>
-      <c r="H53" s="75">
+        <v>55348.4</v>
+      </c>
+      <c r="H53" s="146">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="75">
+      <c r="I53" s="146">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J53" s="82">
+      <c r="J53" s="147">
         <f t="shared" si="5"/>
         <v>40810</v>
       </c>
-      <c r="K53" s="82">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="82">
+      <c r="K53" s="147">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="147">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="82">
+      <c r="M53" s="147">
         <f t="shared" si="7"/>
         <v>13130.035533999999</v>
       </c>
-      <c r="N53" s="82"/>
-      <c r="O53" s="76">
+      <c r="N53" s="147"/>
+      <c r="O53" s="148">
         <f t="shared" si="8"/>
         <v>55348.4</v>
       </c>
-      <c r="P53" s="91">
-        <f t="shared" si="13"/>
+      <c r="P53" s="149">
+        <f t="shared" si="14"/>
         <v>57008.4</v>
       </c>
       <c r="Q53" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>41</v>
       </c>
-      <c r="B54" s="130" t="s">
+      <c r="B54" s="129" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="78" t="s">
@@ -6479,25 +6550,25 @@
         <v>0.81</v>
       </c>
       <c r="F54" s="63">
-        <v>51862.41</v>
+        <v>111641.41</v>
       </c>
       <c r="G54" s="63">
         <v>0</v>
       </c>
       <c r="H54" s="75">
         <f t="shared" si="1"/>
-        <v>51862.41</v>
+        <v>111641.41</v>
       </c>
       <c r="I54" s="75">
         <f t="shared" si="4"/>
-        <v>1555.8723</v>
+        <v>3349.2422999999999</v>
       </c>
       <c r="J54" s="82">
         <f t="shared" si="5"/>
         <v>42930</v>
       </c>
       <c r="K54" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L54" s="82">
@@ -6511,23 +6582,23 @@
       <c r="N54" s="82"/>
       <c r="O54" s="76">
         <f t="shared" si="8"/>
-        <v>111641.41</v>
+        <v>173214.41</v>
       </c>
       <c r="P54" s="91">
-        <f t="shared" si="13"/>
-        <v>114990.41</v>
+        <f t="shared" si="14"/>
+        <v>178410.41</v>
       </c>
       <c r="Q54" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
-      <c r="B55" s="130" t="s">
+      <c r="B55" s="129" t="s">
         <v>112</v>
       </c>
       <c r="C55" s="78" t="s">
@@ -6540,11 +6611,11 @@
         <v>0.77</v>
       </c>
       <c r="F55" s="63">
-        <v>49301.42</v>
-      </c>
-      <c r="G55" s="63">
+        <v>55348.42</v>
+      </c>
+      <c r="G55" s="269">
         <f>F55</f>
-        <v>49301.42</v>
+        <v>55348.42</v>
       </c>
       <c r="H55" s="75">
         <f t="shared" si="1"/>
@@ -6556,7 +6627,7 @@
         <v>40810</v>
       </c>
       <c r="K55" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L55" s="82">
@@ -6573,23 +6644,23 @@
         <v>55348.42</v>
       </c>
       <c r="P55" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57008.42</v>
       </c>
       <c r="Q55" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43</v>
       </c>
-      <c r="B56" s="130" t="s">
+      <c r="B56" s="129" t="s">
         <v>113</v>
       </c>
       <c r="C56" s="78" t="s">
@@ -6600,23 +6671,23 @@
         <v>0.77</v>
       </c>
       <c r="F56" s="63">
-        <v>232481.43</v>
+        <v>294804.43</v>
       </c>
       <c r="G56" s="63"/>
       <c r="H56" s="75">
         <f t="shared" si="1"/>
-        <v>232481.43</v>
+        <v>294804.43</v>
       </c>
       <c r="I56" s="75">
         <f t="shared" si="4"/>
-        <v>6974.4428999999991</v>
+        <v>8844.1328999999987</v>
       </c>
       <c r="J56" s="82">
         <f t="shared" si="5"/>
         <v>40810</v>
       </c>
       <c r="K56" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L56" s="82">
@@ -6630,23 +6701,23 @@
       <c r="N56" s="82"/>
       <c r="O56" s="76">
         <f t="shared" si="8"/>
-        <v>294804.43</v>
+        <v>358996.43</v>
       </c>
       <c r="P56" s="91">
-        <f t="shared" si="13"/>
-        <v>303648.43</v>
+        <f t="shared" si="14"/>
+        <v>369766.43</v>
       </c>
       <c r="Q56" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44</v>
       </c>
-      <c r="B57" s="130" t="s">
+      <c r="B57" s="129" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="78" t="s">
@@ -6657,23 +6728,23 @@
         <v>0.77</v>
       </c>
       <c r="F57" s="63">
-        <v>165242.44</v>
+        <v>225547.44</v>
       </c>
       <c r="G57" s="63"/>
       <c r="H57" s="75">
         <f t="shared" si="1"/>
-        <v>165242.44</v>
+        <v>225547.44</v>
       </c>
       <c r="I57" s="75">
         <f t="shared" si="4"/>
-        <v>4957.2731999999996</v>
+        <v>6766.4232000000002</v>
       </c>
       <c r="J57" s="82">
         <f t="shared" si="5"/>
         <v>40810</v>
       </c>
       <c r="K57" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L57" s="82">
@@ -6687,23 +6758,23 @@
       <c r="N57" s="82"/>
       <c r="O57" s="76">
         <f t="shared" si="8"/>
-        <v>225547.44</v>
+        <v>287662.44</v>
       </c>
       <c r="P57" s="91">
-        <f t="shared" si="13"/>
-        <v>232313.44</v>
+        <f t="shared" si="14"/>
+        <v>296292.44</v>
       </c>
       <c r="Q57" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45</v>
       </c>
-      <c r="B58" s="130" t="s">
+      <c r="B58" s="129" t="s">
         <v>115</v>
       </c>
       <c r="C58" s="78" t="s">
@@ -6716,11 +6787,11 @@
         <v>0.77</v>
       </c>
       <c r="F58" s="63">
-        <v>49301.45</v>
-      </c>
-      <c r="G58" s="63">
-        <f t="shared" ref="G58" si="18">F58</f>
-        <v>49301.45</v>
+        <v>55348.45</v>
+      </c>
+      <c r="G58" s="269">
+        <f t="shared" ref="G58" si="19">F58</f>
+        <v>55348.45</v>
       </c>
       <c r="H58" s="75">
         <f t="shared" si="1"/>
@@ -6735,7 +6806,7 @@
         <v>40810</v>
       </c>
       <c r="K58" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L58" s="82">
@@ -6752,20 +6823,20 @@
         <v>55348.45</v>
       </c>
       <c r="P58" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57008.45</v>
       </c>
       <c r="Q58" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>46</v>
       </c>
-      <c r="B59" s="130" t="s">
+      <c r="B59" s="129" t="s">
         <v>116</v>
       </c>
       <c r="C59" s="78" t="s">
@@ -6776,26 +6847,26 @@
         <v>0.86</v>
       </c>
       <c r="F59" s="63">
-        <v>128840.46</v>
-      </c>
-      <c r="G59" s="63">
-        <f>137000-8160</f>
-        <v>128840</v>
+        <v>61817.46</v>
+      </c>
+      <c r="G59" s="269">
+        <f>132705.46-70888</f>
+        <v>61817.459999999992</v>
       </c>
       <c r="H59" s="75">
         <f t="shared" si="1"/>
-        <v>0.46000000000640284</v>
+        <v>0</v>
       </c>
       <c r="I59" s="75">
         <f t="shared" si="4"/>
-        <v>1.3800000000192084E-2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="82">
         <f t="shared" si="5"/>
         <v>45580</v>
       </c>
       <c r="K59" s="82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L59" s="82">
@@ -6812,20 +6883,20 @@
         <v>61817.46</v>
       </c>
       <c r="P59" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>63672.46</v>
       </c>
       <c r="Q59" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="83"/>
-      <c r="B60" s="130"/>
+      <c r="B60" s="129"/>
       <c r="C60" s="72"/>
       <c r="D60" s="77"/>
       <c r="E60" s="74"/>
@@ -6842,156 +6913,160 @@
       <c r="P60" s="91"/>
       <c r="Q60" s="40"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="84"/>
-      <c r="B61" s="131"/>
+      <c r="B61" s="130"/>
       <c r="C61" s="85"/>
       <c r="D61" s="85"/>
       <c r="E61" s="86">
-        <f t="shared" ref="E61:M61" si="19">SUM(E14:E60)</f>
+        <f t="shared" ref="E61:M61" si="20">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="F61" s="87">
-        <f t="shared" si="19"/>
-        <v>9178994.8100000005</v>
+        <f t="shared" si="20"/>
+        <v>11042768.810000001</v>
       </c>
       <c r="G61" s="88">
         <f>SUM(G14:G60)</f>
-        <v>5479535.0300000003</v>
+        <v>6230781.8999999994</v>
       </c>
       <c r="H61" s="88">
-        <f t="shared" si="19"/>
-        <v>3699459.7800000003</v>
+        <f t="shared" si="20"/>
+        <v>4811986.91</v>
       </c>
       <c r="I61" s="88">
-        <f t="shared" si="19"/>
-        <v>111777.23309999998</v>
+        <f t="shared" si="20"/>
+        <v>144390.61859999999</v>
       </c>
       <c r="J61" s="89">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5300000</v>
       </c>
       <c r="K61" s="89">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L61" s="89">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>182823.00999999992</v>
       </c>
       <c r="M61" s="89">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1705199.4200000009</v>
       </c>
       <c r="N61" s="90"/>
       <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>11042768.810000001</v>
+        <v>12187909.810000001</v>
       </c>
       <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>11374054.810000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12553549.810000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="64"/>
       <c r="D62" s="64"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="233" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="233"/>
-      <c r="E64" s="233"/>
-      <c r="F64" s="233"/>
-      <c r="G64" s="233"/>
-      <c r="H64" s="233"/>
-      <c r="I64" s="233"/>
-      <c r="J64" s="233"/>
-      <c r="K64" s="233"/>
-      <c r="L64" s="233"/>
-      <c r="M64" s="233"/>
-      <c r="N64" s="233"/>
-      <c r="O64" s="233"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="233"/>
-      <c r="D65" s="233"/>
-      <c r="E65" s="233"/>
-      <c r="F65" s="233"/>
-      <c r="G65" s="233"/>
-      <c r="H65" s="233"/>
-      <c r="I65" s="233"/>
-      <c r="J65" s="233"/>
-      <c r="K65" s="233"/>
-      <c r="L65" s="233"/>
-      <c r="M65" s="233"/>
-      <c r="N65" s="233"/>
-      <c r="O65" s="233"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="233"/>
-      <c r="D66" s="233"/>
-      <c r="E66" s="233"/>
-      <c r="F66" s="233"/>
-      <c r="G66" s="233"/>
-      <c r="H66" s="233"/>
-      <c r="I66" s="233"/>
-      <c r="J66" s="233"/>
-      <c r="K66" s="233"/>
-      <c r="L66" s="233"/>
-      <c r="M66" s="233"/>
-      <c r="N66" s="233"/>
-      <c r="O66" s="233"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="233"/>
-      <c r="D67" s="233"/>
-      <c r="E67" s="233"/>
-      <c r="F67" s="233"/>
-      <c r="G67" s="233"/>
-      <c r="H67" s="233"/>
-      <c r="I67" s="233"/>
-      <c r="J67" s="233"/>
-      <c r="K67" s="233"/>
-      <c r="L67" s="233"/>
-      <c r="M67" s="233"/>
-      <c r="N67" s="233"/>
-      <c r="O67" s="233"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="233"/>
-      <c r="D68" s="233"/>
-      <c r="E68" s="233"/>
-      <c r="F68" s="233"/>
-      <c r="G68" s="233"/>
-      <c r="H68" s="233"/>
-      <c r="I68" s="233"/>
-      <c r="J68" s="233"/>
-      <c r="K68" s="233"/>
-      <c r="L68" s="233"/>
-      <c r="M68" s="233"/>
-      <c r="N68" s="233"/>
-      <c r="O68" s="233"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="233"/>
-      <c r="D69" s="233"/>
-      <c r="E69" s="233"/>
-      <c r="F69" s="233"/>
-      <c r="G69" s="233"/>
-      <c r="H69" s="233"/>
-      <c r="I69" s="233"/>
-      <c r="J69" s="233"/>
-      <c r="K69" s="233"/>
-      <c r="L69" s="233"/>
-      <c r="M69" s="233"/>
-      <c r="N69" s="233"/>
-      <c r="O69" s="233"/>
+      <c r="D64" s="229"/>
+      <c r="E64" s="229"/>
+      <c r="F64" s="229"/>
+      <c r="G64" s="229"/>
+      <c r="H64" s="229"/>
+      <c r="I64" s="229"/>
+      <c r="J64" s="229"/>
+      <c r="K64" s="229"/>
+      <c r="L64" s="229"/>
+      <c r="M64" s="229"/>
+      <c r="N64" s="229"/>
+      <c r="O64" s="229"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="229"/>
+      <c r="D65" s="229"/>
+      <c r="E65" s="229"/>
+      <c r="F65" s="229"/>
+      <c r="G65" s="229"/>
+      <c r="H65" s="229"/>
+      <c r="I65" s="229"/>
+      <c r="J65" s="229"/>
+      <c r="K65" s="229"/>
+      <c r="L65" s="229"/>
+      <c r="M65" s="229"/>
+      <c r="N65" s="229"/>
+      <c r="O65" s="229"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="229"/>
+      <c r="D66" s="229"/>
+      <c r="E66" s="229"/>
+      <c r="F66" s="229"/>
+      <c r="G66" s="229"/>
+      <c r="H66" s="229"/>
+      <c r="I66" s="229"/>
+      <c r="J66" s="229"/>
+      <c r="K66" s="229"/>
+      <c r="L66" s="229"/>
+      <c r="M66" s="229"/>
+      <c r="N66" s="229"/>
+      <c r="O66" s="229"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="229"/>
+      <c r="D67" s="229"/>
+      <c r="E67" s="229"/>
+      <c r="F67" s="229"/>
+      <c r="G67" s="229"/>
+      <c r="H67" s="229"/>
+      <c r="I67" s="229"/>
+      <c r="J67" s="229"/>
+      <c r="K67" s="229"/>
+      <c r="L67" s="229"/>
+      <c r="M67" s="229"/>
+      <c r="N67" s="229"/>
+      <c r="O67" s="229"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="229"/>
+      <c r="D68" s="229"/>
+      <c r="E68" s="229"/>
+      <c r="F68" s="229"/>
+      <c r="G68" s="229"/>
+      <c r="H68" s="229"/>
+      <c r="I68" s="229"/>
+      <c r="J68" s="229"/>
+      <c r="K68" s="229"/>
+      <c r="L68" s="229"/>
+      <c r="M68" s="229"/>
+      <c r="N68" s="229"/>
+      <c r="O68" s="229"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="229"/>
+      <c r="D69" s="229"/>
+      <c r="E69" s="229"/>
+      <c r="F69" s="229"/>
+      <c r="G69" s="229"/>
+      <c r="H69" s="229"/>
+      <c r="I69" s="229"/>
+      <c r="J69" s="229"/>
+      <c r="K69" s="229"/>
+      <c r="L69" s="229"/>
+      <c r="M69" s="229"/>
+      <c r="N69" s="229"/>
+      <c r="O69" s="229"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -7008,10 +7083,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7022,51 +7093,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="20"/>
     </row>
-    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="116" t="s">
+    <row r="4" spans="3:12" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="117">
+      <c r="D4" s="116">
         <v>1</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="118" t="s">
+    <row r="5" spans="3:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="119"/>
+      <c r="D5" s="118"/>
       <c r="E5" t="s">
         <v>53</v>
       </c>
       <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="115"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="20"/>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="118" t="s">
+      <c r="J5" s="114"/>
+      <c r="K5" s="272"/>
+      <c r="L5" s="273"/>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>56</v>
       </c>
       <c r="E6" t="s">
@@ -7076,50 +7147,50 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
-      </c>
-      <c r="J6" s="115"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="20"/>
-    </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="J6" s="114"/>
+      <c r="K6" s="272"/>
+      <c r="L6" s="273"/>
+    </row>
+    <row r="7" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="115"/>
-      <c r="K7" s="187"/>
-      <c r="L7" s="20"/>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="270" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="271"/>
-      <c r="E8" s="271"/>
-      <c r="F8" s="271"/>
-      <c r="G8" s="271"/>
-      <c r="H8" s="271"/>
-      <c r="I8" s="271"/>
-      <c r="J8" s="272"/>
-      <c r="K8" s="187"/>
-      <c r="L8" s="20"/>
-    </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="273"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="274"/>
-      <c r="I9" s="274"/>
-      <c r="J9" s="275"/>
-      <c r="K9" s="187"/>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="204" t="s">
+      <c r="J7" s="114"/>
+      <c r="K7" s="272"/>
+      <c r="L7" s="273"/>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="255" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="256"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="256"/>
+      <c r="H8" s="256"/>
+      <c r="I8" s="256"/>
+      <c r="J8" s="257"/>
+      <c r="K8" s="272"/>
+      <c r="L8" s="273"/>
+    </row>
+    <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="259"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="185"/>
+    </row>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="205"/>
+      <c r="D12" s="197"/>
       <c r="E12" t="s">
         <v>53</v>
       </c>
@@ -7127,15 +7198,15 @@
         <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>206</v>
-      </c>
-      <c r="J12" s="115"/>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="204" t="s">
+        <v>194</v>
+      </c>
+      <c r="J12" s="114"/>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="196" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="205" t="s">
+      <c r="D13" s="197" t="s">
         <v>56</v>
       </c>
       <c r="E13" t="s">
@@ -7147,54 +7218,72 @@
       <c r="H13" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="115"/>
-    </row>
-    <row r="14" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="114"/>
+      <c r="K13" s="273"/>
+      <c r="L13" s="273"/>
+    </row>
+    <row r="14" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="115"/>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="270" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="271"/>
-      <c r="E15" s="271"/>
-      <c r="F15" s="271"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="271"/>
-      <c r="I15" s="271"/>
-      <c r="J15" s="272"/>
-    </row>
-    <row r="16" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="273"/>
-      <c r="D16" s="274"/>
-      <c r="E16" s="274"/>
-      <c r="F16" s="274"/>
-      <c r="G16" s="274"/>
-      <c r="H16" s="274"/>
-      <c r="I16" s="274"/>
-      <c r="J16" s="275"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="210" t="s">
+      <c r="J14" s="114"/>
+      <c r="K14" s="273"/>
+      <c r="L14" s="273"/>
+    </row>
+    <row r="15" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C15" s="255" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15" s="256"/>
+      <c r="E15" s="256"/>
+      <c r="F15" s="256"/>
+      <c r="G15" s="256"/>
+      <c r="H15" s="256"/>
+      <c r="I15" s="256"/>
+      <c r="J15" s="257"/>
+      <c r="K15" s="273"/>
+      <c r="L15" s="273"/>
+    </row>
+    <row r="16" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="258"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="259"/>
+      <c r="F16" s="259"/>
+      <c r="G16" s="259"/>
+      <c r="H16" s="259"/>
+      <c r="I16" s="259"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="273"/>
+      <c r="L16" s="273"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="K17" s="273"/>
+      <c r="L17" s="273"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="K18" s="273"/>
+      <c r="L18" s="273"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C19" s="198" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="211"/>
+      <c r="D19" s="199"/>
       <c r="E19" t="s">
         <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="J19" s="115"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="210" t="s">
+      <c r="J19" s="114"/>
+      <c r="K19" s="273"/>
+      <c r="L19" s="273"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C20" s="198" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="211" t="s">
+      <c r="D20" s="199" t="s">
         <v>56</v>
       </c>
       <c r="E20" t="s">
@@ -7204,37 +7293,45 @@
         <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>208</v>
-      </c>
-      <c r="J20" s="115"/>
-    </row>
-    <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="J20" s="114"/>
+      <c r="K20" s="273"/>
+      <c r="L20" s="273"/>
+    </row>
+    <row r="21" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="115"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="270" t="s">
-        <v>209</v>
-      </c>
-      <c r="D22" s="271"/>
-      <c r="E22" s="271"/>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="272"/>
-    </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="273"/>
-      <c r="D23" s="274"/>
-      <c r="E23" s="274"/>
-      <c r="F23" s="274"/>
-      <c r="G23" s="274"/>
-      <c r="H23" s="274"/>
-      <c r="I23" s="274"/>
-      <c r="J23" s="275"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="273"/>
+      <c r="L21" s="273"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C22" s="255" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="256"/>
+      <c r="E22" s="256"/>
+      <c r="F22" s="256"/>
+      <c r="G22" s="256"/>
+      <c r="H22" s="256"/>
+      <c r="I22" s="256"/>
+      <c r="J22" s="257"/>
+      <c r="K22" s="273"/>
+      <c r="L22" s="273"/>
+    </row>
+    <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="258"/>
+      <c r="D23" s="259"/>
+      <c r="E23" s="259"/>
+      <c r="F23" s="259"/>
+      <c r="G23" s="259"/>
+      <c r="H23" s="259"/>
+      <c r="I23" s="259"/>
+      <c r="J23" s="260"/>
+      <c r="K23" s="273"/>
+      <c r="L23" s="273"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C1FB02-ABD3-4FE2-A116-A7C1140F0C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D653A12-3EA2-492E-B1A7-84C66F4C1A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="227">
   <si>
     <t>TOTAL</t>
   </si>
@@ -569,9 +569,6 @@
     <t>Abono de 2 meses</t>
   </si>
   <si>
-    <t>Haberes + SAC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gastos bancarios </t>
   </si>
   <si>
@@ -591,9 +588,6 @@
   </si>
   <si>
     <t>FCI Super ahorro plus</t>
-  </si>
-  <si>
-    <t>Egreso pago de metrogas</t>
   </si>
   <si>
     <t>Gasto particular / SUM</t>
@@ -618,9 +612,6 @@
     <t>Inicio del mes</t>
   </si>
   <si>
-    <t>La caja nos da una diferencia de $60.000 pesos aprox que Cabrera le debe al consorcio de ohgiggins</t>
-  </si>
-  <si>
     <t>Silvina albaneda volvio a no respetar centavos, transfirio: $ 249002,48 - Sumo: $243079,14 dpto
 $5923,34 cochera</t>
   </si>
@@ -724,7 +715,16 @@
     <t>Rescate 12/08</t>
   </si>
   <si>
-    <t>Deposito ya identificad 29/6</t>
+    <t xml:space="preserve">Haberes </t>
+  </si>
+  <si>
+    <t>Transf 31/08</t>
+  </si>
+  <si>
+    <t>Cambio de semaforo - Materiales y mano de obra</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado 29/6</t>
   </si>
 </sst>
 </file>
@@ -741,7 +741,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,21 +898,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="0.59999389629810485"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1015,12 +1009,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="40">
     <border>
@@ -1524,7 +1512,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1845,55 +1833,163 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1913,12 +2009,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1928,84 +2018,6 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2024,29 +2036,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="18" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="18" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="18" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="21" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="18" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="18" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2469,12 +2460,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="210" t="s">
+      <c r="B1" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="212"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2487,12 +2478,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="213"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="216"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2510,7 +2501,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2520,7 +2511,7 @@
     </row>
     <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2530,54 +2521,54 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="214" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="214"/>
+      <c r="B8" s="217" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="217"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="214"/>
-      <c r="C9" s="214"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="215" t="s">
+      <c r="A13" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="215"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="215"/>
-      <c r="E13" s="215"/>
+      <c r="B13" s="218"/>
+      <c r="C13" s="218"/>
+      <c r="D13" s="218"/>
+      <c r="E13" s="218"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="215"/>
-      <c r="B14" s="215"/>
-      <c r="C14" s="215"/>
-      <c r="D14" s="215"/>
-      <c r="E14" s="215"/>
+      <c r="A14" s="218"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="215"/>
-      <c r="B15" s="215"/>
-      <c r="C15" s="215"/>
-      <c r="D15" s="215"/>
-      <c r="E15" s="215"/>
+      <c r="A15" s="218"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="215"/>
-      <c r="B16" s="215"/>
-      <c r="C16" s="215"/>
-      <c r="D16" s="215"/>
-      <c r="E16" s="215"/>
+      <c r="A16" s="218"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2603,24 +2594,24 @@
       <c r="E21" s="96"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="216" t="s">
-        <v>175</v>
-      </c>
-      <c r="B22" s="217"/>
+      <c r="A22" s="219" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="220"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="266">
+      <c r="D22" s="209">
         <v>1460357.72</v>
       </c>
       <c r="E22" s="97"/>
       <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="206" t="s">
+      <c r="A23" s="213" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="207"/>
+      <c r="B23" s="214"/>
       <c r="C23" s="150"/>
-      <c r="D23" s="266">
+      <c r="D23" s="209">
         <v>-317627.71999999997</v>
       </c>
       <c r="E23" s="21"/>
@@ -2628,10 +2619,10 @@
       <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="206" t="s">
+      <c r="A24" s="213" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="207"/>
+      <c r="B24" s="214"/>
       <c r="C24" s="150"/>
       <c r="D24" s="194"/>
       <c r="E24" s="21"/>
@@ -2714,11 +2705,11 @@
       </c>
       <c r="B32" s="153"/>
       <c r="C32" s="153"/>
-      <c r="D32" s="263">
+      <c r="D32" s="28">
         <v>673382.02</v>
       </c>
       <c r="E32" s="100" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
@@ -2728,14 +2719,14 @@
         <v>147</v>
       </c>
       <c r="B33" s="150" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C33" s="153"/>
-      <c r="D33" s="263">
+      <c r="D33" s="28">
         <v>182823.01</v>
       </c>
       <c r="E33" s="100" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
@@ -2746,11 +2737,11 @@
       </c>
       <c r="B34" s="153"/>
       <c r="C34" s="153"/>
-      <c r="D34" s="263">
+      <c r="D34" s="28">
         <v>61610.09</v>
       </c>
       <c r="E34" s="100" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
@@ -2761,7 +2752,7 @@
       </c>
       <c r="B35" s="153"/>
       <c r="C35" s="153"/>
-      <c r="D35" s="263">
+      <c r="D35" s="28">
         <v>6845.57</v>
       </c>
       <c r="E35" s="100" t="str">
@@ -2777,7 +2768,7 @@
       </c>
       <c r="B36" s="153"/>
       <c r="C36" s="153"/>
-      <c r="D36" s="263">
+      <c r="D36" s="28">
         <v>110477.88</v>
       </c>
       <c r="E36" s="100" t="str">
@@ -2810,12 +2801,12 @@
       <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="201" t="s">
+      <c r="A39" s="221" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="202"/>
+      <c r="B39" s="222"/>
       <c r="C39" s="154"/>
-      <c r="D39" s="261">
+      <c r="D39" s="195">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2824,14 +2815,13 @@
       <c r="F39" s="38"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="201" t="s">
+      <c r="A40" s="221" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="202"/>
+      <c r="B40" s="222"/>
       <c r="C40" s="154"/>
       <c r="D40" s="195">
-        <f>1285.32+12020</f>
-        <v>13305.32</v>
+        <v>0</v>
       </c>
       <c r="E40" s="21" t="str">
         <f>E39</f>
@@ -2848,7 +2838,7 @@
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
-        <v>218339.03</v>
+        <v>205033.71</v>
       </c>
       <c r="F41" s="38"/>
     </row>
@@ -2868,11 +2858,11 @@
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="262">
+      <c r="D43" s="206">
         <v>1726596.39</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F43" s="38"/>
     </row>
@@ -2882,11 +2872,11 @@
       </c>
       <c r="B44" s="155"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="262">
+      <c r="D44" s="206">
         <v>6637.89</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F44" s="38"/>
     </row>
@@ -2895,28 +2885,28 @@
         <v>65</v>
       </c>
       <c r="B45" s="155" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C45" s="33"/>
-      <c r="D45" s="262">
+      <c r="D45" s="206">
         <v>6637.89</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F45" s="38"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="201" t="s">
+      <c r="A46" s="221" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="202"/>
+      <c r="B46" s="222"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="262">
+      <c r="D46" s="206">
         <v>542877.21</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F46" s="38"/>
     </row>
@@ -2928,11 +2918,11 @@
         <v>174</v>
       </c>
       <c r="C47" s="33"/>
-      <c r="D47" s="262">
+      <c r="D47" s="206">
         <v>40810.79</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F47" s="38"/>
     </row>
@@ -2960,425 +2950,429 @@
       <c r="F49" s="38"/>
     </row>
     <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="206" t="s">
+      <c r="A50" s="213" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="214"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="206">
+        <v>250600</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F50" s="38"/>
+    </row>
+    <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="213" t="s">
         <v>215</v>
       </c>
-      <c r="B50" s="207"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="262">
-        <v>250600</v>
-      </c>
-      <c r="E50" s="27" t="s">
+      <c r="B51" s="214"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="206">
+        <v>298200</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F51" s="38"/>
+    </row>
+    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="221" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" s="222"/>
+      <c r="C52" s="150"/>
+      <c r="D52" s="206">
+        <v>300000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F52" s="132"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="223" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" s="224"/>
+      <c r="C53" s="150"/>
+      <c r="D53" s="206">
+        <v>150000</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" s="132"/>
+    </row>
+    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="223" t="s">
+        <v>206</v>
+      </c>
+      <c r="B54" s="224"/>
+      <c r="C54" s="150"/>
+      <c r="D54" s="206">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="132"/>
+    </row>
+    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="201" t="s">
+        <v>225</v>
+      </c>
+      <c r="B55" s="202"/>
+      <c r="C55" s="150"/>
+      <c r="D55" s="206">
+        <v>240000</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="F55" s="132"/>
+    </row>
+    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="223" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" s="224"/>
+      <c r="C56" s="150"/>
+      <c r="D56" s="206">
+        <v>202973</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" s="132"/>
+    </row>
+    <row r="57" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="221" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="38"/>
-    </row>
-    <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="206" t="s">
-        <v>218</v>
-      </c>
-      <c r="B51" s="207"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="262">
-        <v>298200</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F51" s="38"/>
-    </row>
-    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="201" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="202"/>
-      <c r="C52" s="150"/>
-      <c r="D52" s="262">
-        <v>300000</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="F52" s="132"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="204" t="s">
-        <v>208</v>
-      </c>
-      <c r="B53" s="205"/>
-      <c r="C53" s="150"/>
-      <c r="D53" s="262">
-        <v>150000</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="F53" s="132"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="204" t="s">
-        <v>209</v>
-      </c>
-      <c r="B54" s="205"/>
-      <c r="C54" s="150"/>
-      <c r="D54" s="262">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="F54" s="132"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="204" t="s">
-        <v>204</v>
-      </c>
-      <c r="B55" s="205"/>
-      <c r="C55" s="150"/>
-      <c r="D55" s="262">
-        <v>202973</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="F55" s="132"/>
-    </row>
-    <row r="56" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="201" t="s">
+      <c r="B57" s="222"/>
+      <c r="C57" s="150"/>
+      <c r="D57" s="206">
+        <v>180000</v>
+      </c>
+      <c r="E57" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="B56" s="202"/>
-      <c r="C56" s="150"/>
-      <c r="D56" s="262">
-        <v>180000</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="F56" s="38"/>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="B57" s="207"/>
-      <c r="C57" s="150"/>
-      <c r="D57" s="262">
+      <c r="F57" s="38"/>
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="213" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="214"/>
+      <c r="C58" s="150"/>
+      <c r="D58" s="206">
         <v>265200</v>
       </c>
-      <c r="E57" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F57" s="38"/>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="193" t="s">
-        <v>188</v>
-      </c>
-      <c r="B58" s="158"/>
-      <c r="C58" s="150"/>
-      <c r="D58" s="262">
-        <v>130500</v>
-      </c>
       <c r="E58" s="27" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="200" t="s">
-        <v>188</v>
+    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="193" t="s">
+        <v>186</v>
       </c>
       <c r="B59" s="158"/>
       <c r="C59" s="150"/>
-      <c r="D59" s="262">
+      <c r="D59" s="206">
+        <v>130500</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="F59" s="38"/>
+    </row>
+    <row r="60" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="200" t="s">
+        <v>186</v>
+      </c>
+      <c r="B60" s="158"/>
+      <c r="C60" s="150"/>
+      <c r="D60" s="206">
         <v>118800</v>
       </c>
-      <c r="E59" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="F59" s="132"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="151" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="32">
-        <f>SUM(D50:D59)</f>
-        <v>2246273</v>
-      </c>
-      <c r="F60" s="38"/>
+      <c r="E60" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="F60" s="132"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
-        <v>13</v>
+      <c r="A61" s="151" t="s">
+        <v>0</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="96"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="32">
+        <f>SUM(D50:D60)</f>
+        <v>2486273</v>
+      </c>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="206" t="s">
-        <v>221</v>
-      </c>
-      <c r="B62" s="207"/>
-      <c r="C62" s="150"/>
-      <c r="D62" s="265">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="96"/>
+      <c r="F62" s="38"/>
+    </row>
+    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="213" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="214"/>
+      <c r="C63" s="150"/>
+      <c r="D63" s="207">
         <v>210000</v>
-      </c>
-      <c r="E62" s="97"/>
-      <c r="F62" s="38"/>
-    </row>
-    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="206" t="s">
-        <v>222</v>
-      </c>
-      <c r="B63" s="207"/>
-      <c r="C63" s="150"/>
-      <c r="D63" s="264">
-        <v>0</v>
       </c>
       <c r="E63" s="97"/>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="159" t="s">
-        <v>213</v>
-      </c>
-      <c r="B64" s="158"/>
+    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="213" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="214"/>
       <c r="C64" s="150"/>
-      <c r="D64" s="264">
-        <v>150000</v>
+      <c r="D64" s="208">
+        <v>0</v>
       </c>
       <c r="E64" s="97"/>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="151" t="s">
+    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="159" t="s">
+        <v>210</v>
+      </c>
+      <c r="B65" s="158"/>
+      <c r="C65" s="150"/>
+      <c r="D65" s="208">
+        <v>150000</v>
+      </c>
+      <c r="E65" s="97" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="38"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="151"/>
-      <c r="C65" s="151"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="98">
-        <f>SUM(D62:D64)</f>
+      <c r="B66" s="151"/>
+      <c r="C66" s="151"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="98">
+        <f>SUM(D63:D65)</f>
         <v>360000</v>
       </c>
-      <c r="F65" s="38"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="29" t="s">
+      <c r="F66" s="38"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="160"/>
-      <c r="C66" s="151"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="38"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" s="161"/>
-      <c r="C67" s="161"/>
-      <c r="D67" s="267">
-        <v>69000</v>
-      </c>
-      <c r="E67" s="105"/>
+      <c r="B67" s="160"/>
+      <c r="C67" s="151"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="32"/>
       <c r="F67" s="38"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="33" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="B68" s="161"/>
       <c r="C68" s="161"/>
       <c r="D68" s="162">
-        <v>110424.89</v>
+        <v>69000</v>
       </c>
       <c r="E68" s="105"/>
       <c r="F68" s="38"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="163" t="s">
+      <c r="A69" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B69" s="161"/>
+      <c r="C69" s="161"/>
+      <c r="D69" s="162">
+        <f>114820.43-36</f>
+        <v>114784.43</v>
+      </c>
+      <c r="E69" s="105"/>
+      <c r="F69" s="38"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B69" s="163"/>
-      <c r="C69" s="163"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="32">
-        <f>SUM(D67:D68)</f>
-        <v>179424.89</v>
-      </c>
-      <c r="F69" s="38"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="33"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="33"/>
-      <c r="E70" s="34"/>
+      <c r="B70" s="163"/>
+      <c r="C70" s="163"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="32">
+        <f>SUM(D68:D69)</f>
+        <v>183784.43</v>
+      </c>
       <c r="F70" s="38"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="164" t="s">
+      <c r="A71" s="33"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="38"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="B71" s="164"/>
-      <c r="C71" s="164"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="38"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="165"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="132"/>
+      <c r="B72" s="164"/>
+      <c r="C72" s="164"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="38"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="166" t="s">
+      <c r="A73" s="165"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="132"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="167"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="42">
-        <f>(SUM(E21:E71))</f>
-        <v>7505465.6599999992</v>
-      </c>
-      <c r="F73" s="168"/>
-      <c r="G73" s="40"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="38"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="167"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="42">
+        <f>(SUM(E21:E72))</f>
+        <v>7736519.879999999</v>
+      </c>
+      <c r="F74" s="168"/>
+      <c r="G74" s="40"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="38"/>
       <c r="B75" s="38"/>
       <c r="C75" s="38"/>
       <c r="D75" s="38"/>
       <c r="E75" s="38"/>
       <c r="F75" s="38"/>
-      <c r="H75" s="44"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="169" t="s">
+    </row>
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="38"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="H76" s="44"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="B76" s="170"/>
-      <c r="C76" s="171"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="38"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="209"/>
-      <c r="B77" s="203"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="172"/>
-      <c r="E77" s="119"/>
+      <c r="B77" s="170"/>
+      <c r="C77" s="171"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="46"/>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="38"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="226"/>
+      <c r="B78" s="227"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="172"/>
+      <c r="E78" s="119"/>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="173"/>
-      <c r="B79" s="174"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="47"/>
+    <row r="79" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="38"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="33"/>
       <c r="F79" s="38"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="175" t="s">
+      <c r="A80" s="173"/>
+      <c r="B80" s="174"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="47"/>
+      <c r="F80" s="38"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="B80" s="176"/>
-      <c r="C80" s="176"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="106">
-        <f>SUM(D77:D79)</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="38"/>
-    </row>
-    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="38"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
+      <c r="B81" s="176"/>
+      <c r="C81" s="176"/>
+      <c r="D81" s="80"/>
+      <c r="E81" s="106">
+        <f>SUM(D78:D80)</f>
+        <v>0</v>
+      </c>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="164" t="s">
+    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="38"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="B82" s="164"/>
-      <c r="C82" s="164"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="109">
-        <v>0</v>
-      </c>
-      <c r="F82" s="38"/>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="38"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
+      <c r="B83" s="164"/>
+      <c r="C83" s="164"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="109">
+        <v>0</v>
+      </c>
       <c r="F83" s="38"/>
     </row>
     <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="166" t="s">
+      <c r="A84" s="38"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="B84" s="167"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="42">
-        <f>E80+E82</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="38"/>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="38"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
+      <c r="B85" s="167"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="42">
+        <f>E81+E83</f>
+        <v>0</v>
+      </c>
       <c r="F85" s="38"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="177" t="s">
-        <v>20</v>
-      </c>
-      <c r="B86" s="178">
-        <f>E73</f>
-        <v>7505465.6599999992</v>
-      </c>
+      <c r="A86" s="38"/>
+      <c r="B86" s="38"/>
       <c r="C86" s="38"/>
       <c r="D86" s="38"/>
       <c r="E86" s="38"/>
@@ -3386,11 +3380,11 @@
     </row>
     <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="177" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B87" s="178">
-        <f>E73-E71</f>
-        <v>7505465.6599999992</v>
+        <f>E74</f>
+        <v>7736519.879999999</v>
       </c>
       <c r="C87" s="38"/>
       <c r="D87" s="38"/>
@@ -3399,11 +3393,11 @@
     </row>
     <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="177" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B88" s="178">
-        <f>E84-E82</f>
-        <v>0</v>
+        <f>E74-E72</f>
+        <v>7736519.879999999</v>
       </c>
       <c r="C88" s="38"/>
       <c r="D88" s="38"/>
@@ -3412,10 +3406,10 @@
     </row>
     <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="177" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B89" s="178">
-        <f>E84</f>
+        <f>E85-E83</f>
         <v>0</v>
       </c>
       <c r="C89" s="38"/>
@@ -3423,9 +3417,14 @@
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="38"/>
-      <c r="B90" s="38"/>
+    <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="177" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="178">
+        <f>E85</f>
+        <v>0</v>
+      </c>
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="38"/>
@@ -3440,35 +3439,31 @@
       <c r="F91" s="38"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="111" t="s">
-        <v>182</v>
-      </c>
-      <c r="B92" s="179">
-        <v>0</v>
-      </c>
+      <c r="A92" s="38"/>
+      <c r="B92" s="38"/>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="154" t="s">
-        <v>190</v>
-      </c>
-      <c r="B93" s="180">
-        <v>6500000</v>
+      <c r="A93" s="111" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" s="179">
+        <v>0</v>
       </c>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="154" t="s">
-        <v>225</v>
-      </c>
-      <c r="B94" s="268">
-        <v>-2000574.76</v>
+        <v>188</v>
+      </c>
+      <c r="B94" s="180">
+        <v>5125397.67</v>
       </c>
       <c r="C94" s="38"/>
       <c r="D94" s="38"/>
@@ -3477,33 +3472,36 @@
     </row>
     <row r="95" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="154" t="s">
-        <v>189</v>
-      </c>
-      <c r="B95" s="133">
-        <f>5125397.67-4998045.07</f>
-        <v>127352.59999999963</v>
+        <v>222</v>
+      </c>
+      <c r="B95" s="205">
+        <v>-2000574.76</v>
       </c>
       <c r="C95" s="38"/>
       <c r="D95" s="38"/>
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="181" t="s">
-        <v>178</v>
-      </c>
-      <c r="B96" s="182">
-        <f>SUM(B92:B95)</f>
-        <v>4626777.84</v>
+    <row r="96" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="154" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" s="133">
+        <f>B97-(B94+B95)</f>
+        <v>66737.25</v>
       </c>
       <c r="C96" s="38"/>
       <c r="D96" s="38"/>
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="183"/>
-      <c r="B97" s="184"/>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="181" t="s">
+        <v>177</v>
+      </c>
+      <c r="B97" s="182">
+        <v>3191560.16</v>
+      </c>
       <c r="C97" s="38"/>
       <c r="D97" s="38"/>
       <c r="E97" s="38"/>
@@ -3518,23 +3516,19 @@
       <c r="F98" s="38"/>
     </row>
     <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="111" t="s">
-        <v>160</v>
-      </c>
-      <c r="B99" s="51">
-        <v>231400</v>
-      </c>
+      <c r="A99" s="183"/>
+      <c r="B99" s="184"/>
       <c r="C99" s="38"/>
       <c r="D99" s="38"/>
       <c r="E99" s="38"/>
       <c r="F99" s="38"/>
     </row>
     <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="154" t="s">
-        <v>161</v>
-      </c>
-      <c r="B100" s="180">
-        <v>0</v>
+      <c r="A100" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="B100" s="51">
+        <v>231400</v>
       </c>
       <c r="C100" s="38"/>
       <c r="D100" s="38"/>
@@ -3543,53 +3537,53 @@
     </row>
     <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="154" t="s">
-        <v>162</v>
-      </c>
-      <c r="B101" s="133"/>
+        <v>161</v>
+      </c>
+      <c r="B101" s="180">
+        <v>0</v>
+      </c>
       <c r="C101" s="38"/>
       <c r="D101" s="38"/>
       <c r="E101" s="38"/>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="181" t="s">
-        <v>178</v>
-      </c>
-      <c r="B102" s="182">
-        <f>SUM(B99:B101)</f>
-        <v>231400</v>
-      </c>
+    <row r="102" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="154" t="s">
+        <v>162</v>
+      </c>
+      <c r="B102" s="133"/>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
       <c r="F102" s="38"/>
     </row>
-    <row r="103" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="183"/>
-      <c r="B103" s="184"/>
+    <row r="103" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="181" t="s">
+        <v>177</v>
+      </c>
+      <c r="B103" s="182">
+        <f>SUM(B100:B102)</f>
+        <v>231400</v>
+      </c>
       <c r="C103" s="38"/>
       <c r="D103" s="38"/>
       <c r="E103" s="38"/>
       <c r="F103" s="38"/>
     </row>
     <row r="104" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="B104" s="51">
-        <v>58418</v>
-      </c>
+      <c r="A104" s="183"/>
+      <c r="B104" s="184"/>
       <c r="C104" s="38"/>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
       <c r="F104" s="38"/>
     </row>
     <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="154" t="s">
-        <v>161</v>
-      </c>
-      <c r="B105" s="180">
-        <v>0</v>
+      <c r="A105" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" s="51">
+        <v>58418</v>
       </c>
       <c r="C105" s="38"/>
       <c r="D105" s="38"/>
@@ -3598,9 +3592,9 @@
     </row>
     <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="154" t="s">
-        <v>183</v>
-      </c>
-      <c r="B106" s="133">
+        <v>161</v>
+      </c>
+      <c r="B106" s="180">
         <v>0</v>
       </c>
       <c r="C106" s="38"/>
@@ -3610,10 +3604,10 @@
     </row>
     <row r="107" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="181" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B107" s="182">
-        <f>SUM(B104:B106)</f>
+        <f>SUM(B105:B106)</f>
         <v>58418</v>
       </c>
       <c r="C107" s="38"/>
@@ -3630,10 +3624,10 @@
     </row>
     <row r="109" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="111" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B109" s="51">
-        <v>281967.3499999987</v>
+        <v>-62147.730000001146</v>
       </c>
       <c r="C109" s="49"/>
       <c r="D109" s="108"/>
@@ -3644,8 +3638,8 @@
         <v>43</v>
       </c>
       <c r="B110" s="134">
-        <f>-B87-B88</f>
-        <v>-7505465.6599999992</v>
+        <f>-B88-B89</f>
+        <v>-7736519.879999999</v>
       </c>
       <c r="D110" s="38"/>
       <c r="E110" s="38"/>
@@ -3668,7 +3662,7 @@
       </c>
       <c r="B112" s="53">
         <f>PRORRATEO!G61</f>
-        <v>6230781.8999999994</v>
+        <v>5966274.4000000004</v>
       </c>
       <c r="D112" s="38"/>
       <c r="E112" s="38"/>
@@ -3678,7 +3672,7 @@
       <c r="A113" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="268">
+      <c r="B113" s="205">
         <v>-160000</v>
       </c>
       <c r="D113" s="38"/>
@@ -3687,21 +3681,21 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B114" s="268">
+        <v>180</v>
+      </c>
+      <c r="B114" s="205">
         <v>-16162</v>
       </c>
       <c r="D114" s="38"/>
-      <c r="E114" s="38"/>
+      <c r="E114" s="132"/>
       <c r="F114" s="48"/>
     </row>
     <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B115" s="268">
-        <f>-B94</f>
+        <v>185</v>
+      </c>
+      <c r="B115" s="210">
+        <f>-B95</f>
         <v>2000574.76</v>
       </c>
       <c r="D115" s="132"/>
@@ -3714,39 +3708,38 @@
       </c>
       <c r="B116" s="55">
         <f>SUM(B109:C115)</f>
-        <v>831696.34999999893</v>
+        <v>-7980.4499999999534</v>
       </c>
       <c r="D116" s="48"/>
       <c r="E116" s="40"/>
       <c r="F116" s="40"/>
     </row>
-    <row r="117" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E117" s="40"/>
+    </row>
     <row r="118" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="135" t="s">
         <v>164</v>
       </c>
       <c r="B118" s="136">
-        <f>B116+B102</f>
-        <v>1063096.3499999989</v>
+        <f>B116+B103</f>
+        <v>223419.55000000005</v>
       </c>
       <c r="D118" s="40"/>
       <c r="E118" s="40"/>
-      <c r="H118" t="s">
-        <v>191</v>
-      </c>
     </row>
     <row r="119" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="208" t="s">
+      <c r="A120" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="B120" s="208"/>
-      <c r="C120" s="208"/>
+      <c r="B120" s="225"/>
+      <c r="C120" s="225"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="208"/>
-      <c r="B121" s="208"/>
-      <c r="C121" s="208"/>
+      <c r="A121" s="225"/>
+      <c r="B121" s="225"/>
+      <c r="C121" s="225"/>
     </row>
     <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56"/>
@@ -3769,14 +3762,15 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A120:C121"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
@@ -3786,11 +3780,10 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3832,19 +3825,19 @@
       <c r="G1" s="126"/>
       <c r="H1" s="126"/>
       <c r="I1" s="126"/>
-      <c r="J1" s="218" t="str">
+      <c r="J1" s="256" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="218"/>
-      <c r="P1" s="219"/>
+      <c r="K1" s="256"/>
+      <c r="L1" s="256"/>
+      <c r="M1" s="256"/>
+      <c r="N1" s="256"/>
+      <c r="O1" s="256"/>
+      <c r="P1" s="257"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3852,22 +3845,24 @@
       </c>
       <c r="B2" s="127"/>
       <c r="C2" s="138">
-        <f>7325605.04-C5-305000.04-15405.58</f>
-        <v>5300000</v>
-      </c>
-      <c r="D2" s="68"/>
+        <f>D2-C4-C5</f>
+        <v>5827100.4799999995</v>
+      </c>
+      <c r="D2" s="271">
+        <v>7736519.879999999</v>
+      </c>
       <c r="E2" s="68"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="220"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="220"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="221"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="258"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
       <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3884,13 +3879,13 @@
       <c r="G3" s="131"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="220"/>
-      <c r="K3" s="220"/>
-      <c r="L3" s="220"/>
-      <c r="M3" s="220"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="220"/>
-      <c r="P3" s="221"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="M3" s="258"/>
+      <c r="N3" s="258"/>
+      <c r="O3" s="258"/>
+      <c r="P3" s="259"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
@@ -3908,13 +3903,13 @@
       <c r="G4" s="131"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="221"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="M4" s="258"/>
+      <c r="N4" s="258"/>
+      <c r="O4" s="258"/>
+      <c r="P4" s="259"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
@@ -3924,7 +3919,7 @@
       </c>
       <c r="B5" s="128"/>
       <c r="C5" s="139">
-        <v>1705199.42</v>
+        <v>1726596.39</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="69"/>
@@ -3932,201 +3927,201 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
-      <c r="M5" s="222"/>
-      <c r="N5" s="222"/>
-      <c r="O5" s="222"/>
-      <c r="P5" s="223"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
+      <c r="M5" s="260"/>
+      <c r="N5" s="260"/>
+      <c r="O5" s="260"/>
+      <c r="P5" s="261"/>
       <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="230" t="s">
+      <c r="A6" s="229" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="231"/>
-      <c r="C6" s="232"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="232"/>
-      <c r="I6" s="232"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="232"/>
-      <c r="L6" s="232"/>
-      <c r="M6" s="232"/>
-      <c r="N6" s="232"/>
-      <c r="O6" s="232"/>
-      <c r="P6" s="233"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="231"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="231"/>
+      <c r="G6" s="231"/>
+      <c r="H6" s="231"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="231"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="231"/>
+      <c r="M6" s="231"/>
+      <c r="N6" s="231"/>
+      <c r="O6" s="231"/>
+      <c r="P6" s="232"/>
       <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="234"/>
-      <c r="B7" s="235"/>
-      <c r="C7" s="235"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="235"/>
-      <c r="I7" s="235"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="235"/>
-      <c r="L7" s="235"/>
-      <c r="M7" s="235"/>
-      <c r="N7" s="235"/>
-      <c r="O7" s="235"/>
-      <c r="P7" s="236"/>
+      <c r="A7" s="233"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="234"/>
+      <c r="H7" s="234"/>
+      <c r="I7" s="234"/>
+      <c r="J7" s="234"/>
+      <c r="K7" s="234"/>
+      <c r="L7" s="234"/>
+      <c r="M7" s="234"/>
+      <c r="N7" s="234"/>
+      <c r="O7" s="234"/>
+      <c r="P7" s="235"/>
       <c r="Q7" s="62"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="234"/>
-      <c r="B8" s="235"/>
-      <c r="C8" s="235"/>
-      <c r="D8" s="235"/>
-      <c r="E8" s="235"/>
-      <c r="F8" s="235"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="235"/>
-      <c r="I8" s="235"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="235"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
-      <c r="N8" s="235"/>
-      <c r="O8" s="235"/>
-      <c r="P8" s="236"/>
+      <c r="A8" s="233"/>
+      <c r="B8" s="234"/>
+      <c r="C8" s="234"/>
+      <c r="D8" s="234"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="234"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="235"/>
       <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="234"/>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="236"/>
+      <c r="A9" s="233"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="235"/>
       <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="238"/>
-      <c r="O10" s="238"/>
-      <c r="P10" s="239"/>
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="237"/>
+      <c r="J10" s="237"/>
+      <c r="K10" s="237"/>
+      <c r="L10" s="237"/>
+      <c r="M10" s="237"/>
+      <c r="N10" s="237"/>
+      <c r="O10" s="237"/>
+      <c r="P10" s="238"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="248" t="s">
+      <c r="A11" s="249" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
-      <c r="M11" s="249"/>
-      <c r="N11" s="249"/>
-      <c r="O11" s="249"/>
-      <c r="P11" s="250"/>
+      <c r="B11" s="250"/>
+      <c r="C11" s="250"/>
+      <c r="D11" s="250"/>
+      <c r="E11" s="250"/>
+      <c r="F11" s="250"/>
+      <c r="G11" s="250"/>
+      <c r="H11" s="250"/>
+      <c r="I11" s="250"/>
+      <c r="J11" s="250"/>
+      <c r="K11" s="250"/>
+      <c r="L11" s="250"/>
+      <c r="M11" s="250"/>
+      <c r="N11" s="250"/>
+      <c r="O11" s="250"/>
+      <c r="P11" s="251"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="240" t="s">
+      <c r="A12" s="239" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="253" t="s">
+      <c r="B12" s="254" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="242" t="s">
+      <c r="C12" s="241" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="242" t="s">
+      <c r="D12" s="241" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="242" t="s">
+      <c r="E12" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="224" t="s">
+      <c r="F12" s="243" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="244" t="s">
+      <c r="G12" s="245" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="246" t="s">
+      <c r="H12" s="247" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="224" t="s">
+      <c r="I12" s="243" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="224" t="s">
+      <c r="J12" s="243" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="224" t="s">
+      <c r="K12" s="243" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="253" t="s">
+      <c r="L12" s="254" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="224" t="s">
+      <c r="M12" s="243" t="s">
         <v>167</v>
       </c>
-      <c r="N12" s="251" t="s">
-        <v>184</v>
+      <c r="N12" s="252" t="s">
+        <v>182</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="226" t="s">
+      <c r="P12" s="262" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="241"/>
-      <c r="B13" s="254"/>
-      <c r="C13" s="243"/>
-      <c r="D13" s="243"/>
-      <c r="E13" s="243"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="247"/>
-      <c r="I13" s="225"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="254"/>
-      <c r="M13" s="225"/>
-      <c r="N13" s="252"/>
+      <c r="A13" s="240"/>
+      <c r="B13" s="255"/>
+      <c r="C13" s="242"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="255"/>
+      <c r="M13" s="244"/>
+      <c r="N13" s="253"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P13" s="227"/>
+      <c r="P13" s="263"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
@@ -4145,7 +4140,7 @@
       <c r="F14" s="63">
         <v>375215.01</v>
       </c>
-      <c r="G14" s="269">
+      <c r="G14" s="63">
         <f t="shared" ref="G14" si="0">F14</f>
         <v>375215.01</v>
       </c>
@@ -4159,7 +4154,7 @@
       </c>
       <c r="J14" s="82">
         <f>C$2*E14/100</f>
-        <v>276660</v>
+        <v>304174.64505599992</v>
       </c>
       <c r="K14" s="82">
         <f t="shared" ref="K14:K45" si="2">F$2*E14/100</f>
@@ -4171,16 +4166,16 @@
       </c>
       <c r="M14" s="82">
         <f>C$5*E14/100</f>
-        <v>89011.409723999983</v>
+        <v>90128.331558000005</v>
       </c>
       <c r="N14" s="82"/>
       <c r="O14" s="76">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
-        <v>375215.01</v>
+        <v>403846.01</v>
       </c>
       <c r="P14" s="91">
         <f t="shared" ref="P14:P34" si="3">ROUND(O14*3%,0) + O14</f>
-        <v>386471.01</v>
+        <v>415961.01</v>
       </c>
       <c r="Q14" s="40">
         <v>0.01</v>
@@ -4216,7 +4211,7 @@
       </c>
       <c r="J15" s="82">
         <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K15" s="82">
         <f t="shared" si="2"/>
@@ -4228,16 +4223,16 @@
       </c>
       <c r="M15" s="82">
         <f t="shared" ref="M15:M59" si="7">C$5*E15/100</f>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N15" s="82"/>
       <c r="O15" s="76">
         <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>531420.02</v>
+        <v>550069.02</v>
       </c>
       <c r="P15" s="91">
         <f t="shared" si="3"/>
-        <v>547363.02</v>
+        <v>566571.02</v>
       </c>
       <c r="Q15" s="40">
         <f>Q14+0.01</f>
@@ -4263,7 +4258,7 @@
       <c r="F16" s="63">
         <v>182576.03</v>
       </c>
-      <c r="G16" s="269">
+      <c r="G16" s="63">
         <v>183000</v>
       </c>
       <c r="H16" s="75">
@@ -4276,7 +4271,7 @@
       </c>
       <c r="J16" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K16" s="82">
         <f t="shared" si="2"/>
@@ -4288,16 +4283,16 @@
       </c>
       <c r="M16" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N16" s="82"/>
       <c r="O16" s="76">
         <f t="shared" si="8"/>
-        <v>182152.03</v>
+        <v>196084.03</v>
       </c>
       <c r="P16" s="91">
         <f t="shared" si="3"/>
-        <v>187617.03</v>
+        <v>201967.03</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
@@ -4326,7 +4321,7 @@
       <c r="F17" s="63">
         <v>361285.04</v>
       </c>
-      <c r="G17" s="269">
+      <c r="G17" s="63">
         <f>435125-G55-G44</f>
         <v>374026.27</v>
       </c>
@@ -4340,7 +4335,7 @@
       </c>
       <c r="J17" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K17" s="82">
         <f t="shared" si="2"/>
@@ -4352,16 +4347,18 @@
       </c>
       <c r="M17" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
-      </c>
-      <c r="N17" s="82"/>
+        <v>89610.352641000005</v>
+      </c>
+      <c r="N17" s="82">
+        <v>43500</v>
+      </c>
       <c r="O17" s="76">
         <f t="shared" si="8"/>
-        <v>360317.04</v>
+        <v>432284.04</v>
       </c>
       <c r="P17" s="91">
         <f t="shared" si="3"/>
-        <v>371127.03999999998</v>
+        <v>445253.04</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="9"/>
@@ -4391,20 +4388,19 @@
         <v>244044.05</v>
       </c>
       <c r="G18" s="63">
-        <f>77540+140500</f>
-        <v>218040</v>
+        <v>0</v>
       </c>
       <c r="H18" s="75">
         <f t="shared" si="1"/>
-        <v>26004.049999999988</v>
+        <v>244044.05</v>
       </c>
       <c r="I18" s="75">
         <f t="shared" si="4"/>
-        <v>780.12149999999963</v>
+        <v>7321.3214999999991</v>
       </c>
       <c r="J18" s="82">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K18" s="82">
         <f t="shared" si="2"/>
@@ -4416,16 +4412,16 @@
       </c>
       <c r="M18" s="82">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N18" s="82"/>
       <c r="O18" s="76">
         <f t="shared" si="8"/>
-        <v>271177.05</v>
+        <v>514407.05</v>
       </c>
       <c r="P18" s="91">
         <f t="shared" si="3"/>
-        <v>279312.05</v>
+        <v>529839.05000000005</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="9"/>
@@ -4443,7 +4439,7 @@
         <v>118</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
@@ -4451,7 +4447,7 @@
       <c r="F19" s="63">
         <v>182576.06</v>
       </c>
-      <c r="G19" s="269">
+      <c r="G19" s="63">
         <f>F19</f>
         <v>182576.06</v>
       </c>
@@ -4465,7 +4461,7 @@
       </c>
       <c r="J19" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K19" s="82">
         <f t="shared" si="2"/>
@@ -4477,16 +4473,16 @@
       </c>
       <c r="M19" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N19" s="82"/>
       <c r="O19" s="76">
         <f t="shared" si="8"/>
-        <v>182576.06</v>
+        <v>196508.06</v>
       </c>
       <c r="P19" s="91">
         <f t="shared" si="3"/>
-        <v>188053.06</v>
+        <v>202403.06</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="9"/>
@@ -4510,7 +4506,7 @@
       <c r="F20" s="63">
         <v>373058.07</v>
       </c>
-      <c r="G20" s="269">
+      <c r="G20" s="63">
         <f t="shared" ref="G20:G25" si="10">F20</f>
         <v>373058.07</v>
       </c>
@@ -4524,7 +4520,7 @@
       </c>
       <c r="J20" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K20" s="82">
         <f t="shared" si="2"/>
@@ -4536,16 +4532,16 @@
       </c>
       <c r="M20" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
+        <v>89610.352641000005</v>
       </c>
       <c r="N20" s="82"/>
       <c r="O20" s="76">
         <f t="shared" si="8"/>
-        <v>373058.07</v>
+        <v>401525.07</v>
       </c>
       <c r="P20" s="91">
         <f t="shared" si="3"/>
-        <v>384250.07</v>
+        <v>413571.07</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="9"/>
@@ -4569,7 +4565,7 @@
       <c r="F21" s="63">
         <v>244393.08</v>
       </c>
-      <c r="G21" s="269">
+      <c r="G21" s="63">
         <f t="shared" si="10"/>
         <v>244393.08</v>
       </c>
@@ -4583,7 +4579,7 @@
       </c>
       <c r="J21" s="82">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K21" s="82">
         <f t="shared" si="2"/>
@@ -4595,16 +4591,16 @@
       </c>
       <c r="M21" s="82">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N21" s="82"/>
       <c r="O21" s="76">
         <f t="shared" si="8"/>
-        <v>244393.08</v>
+        <v>263042.08</v>
       </c>
       <c r="P21" s="91">
         <f t="shared" si="3"/>
-        <v>251725.08</v>
+        <v>270933.08</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="9"/>
@@ -4630,7 +4626,7 @@
       <c r="F22" s="63">
         <v>182576.09</v>
       </c>
-      <c r="G22" s="269">
+      <c r="G22" s="63">
         <f t="shared" si="10"/>
         <v>182576.09</v>
       </c>
@@ -4644,7 +4640,7 @@
       </c>
       <c r="J22" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K22" s="82">
         <f t="shared" si="2"/>
@@ -4656,16 +4652,16 @@
       </c>
       <c r="M22" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N22" s="82"/>
       <c r="O22" s="76">
         <f t="shared" si="8"/>
-        <v>182576.09</v>
+        <v>196508.09</v>
       </c>
       <c r="P22" s="91">
         <f t="shared" si="3"/>
-        <v>188053.09</v>
+        <v>202403.09</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="9"/>
@@ -4689,7 +4685,7 @@
       <c r="F23" s="63">
         <v>373058.1</v>
       </c>
-      <c r="G23" s="269">
+      <c r="G23" s="63">
         <f t="shared" si="10"/>
         <v>373058.1</v>
       </c>
@@ -4703,7 +4699,7 @@
       </c>
       <c r="J23" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K23" s="82">
         <f t="shared" si="2"/>
@@ -4715,16 +4711,16 @@
       </c>
       <c r="M23" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
+        <v>89610.352641000005</v>
       </c>
       <c r="N23" s="82"/>
       <c r="O23" s="76">
         <f t="shared" si="8"/>
-        <v>373058.1</v>
+        <v>401525.1</v>
       </c>
       <c r="P23" s="91">
         <f t="shared" si="3"/>
-        <v>384250.1</v>
+        <v>413571.1</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="9"/>
@@ -4750,7 +4746,7 @@
       <c r="F24" s="63">
         <v>244393.11</v>
       </c>
-      <c r="G24" s="269">
+      <c r="G24" s="63">
         <f t="shared" si="10"/>
         <v>244393.11</v>
       </c>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="J24" s="82">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K24" s="82">
         <f t="shared" si="2"/>
@@ -4776,16 +4772,16 @@
       </c>
       <c r="M24" s="82">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N24" s="82"/>
       <c r="O24" s="76">
         <f t="shared" si="8"/>
-        <v>244393.11</v>
+        <v>263042.11</v>
       </c>
       <c r="P24" s="91">
         <f t="shared" si="3"/>
-        <v>251725.11</v>
+        <v>270933.11</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="9"/>
@@ -4811,7 +4807,7 @@
       <c r="F25" s="63">
         <v>182576.12</v>
       </c>
-      <c r="G25" s="269">
+      <c r="G25" s="63">
         <f t="shared" si="10"/>
         <v>182576.12</v>
       </c>
@@ -4825,7 +4821,7 @@
       </c>
       <c r="J25" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K25" s="82">
         <f t="shared" si="2"/>
@@ -4837,16 +4833,16 @@
       </c>
       <c r="M25" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N25" s="82"/>
       <c r="O25" s="76">
         <f t="shared" si="8"/>
-        <v>182576.12</v>
+        <v>196508.12</v>
       </c>
       <c r="P25" s="91">
         <f t="shared" si="3"/>
-        <v>188053.12</v>
+        <v>202403.12</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="9"/>
@@ -4861,7 +4857,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="77"/>
       <c r="E26" s="74">
@@ -4870,7 +4866,7 @@
       <c r="F26" s="63">
         <v>363291.13</v>
       </c>
-      <c r="G26" s="269">
+      <c r="G26" s="63">
         <f>F26</f>
         <v>363291.13</v>
       </c>
@@ -4884,7 +4880,7 @@
       </c>
       <c r="J26" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K26" s="82">
         <f t="shared" si="2"/>
@@ -4896,16 +4892,16 @@
       </c>
       <c r="M26" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
+        <v>89610.352641000005</v>
       </c>
       <c r="N26" s="82"/>
       <c r="O26" s="76">
         <f t="shared" si="8"/>
-        <v>373058.13</v>
+        <v>401525.13</v>
       </c>
       <c r="P26" s="91">
         <f t="shared" si="3"/>
-        <v>384250.13</v>
+        <v>413571.13</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="9"/>
@@ -4929,7 +4925,7 @@
       <c r="F27" s="145">
         <v>235999.14</v>
       </c>
-      <c r="G27" s="270">
+      <c r="G27" s="145">
         <f>314895.52-G51</f>
         <v>245171.14</v>
       </c>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="J27" s="147">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K27" s="147">
         <f t="shared" si="2"/>
@@ -4955,16 +4951,16 @@
       </c>
       <c r="M27" s="147">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N27" s="147"/>
       <c r="O27" s="148">
         <f t="shared" si="8"/>
-        <v>235221.14</v>
+        <v>253870.14</v>
       </c>
       <c r="P27" s="149">
         <f t="shared" si="3"/>
-        <v>242278.14</v>
+        <v>261486.14</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="9"/>
@@ -4990,7 +4986,7 @@
       <c r="F28" s="63">
         <v>182576.15</v>
       </c>
-      <c r="G28" s="269">
+      <c r="G28" s="63">
         <f t="shared" ref="G28" si="11">F28</f>
         <v>182576.15</v>
       </c>
@@ -5004,7 +5000,7 @@
       </c>
       <c r="J28" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K28" s="82">
         <f t="shared" si="2"/>
@@ -5016,16 +5012,16 @@
       </c>
       <c r="M28" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N28" s="82"/>
       <c r="O28" s="76">
         <f t="shared" si="8"/>
-        <v>182576.15</v>
+        <v>196508.15</v>
       </c>
       <c r="P28" s="91">
         <f t="shared" si="3"/>
-        <v>188053.15</v>
+        <v>202403.15</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="9"/>
@@ -5049,7 +5045,7 @@
       <c r="F29" s="63">
         <v>373058.16</v>
       </c>
-      <c r="G29" s="269">
+      <c r="G29" s="63">
         <f>F29</f>
         <v>373058.16</v>
       </c>
@@ -5063,7 +5059,7 @@
       </c>
       <c r="J29" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K29" s="82">
         <f t="shared" si="2"/>
@@ -5075,16 +5071,16 @@
       </c>
       <c r="M29" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
+        <v>89610.352641000005</v>
       </c>
       <c r="N29" s="82"/>
       <c r="O29" s="76">
         <f t="shared" si="8"/>
-        <v>373058.16</v>
+        <v>401525.16</v>
       </c>
       <c r="P29" s="91">
         <f t="shared" si="3"/>
-        <v>384250.16</v>
+        <v>413571.16</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" si="9"/>
@@ -5110,7 +5106,7 @@
       <c r="F30" s="63">
         <v>242901.17</v>
       </c>
-      <c r="G30" s="269">
+      <c r="G30" s="63">
         <f>243901.17</f>
         <v>243901.17</v>
       </c>
@@ -5124,7 +5120,7 @@
       </c>
       <c r="J30" s="82">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K30" s="82">
         <f t="shared" si="2"/>
@@ -5136,16 +5132,16 @@
       </c>
       <c r="M30" s="82">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N30" s="82"/>
       <c r="O30" s="76">
         <f t="shared" si="8"/>
-        <v>243393.17</v>
+        <v>262042.17</v>
       </c>
       <c r="P30" s="91">
         <f t="shared" si="3"/>
-        <v>250695.17</v>
+        <v>269903.17000000004</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="9"/>
@@ -5180,7 +5176,7 @@
       </c>
       <c r="J31" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K31" s="82">
         <f t="shared" si="2"/>
@@ -5192,16 +5188,16 @@
       </c>
       <c r="M31" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N31" s="82"/>
       <c r="O31" s="76">
         <f t="shared" si="8"/>
-        <v>2084625.18</v>
+        <v>2098557.1800000002</v>
       </c>
       <c r="P31" s="91">
         <f t="shared" si="3"/>
-        <v>2147164.1799999997</v>
+        <v>2161514.1800000002</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="9"/>
@@ -5238,7 +5234,7 @@
       </c>
       <c r="J32" s="82">
         <f t="shared" si="5"/>
-        <v>275070.00000000006</v>
+        <v>302426.51491199998</v>
       </c>
       <c r="K32" s="82">
         <f t="shared" si="2"/>
@@ -5250,18 +5246,16 @@
       </c>
       <c r="M32" s="82">
         <f t="shared" si="7"/>
-        <v>88499.849898</v>
-      </c>
-      <c r="N32" s="82">
-        <v>43500</v>
-      </c>
+        <v>89610.352641000005</v>
+      </c>
+      <c r="N32" s="82"/>
       <c r="O32" s="76">
         <f t="shared" si="8"/>
-        <v>2058901.19</v>
+        <v>2043868.19</v>
       </c>
       <c r="P32" s="91">
         <f t="shared" si="3"/>
-        <v>2120668.19</v>
+        <v>2105184.19</v>
       </c>
       <c r="Q32" s="40">
         <f>Q31+0.01</f>
@@ -5285,7 +5279,7 @@
       <c r="F33" s="188">
         <v>237260.2</v>
       </c>
-      <c r="G33" s="271">
+      <c r="G33" s="188">
         <f>249002-G47</f>
         <v>243251.66</v>
       </c>
@@ -5296,7 +5290,7 @@
       <c r="I33" s="189"/>
       <c r="J33" s="190">
         <f t="shared" si="5"/>
-        <v>180200</v>
+        <v>198121.41631999999</v>
       </c>
       <c r="K33" s="190">
         <f t="shared" si="2"/>
@@ -5308,16 +5302,16 @@
       </c>
       <c r="M33" s="190">
         <f t="shared" si="7"/>
-        <v>57976.780279999999</v>
+        <v>58704.277259999995</v>
       </c>
       <c r="N33" s="190"/>
       <c r="O33" s="191">
         <f t="shared" si="8"/>
-        <v>238401.2</v>
+        <v>257050.2</v>
       </c>
       <c r="P33" s="192">
         <f t="shared" si="3"/>
-        <v>245553.2</v>
+        <v>264762.2</v>
       </c>
       <c r="Q33" s="40">
         <f t="shared" ref="Q33:Q59" si="12">Q32+0.01</f>
@@ -5343,7 +5337,7 @@
       <c r="F34" s="63">
         <v>182576.21</v>
       </c>
-      <c r="G34" s="269">
+      <c r="G34" s="63">
         <f t="shared" ref="G34:G35" si="13">F34</f>
         <v>182576.21</v>
       </c>
@@ -5357,7 +5351,7 @@
       </c>
       <c r="J34" s="82">
         <f t="shared" si="5"/>
-        <v>134620</v>
+        <v>148008.35219199999</v>
       </c>
       <c r="K34" s="82">
         <f t="shared" si="2"/>
@@ -5369,16 +5363,16 @@
       </c>
       <c r="M34" s="82">
         <f t="shared" si="7"/>
-        <v>43312.065267999998</v>
+        <v>43855.548305999997</v>
       </c>
       <c r="N34" s="82"/>
       <c r="O34" s="76">
         <f t="shared" si="8"/>
-        <v>182576.21</v>
+        <v>196508.21</v>
       </c>
       <c r="P34" s="91">
         <f t="shared" si="3"/>
-        <v>188053.21</v>
+        <v>202403.21</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" si="12"/>
@@ -5405,7 +5399,7 @@
       <c r="F35" s="63">
         <v>355088.22</v>
       </c>
-      <c r="G35" s="269">
+      <c r="G35" s="63">
         <f t="shared" si="13"/>
         <v>355088.22</v>
       </c>
@@ -5419,7 +5413,7 @@
       </c>
       <c r="J35" s="82">
         <f t="shared" si="5"/>
-        <v>261820.00000000003</v>
+        <v>287858.76371199999</v>
       </c>
       <c r="K35" s="82">
         <f t="shared" si="2"/>
@@ -5431,16 +5425,16 @@
       </c>
       <c r="M35" s="82">
         <f t="shared" si="7"/>
-        <v>84236.851347999997</v>
+        <v>85293.861665999997</v>
       </c>
       <c r="N35" s="82"/>
       <c r="O35" s="76">
         <f t="shared" si="8"/>
-        <v>355088.22</v>
+        <v>382184.22</v>
       </c>
       <c r="P35" s="91">
         <f t="shared" ref="P35:P59" si="14">ROUND(O35*3%,0) + O35</f>
-        <v>365741.22</v>
+        <v>393650.22</v>
       </c>
       <c r="Q35" s="40">
         <f t="shared" si="12"/>
@@ -5467,7 +5461,7 @@
       <c r="F36" s="63">
         <v>229421.23</v>
       </c>
-      <c r="G36" s="269">
+      <c r="G36" s="63">
         <f>229441</f>
         <v>229441</v>
       </c>
@@ -5481,7 +5475,7 @@
       </c>
       <c r="J36" s="82">
         <f t="shared" si="5"/>
-        <v>173840</v>
+        <v>191128.89574399998</v>
       </c>
       <c r="K36" s="82">
         <f t="shared" si="2"/>
@@ -5493,16 +5487,16 @@
       </c>
       <c r="M36" s="82">
         <f t="shared" si="7"/>
-        <v>55930.540975999989</v>
+        <v>56632.361591999994</v>
       </c>
       <c r="N36" s="82"/>
       <c r="O36" s="76">
         <f t="shared" si="8"/>
-        <v>235747.23</v>
+        <v>253738.23</v>
       </c>
       <c r="P36" s="91">
         <f t="shared" si="14"/>
-        <v>242819.23</v>
+        <v>261350.23</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="12"/>
@@ -5528,19 +5522,19 @@
         <v>168602.23999999999</v>
       </c>
       <c r="G37" s="63">
-        <v>158933.24</v>
+        <v>0</v>
       </c>
       <c r="H37" s="75">
         <f t="shared" si="1"/>
-        <v>9669</v>
+        <v>168602.23999999999</v>
       </c>
       <c r="I37" s="75">
         <f t="shared" si="4"/>
-        <v>290.07</v>
+        <v>5058.0671999999995</v>
       </c>
       <c r="J37" s="82">
         <f t="shared" si="5"/>
-        <v>127730</v>
+        <v>140433.121568</v>
       </c>
       <c r="K37" s="82">
         <f t="shared" si="2"/>
@@ -5552,16 +5546,16 @@
       </c>
       <c r="M37" s="82">
         <f t="shared" si="7"/>
-        <v>41095.306022000004</v>
+        <v>41610.972998999998</v>
       </c>
       <c r="N37" s="82"/>
       <c r="O37" s="76">
         <f t="shared" si="8"/>
-        <v>183190.24</v>
+        <v>360110.24</v>
       </c>
       <c r="P37" s="91">
         <f t="shared" si="14"/>
-        <v>188686.24</v>
+        <v>370913.24</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="12"/>
@@ -5586,21 +5580,21 @@
       <c r="F38" s="63">
         <v>87050.25</v>
       </c>
-      <c r="G38" s="269">
-        <f>16162+70888</f>
-        <v>87050</v>
+      <c r="G38" s="63">
+        <f>16162+70888+(152000/3)</f>
+        <v>137716.66666666666</v>
       </c>
       <c r="H38" s="75">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>-50666.416666666657</v>
       </c>
       <c r="I38" s="75">
         <f t="shared" si="4"/>
-        <v>7.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="J38" s="82">
         <f t="shared" si="5"/>
-        <v>23320</v>
+        <v>25639.242111999996</v>
       </c>
       <c r="K38" s="82">
         <f t="shared" si="2"/>
@@ -5612,16 +5606,16 @@
       </c>
       <c r="M38" s="82">
         <f t="shared" si="7"/>
-        <v>7502.8774480000002</v>
+        <v>7597.0241159999996</v>
       </c>
       <c r="N38" s="82"/>
       <c r="O38" s="76">
         <f t="shared" si="8"/>
-        <v>31628.25</v>
+        <v>-16625.75</v>
       </c>
       <c r="P38" s="91">
         <f t="shared" si="14"/>
-        <v>32577.25</v>
+        <v>-17124.75</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" si="12"/>
@@ -5650,20 +5644,19 @@
         <v>39534.26</v>
       </c>
       <c r="G39" s="63">
-        <f t="shared" ref="G39:G40" si="16">F39</f>
-        <v>39534.26</v>
+        <v>0</v>
       </c>
       <c r="H39" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39534.26</v>
       </c>
       <c r="I39" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1186.0278000000001</v>
       </c>
       <c r="J39" s="82">
         <f t="shared" si="5"/>
-        <v>29150.000000000004</v>
+        <v>32049.052639999998</v>
       </c>
       <c r="K39" s="82">
         <f t="shared" si="2"/>
@@ -5675,16 +5668,16 @@
       </c>
       <c r="M39" s="82">
         <f t="shared" si="7"/>
-        <v>9378.5968099999991</v>
+        <v>9496.2801450000006</v>
       </c>
       <c r="N39" s="82"/>
       <c r="O39" s="76">
         <f t="shared" si="8"/>
-        <v>39534.26</v>
+        <v>83271.259999999995</v>
       </c>
       <c r="P39" s="91">
         <f t="shared" si="14"/>
-        <v>40720.26</v>
+        <v>85769.26</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" si="12"/>
@@ -5709,8 +5702,8 @@
       <c r="F40" s="63">
         <v>38097.269999999997</v>
       </c>
-      <c r="G40" s="269">
-        <f t="shared" si="16"/>
+      <c r="G40" s="63">
+        <f t="shared" ref="G40" si="16">F40</f>
         <v>38097.269999999997</v>
       </c>
       <c r="H40" s="75">
@@ -5723,7 +5716,7 @@
       </c>
       <c r="J40" s="82">
         <f t="shared" si="5"/>
-        <v>28090</v>
+        <v>30883.632544</v>
       </c>
       <c r="K40" s="82">
         <f t="shared" si="2"/>
@@ -5735,16 +5728,16 @@
       </c>
       <c r="M40" s="82">
         <f t="shared" si="7"/>
-        <v>9037.5569259999993</v>
+        <v>9150.9608669999998</v>
       </c>
       <c r="N40" s="82"/>
       <c r="O40" s="76">
         <f t="shared" si="8"/>
-        <v>38097.269999999997</v>
+        <v>41004.269999999997</v>
       </c>
       <c r="P40" s="91">
         <f t="shared" si="14"/>
-        <v>39240.269999999997</v>
+        <v>42234.27</v>
       </c>
       <c r="Q40" s="40">
         <f t="shared" si="12"/>
@@ -5782,7 +5775,7 @@
       </c>
       <c r="J41" s="82">
         <f t="shared" si="5"/>
-        <v>15370</v>
+        <v>16898.591391999995</v>
       </c>
       <c r="K41" s="82">
         <f t="shared" si="2"/>
@@ -5794,16 +5787,16 @@
       </c>
       <c r="M41" s="82">
         <f t="shared" si="7"/>
-        <v>4945.0783179999989</v>
+        <v>5007.1295309999996</v>
       </c>
       <c r="N41" s="82"/>
       <c r="O41" s="76">
         <f t="shared" si="8"/>
-        <v>62016.28</v>
+        <v>63606.28</v>
       </c>
       <c r="P41" s="91">
         <f t="shared" si="14"/>
-        <v>63876.28</v>
+        <v>65514.28</v>
       </c>
       <c r="Q41" s="40">
         <f t="shared" si="12"/>
@@ -5830,7 +5823,7 @@
       <c r="F42" s="63">
         <v>5750.29</v>
       </c>
-      <c r="G42" s="269">
+      <c r="G42" s="63">
         <f t="shared" ref="G42:G43" si="17">F42</f>
         <v>5750.29</v>
       </c>
@@ -5844,7 +5837,7 @@
       </c>
       <c r="J42" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K42" s="82">
         <f t="shared" si="2"/>
@@ -5856,16 +5849,16 @@
       </c>
       <c r="M42" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N42" s="82"/>
       <c r="O42" s="76">
         <f t="shared" si="8"/>
-        <v>5750.29</v>
+        <v>6189.29</v>
       </c>
       <c r="P42" s="91">
         <f t="shared" si="14"/>
-        <v>5923.29</v>
+        <v>6375.29</v>
       </c>
       <c r="Q42" s="40">
         <f t="shared" si="12"/>
@@ -5890,7 +5883,7 @@
       <c r="F43" s="63">
         <v>5750.3</v>
       </c>
-      <c r="G43" s="269">
+      <c r="G43" s="63">
         <f t="shared" si="17"/>
         <v>5750.3</v>
       </c>
@@ -5904,7 +5897,7 @@
       </c>
       <c r="J43" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K43" s="82">
         <f t="shared" si="2"/>
@@ -5916,16 +5909,16 @@
       </c>
       <c r="M43" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N43" s="82"/>
       <c r="O43" s="76">
         <f t="shared" si="8"/>
-        <v>5750.3</v>
+        <v>6189.3</v>
       </c>
       <c r="P43" s="91">
         <f t="shared" si="14"/>
-        <v>5923.3</v>
+        <v>6375.3</v>
       </c>
       <c r="Q43" s="40">
         <f t="shared" si="12"/>
@@ -5952,7 +5945,7 @@
       <c r="F44" s="63">
         <v>5750.31</v>
       </c>
-      <c r="G44" s="269">
+      <c r="G44" s="63">
         <f>F44</f>
         <v>5750.31</v>
       </c>
@@ -5966,7 +5959,7 @@
       </c>
       <c r="J44" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K44" s="82">
         <f t="shared" si="2"/>
@@ -5978,16 +5971,16 @@
       </c>
       <c r="M44" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N44" s="82"/>
       <c r="O44" s="76">
         <f t="shared" si="8"/>
-        <v>5750.31</v>
+        <v>6189.31</v>
       </c>
       <c r="P44" s="91">
         <f t="shared" si="14"/>
-        <v>5923.31</v>
+        <v>6375.31</v>
       </c>
       <c r="Q44" s="40">
         <f t="shared" si="12"/>
@@ -6015,7 +6008,7 @@
       <c r="F45" s="63">
         <v>5750.32</v>
       </c>
-      <c r="G45" s="269">
+      <c r="G45" s="63">
         <f>F45</f>
         <v>5750.32</v>
       </c>
@@ -6029,7 +6022,7 @@
       </c>
       <c r="J45" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K45" s="82">
         <f t="shared" si="2"/>
@@ -6041,16 +6034,16 @@
       </c>
       <c r="M45" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N45" s="82"/>
       <c r="O45" s="76">
         <f t="shared" si="8"/>
-        <v>5750.32</v>
+        <v>6189.32</v>
       </c>
       <c r="P45" s="91">
         <f t="shared" si="14"/>
-        <v>5923.32</v>
+        <v>6375.32</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="12"/>
@@ -6083,7 +6076,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K46" s="82">
         <f t="shared" ref="K46:K59" si="18">F$2*E46/100</f>
@@ -6095,16 +6088,16 @@
       </c>
       <c r="M46" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N46" s="82"/>
       <c r="O46" s="76">
         <f t="shared" si="8"/>
-        <v>34936.33</v>
+        <v>35375.33</v>
       </c>
       <c r="P46" s="91">
         <f t="shared" si="14"/>
-        <v>35984.33</v>
+        <v>36436.33</v>
       </c>
       <c r="Q46" s="40">
         <f t="shared" si="12"/>
@@ -6129,7 +6122,7 @@
       <c r="F47" s="63">
         <v>5750.34</v>
       </c>
-      <c r="G47" s="269">
+      <c r="G47" s="63">
         <f>F47</f>
         <v>5750.34</v>
       </c>
@@ -6143,7 +6136,7 @@
       </c>
       <c r="J47" s="82">
         <f t="shared" si="5"/>
-        <v>4240</v>
+        <v>4661.6803839999993</v>
       </c>
       <c r="K47" s="82">
         <f t="shared" si="18"/>
@@ -6155,16 +6148,16 @@
       </c>
       <c r="M47" s="82">
         <f t="shared" si="7"/>
-        <v>1364.1595360000001</v>
+        <v>1381.277112</v>
       </c>
       <c r="N47" s="82"/>
       <c r="O47" s="76">
         <f t="shared" si="8"/>
-        <v>5750.34</v>
+        <v>6189.34</v>
       </c>
       <c r="P47" s="91">
         <f t="shared" si="14"/>
-        <v>5923.34</v>
+        <v>6375.34</v>
       </c>
       <c r="Q47" s="40">
         <f t="shared" si="12"/>
@@ -6189,7 +6182,7 @@
       <c r="F48" s="63">
         <v>12404.35</v>
       </c>
-      <c r="G48" s="269">
+      <c r="G48" s="63">
         <f>12776.35</f>
         <v>12776.35</v>
       </c>
@@ -6203,7 +6196,7 @@
       </c>
       <c r="J48" s="82">
         <f t="shared" si="5"/>
-        <v>4770</v>
+        <v>5244.3904319999992</v>
       </c>
       <c r="K48" s="125">
         <f t="shared" si="18"/>
@@ -6215,16 +6208,16 @@
       </c>
       <c r="M48" s="82">
         <f t="shared" si="7"/>
-        <v>1534.679478</v>
+        <v>1553.936751</v>
       </c>
       <c r="N48" s="125"/>
       <c r="O48" s="76">
         <f t="shared" si="8"/>
-        <v>6097.35</v>
+        <v>6591.35</v>
       </c>
       <c r="P48" s="91">
         <f t="shared" si="14"/>
-        <v>6280.35</v>
+        <v>6789.35</v>
       </c>
       <c r="Q48" s="40">
         <f t="shared" si="12"/>
@@ -6249,7 +6242,7 @@
       <c r="F49" s="63">
         <v>56785.36</v>
       </c>
-      <c r="G49" s="269">
+      <c r="G49" s="63">
         <f>F49</f>
         <v>56785.36</v>
       </c>
@@ -6263,7 +6256,7 @@
       </c>
       <c r="J49" s="82">
         <f t="shared" si="5"/>
-        <v>41870</v>
+        <v>46034.093791999992</v>
       </c>
       <c r="K49" s="82">
         <f t="shared" si="18"/>
@@ -6275,16 +6268,16 @@
       </c>
       <c r="M49" s="82">
         <f t="shared" si="7"/>
-        <v>13471.075418</v>
+        <v>13640.111480999998</v>
       </c>
       <c r="N49" s="82"/>
       <c r="O49" s="76">
         <f t="shared" si="8"/>
-        <v>56785.36</v>
+        <v>61119.360000000001</v>
       </c>
       <c r="P49" s="91">
         <f t="shared" si="14"/>
-        <v>58489.36</v>
+        <v>62953.36</v>
       </c>
       <c r="Q49" s="40">
         <f t="shared" si="12"/>
@@ -6320,7 +6313,7 @@
       </c>
       <c r="J50" s="82">
         <f t="shared" si="5"/>
-        <v>53000</v>
+        <v>58271.004799999995</v>
       </c>
       <c r="K50" s="82">
         <f t="shared" si="18"/>
@@ -6332,16 +6325,16 @@
       </c>
       <c r="M50" s="82">
         <f t="shared" si="7"/>
-        <v>17051.994200000001</v>
+        <v>17265.963899999999</v>
       </c>
       <c r="N50" s="82"/>
       <c r="O50" s="76">
         <f t="shared" si="8"/>
-        <v>469005.37</v>
+        <v>474490.37</v>
       </c>
       <c r="P50" s="91">
         <f t="shared" si="14"/>
-        <v>483075.37</v>
+        <v>488725.37</v>
       </c>
       <c r="Q50" s="40">
         <f t="shared" si="12"/>
@@ -6366,7 +6359,7 @@
       <c r="F51" s="63">
         <v>69724.38</v>
       </c>
-      <c r="G51" s="269">
+      <c r="G51" s="63">
         <f>F51</f>
         <v>69724.38</v>
       </c>
@@ -6380,7 +6373,7 @@
       </c>
       <c r="J51" s="82">
         <f t="shared" si="5"/>
-        <v>51410</v>
+        <v>56522.874656</v>
       </c>
       <c r="K51" s="82">
         <f t="shared" si="18"/>
@@ -6392,16 +6385,16 @@
       </c>
       <c r="M51" s="82">
         <f t="shared" si="7"/>
-        <v>16540.434374</v>
+        <v>16747.984982999998</v>
       </c>
       <c r="N51" s="82"/>
       <c r="O51" s="76">
         <f t="shared" si="8"/>
-        <v>69724.38</v>
+        <v>75044.38</v>
       </c>
       <c r="P51" s="91">
         <f t="shared" si="14"/>
-        <v>71816.38</v>
+        <v>77295.38</v>
       </c>
       <c r="Q51" s="40">
         <f t="shared" si="12"/>
@@ -6426,12 +6419,13 @@
       <c r="F52" s="63">
         <v>159501.39000000001</v>
       </c>
-      <c r="G52" s="269">
-        <v>160000</v>
+      <c r="G52" s="63">
+        <f>160000+(152000/3)</f>
+        <v>210666.66666666666</v>
       </c>
       <c r="H52" s="75">
         <f t="shared" si="1"/>
-        <v>-498.60999999998603</v>
+        <v>-51165.276666666643</v>
       </c>
       <c r="I52" s="75">
         <f t="shared" si="4"/>
@@ -6439,7 +6433,7 @@
       </c>
       <c r="J52" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
+        <v>44868.673695999998</v>
       </c>
       <c r="K52" s="82">
         <f t="shared" si="18"/>
@@ -6451,16 +6445,16 @@
       </c>
       <c r="M52" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
+        <v>13294.792202999999</v>
       </c>
       <c r="N52" s="82"/>
       <c r="O52" s="76">
         <f t="shared" si="8"/>
-        <v>54849.39</v>
+        <v>8406.39</v>
       </c>
       <c r="P52" s="91">
         <f t="shared" si="14"/>
-        <v>56494.39</v>
+        <v>8658.39</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" si="12"/>
@@ -6471,61 +6465,61 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="140">
+      <c r="A53" s="83">
         <f t="shared" si="15"/>
         <v>40</v>
       </c>
-      <c r="B53" s="141" t="s">
+      <c r="B53" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="274" t="s">
+      <c r="C53" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="143" t="s">
+      <c r="D53" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="E53" s="144">
+      <c r="E53" s="74">
         <v>0.77</v>
       </c>
-      <c r="F53" s="145">
+      <c r="F53" s="63">
         <v>55348.4</v>
       </c>
-      <c r="G53" s="270">
+      <c r="G53" s="63">
         <f>F53</f>
         <v>55348.4</v>
       </c>
-      <c r="H53" s="146">
+      <c r="H53" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="146">
+      <c r="I53" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J53" s="147">
+      <c r="J53" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
-      </c>
-      <c r="K53" s="147">
+        <v>44868.673695999998</v>
+      </c>
+      <c r="K53" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L53" s="147">
+      <c r="L53" s="82">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="147">
+      <c r="M53" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
-      </c>
-      <c r="N53" s="147"/>
-      <c r="O53" s="148">
+        <v>13294.792202999999</v>
+      </c>
+      <c r="N53" s="82"/>
+      <c r="O53" s="76">
         <f t="shared" si="8"/>
-        <v>55348.4</v>
-      </c>
-      <c r="P53" s="149">
+        <v>59571.4</v>
+      </c>
+      <c r="P53" s="91">
         <f t="shared" si="14"/>
-        <v>57008.4</v>
+        <v>61358.400000000001</v>
       </c>
       <c r="Q53" s="40">
         <f t="shared" si="12"/>
@@ -6565,7 +6559,7 @@
       </c>
       <c r="J54" s="82">
         <f t="shared" si="5"/>
-        <v>42930</v>
+        <v>47199.513888000001</v>
       </c>
       <c r="K54" s="82">
         <f t="shared" si="18"/>
@@ -6577,16 +6571,16 @@
       </c>
       <c r="M54" s="82">
         <f t="shared" si="7"/>
-        <v>13812.115301999998</v>
+        <v>13985.430759000001</v>
       </c>
       <c r="N54" s="82"/>
       <c r="O54" s="76">
         <f t="shared" si="8"/>
-        <v>173214.41</v>
+        <v>177656.41</v>
       </c>
       <c r="P54" s="91">
         <f t="shared" si="14"/>
-        <v>178410.41</v>
+        <v>182986.41</v>
       </c>
       <c r="Q54" s="40">
         <f t="shared" si="12"/>
@@ -6613,7 +6607,7 @@
       <c r="F55" s="63">
         <v>55348.42</v>
       </c>
-      <c r="G55" s="269">
+      <c r="G55" s="63">
         <f>F55</f>
         <v>55348.42</v>
       </c>
@@ -6624,7 +6618,7 @@
       <c r="I55" s="75"/>
       <c r="J55" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
+        <v>44868.673695999998</v>
       </c>
       <c r="K55" s="82">
         <f t="shared" si="18"/>
@@ -6636,16 +6630,16 @@
       </c>
       <c r="M55" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
+        <v>13294.792202999999</v>
       </c>
       <c r="N55" s="82"/>
       <c r="O55" s="76">
         <f t="shared" si="8"/>
-        <v>55348.42</v>
+        <v>59571.42</v>
       </c>
       <c r="P55" s="91">
         <f t="shared" si="14"/>
-        <v>57008.42</v>
+        <v>61358.42</v>
       </c>
       <c r="Q55" s="40">
         <f t="shared" si="12"/>
@@ -6684,7 +6678,7 @@
       </c>
       <c r="J56" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
+        <v>44868.673695999998</v>
       </c>
       <c r="K56" s="82">
         <f t="shared" si="18"/>
@@ -6696,16 +6690,16 @@
       </c>
       <c r="M56" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
+        <v>13294.792202999999</v>
       </c>
       <c r="N56" s="82"/>
       <c r="O56" s="76">
         <f t="shared" si="8"/>
-        <v>358996.43</v>
+        <v>363220.43</v>
       </c>
       <c r="P56" s="91">
         <f t="shared" si="14"/>
-        <v>369766.43</v>
+        <v>374117.43</v>
       </c>
       <c r="Q56" s="40">
         <f t="shared" si="12"/>
@@ -6741,7 +6735,7 @@
       </c>
       <c r="J57" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
+        <v>44868.673695999998</v>
       </c>
       <c r="K57" s="82">
         <f t="shared" si="18"/>
@@ -6753,16 +6747,16 @@
       </c>
       <c r="M57" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
+        <v>13294.792202999999</v>
       </c>
       <c r="N57" s="82"/>
       <c r="O57" s="76">
         <f t="shared" si="8"/>
-        <v>287662.44</v>
+        <v>291885.44</v>
       </c>
       <c r="P57" s="91">
         <f t="shared" si="14"/>
-        <v>296292.44</v>
+        <v>300642.44</v>
       </c>
       <c r="Q57" s="40">
         <f t="shared" si="12"/>
@@ -6789,7 +6783,7 @@
       <c r="F58" s="63">
         <v>55348.45</v>
       </c>
-      <c r="G58" s="269">
+      <c r="G58" s="63">
         <f t="shared" ref="G58" si="19">F58</f>
         <v>55348.45</v>
       </c>
@@ -6803,7 +6797,7 @@
       </c>
       <c r="J58" s="82">
         <f t="shared" si="5"/>
-        <v>40810</v>
+        <v>44868.673695999998</v>
       </c>
       <c r="K58" s="82">
         <f t="shared" si="18"/>
@@ -6815,16 +6809,16 @@
       </c>
       <c r="M58" s="82">
         <f t="shared" si="7"/>
-        <v>13130.035533999999</v>
+        <v>13294.792202999999</v>
       </c>
       <c r="N58" s="82"/>
       <c r="O58" s="76">
         <f t="shared" si="8"/>
-        <v>55348.45</v>
+        <v>59571.45</v>
       </c>
       <c r="P58" s="91">
         <f t="shared" si="14"/>
-        <v>57008.45</v>
+        <v>61358.45</v>
       </c>
       <c r="Q58" s="40">
         <f t="shared" si="12"/>
@@ -6849,13 +6843,13 @@
       <c r="F59" s="63">
         <v>61817.46</v>
       </c>
-      <c r="G59" s="269">
-        <f>132705.46-70888</f>
-        <v>61817.459999999992</v>
+      <c r="G59" s="63">
+        <f>132705.46-70888+(152000/3)</f>
+        <v>112484.12666666665</v>
       </c>
       <c r="H59" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-50666.66666666665</v>
       </c>
       <c r="I59" s="75">
         <f t="shared" si="4"/>
@@ -6863,7 +6857,7 @@
       </c>
       <c r="J59" s="82">
         <f t="shared" si="5"/>
-        <v>45580</v>
+        <v>50113.064127999991</v>
       </c>
       <c r="K59" s="82">
         <f t="shared" si="18"/>
@@ -6875,16 +6869,16 @@
       </c>
       <c r="M59" s="82">
         <f t="shared" si="7"/>
-        <v>14664.715011999999</v>
+        <v>14848.728953999998</v>
       </c>
       <c r="N59" s="82"/>
       <c r="O59" s="76">
         <f t="shared" si="8"/>
-        <v>61817.46</v>
+        <v>15867.46</v>
       </c>
       <c r="P59" s="91">
         <f t="shared" si="14"/>
-        <v>63672.46</v>
+        <v>16343.46</v>
       </c>
       <c r="Q59" s="40">
         <f t="shared" si="12"/>
@@ -6928,19 +6922,19 @@
       </c>
       <c r="G61" s="88">
         <f>SUM(G14:G60)</f>
-        <v>6230781.8999999994</v>
+        <v>5966274.4000000004</v>
       </c>
       <c r="H61" s="88">
         <f t="shared" si="20"/>
-        <v>4811986.91</v>
+        <v>5076494.41</v>
       </c>
       <c r="I61" s="88">
         <f t="shared" si="20"/>
-        <v>144390.61859999999</v>
+        <v>156885.83609999999</v>
       </c>
       <c r="J61" s="89">
         <f t="shared" si="20"/>
-        <v>5300000</v>
+        <v>5827100.4799999986</v>
       </c>
       <c r="K61" s="89">
         <f t="shared" si="20"/>
@@ -6952,16 +6946,16 @@
       </c>
       <c r="M61" s="89">
         <f t="shared" si="20"/>
-        <v>1705199.4200000009</v>
+        <v>1726596.389999999</v>
       </c>
       <c r="N61" s="90"/>
       <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>12187909.810000001</v>
+        <v>13013409.810000001</v>
       </c>
       <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>12553549.810000001</v>
+        <v>13403813.810000001</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6970,103 +6964,99 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="229" t="s">
+      <c r="C64" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="229"/>
-      <c r="E64" s="229"/>
-      <c r="F64" s="229"/>
-      <c r="G64" s="229"/>
-      <c r="H64" s="229"/>
-      <c r="I64" s="229"/>
-      <c r="J64" s="229"/>
-      <c r="K64" s="229"/>
-      <c r="L64" s="229"/>
-      <c r="M64" s="229"/>
-      <c r="N64" s="229"/>
-      <c r="O64" s="229"/>
+      <c r="D64" s="228"/>
+      <c r="E64" s="228"/>
+      <c r="F64" s="228"/>
+      <c r="G64" s="228"/>
+      <c r="H64" s="228"/>
+      <c r="I64" s="228"/>
+      <c r="J64" s="228"/>
+      <c r="K64" s="228"/>
+      <c r="L64" s="228"/>
+      <c r="M64" s="228"/>
+      <c r="N64" s="228"/>
+      <c r="O64" s="228"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="229"/>
-      <c r="D65" s="229"/>
-      <c r="E65" s="229"/>
-      <c r="F65" s="229"/>
-      <c r="G65" s="229"/>
-      <c r="H65" s="229"/>
-      <c r="I65" s="229"/>
-      <c r="J65" s="229"/>
-      <c r="K65" s="229"/>
-      <c r="L65" s="229"/>
-      <c r="M65" s="229"/>
-      <c r="N65" s="229"/>
-      <c r="O65" s="229"/>
+      <c r="C65" s="228"/>
+      <c r="D65" s="228"/>
+      <c r="E65" s="228"/>
+      <c r="F65" s="228"/>
+      <c r="G65" s="228"/>
+      <c r="H65" s="228"/>
+      <c r="I65" s="228"/>
+      <c r="J65" s="228"/>
+      <c r="K65" s="228"/>
+      <c r="L65" s="228"/>
+      <c r="M65" s="228"/>
+      <c r="N65" s="228"/>
+      <c r="O65" s="228"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="229"/>
-      <c r="D66" s="229"/>
-      <c r="E66" s="229"/>
-      <c r="F66" s="229"/>
-      <c r="G66" s="229"/>
-      <c r="H66" s="229"/>
-      <c r="I66" s="229"/>
-      <c r="J66" s="229"/>
-      <c r="K66" s="229"/>
-      <c r="L66" s="229"/>
-      <c r="M66" s="229"/>
-      <c r="N66" s="229"/>
-      <c r="O66" s="229"/>
+      <c r="C66" s="228"/>
+      <c r="D66" s="228"/>
+      <c r="E66" s="228"/>
+      <c r="F66" s="228"/>
+      <c r="G66" s="228"/>
+      <c r="H66" s="228"/>
+      <c r="I66" s="228"/>
+      <c r="J66" s="228"/>
+      <c r="K66" s="228"/>
+      <c r="L66" s="228"/>
+      <c r="M66" s="228"/>
+      <c r="N66" s="228"/>
+      <c r="O66" s="228"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="229"/>
-      <c r="D67" s="229"/>
-      <c r="E67" s="229"/>
-      <c r="F67" s="229"/>
-      <c r="G67" s="229"/>
-      <c r="H67" s="229"/>
-      <c r="I67" s="229"/>
-      <c r="J67" s="229"/>
-      <c r="K67" s="229"/>
-      <c r="L67" s="229"/>
-      <c r="M67" s="229"/>
-      <c r="N67" s="229"/>
-      <c r="O67" s="229"/>
+      <c r="C67" s="228"/>
+      <c r="D67" s="228"/>
+      <c r="E67" s="228"/>
+      <c r="F67" s="228"/>
+      <c r="G67" s="228"/>
+      <c r="H67" s="228"/>
+      <c r="I67" s="228"/>
+      <c r="J67" s="228"/>
+      <c r="K67" s="228"/>
+      <c r="L67" s="228"/>
+      <c r="M67" s="228"/>
+      <c r="N67" s="228"/>
+      <c r="O67" s="228"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="229"/>
-      <c r="D68" s="229"/>
-      <c r="E68" s="229"/>
-      <c r="F68" s="229"/>
-      <c r="G68" s="229"/>
-      <c r="H68" s="229"/>
-      <c r="I68" s="229"/>
-      <c r="J68" s="229"/>
-      <c r="K68" s="229"/>
-      <c r="L68" s="229"/>
-      <c r="M68" s="229"/>
-      <c r="N68" s="229"/>
-      <c r="O68" s="229"/>
+      <c r="C68" s="228"/>
+      <c r="D68" s="228"/>
+      <c r="E68" s="228"/>
+      <c r="F68" s="228"/>
+      <c r="G68" s="228"/>
+      <c r="H68" s="228"/>
+      <c r="I68" s="228"/>
+      <c r="J68" s="228"/>
+      <c r="K68" s="228"/>
+      <c r="L68" s="228"/>
+      <c r="M68" s="228"/>
+      <c r="N68" s="228"/>
+      <c r="O68" s="228"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="229"/>
-      <c r="D69" s="229"/>
-      <c r="E69" s="229"/>
-      <c r="F69" s="229"/>
-      <c r="G69" s="229"/>
-      <c r="H69" s="229"/>
-      <c r="I69" s="229"/>
-      <c r="J69" s="229"/>
-      <c r="K69" s="229"/>
-      <c r="L69" s="229"/>
-      <c r="M69" s="229"/>
-      <c r="N69" s="229"/>
-      <c r="O69" s="229"/>
+      <c r="C69" s="228"/>
+      <c r="D69" s="228"/>
+      <c r="E69" s="228"/>
+      <c r="F69" s="228"/>
+      <c r="G69" s="228"/>
+      <c r="H69" s="228"/>
+      <c r="I69" s="228"/>
+      <c r="J69" s="228"/>
+      <c r="K69" s="228"/>
+      <c r="L69" s="228"/>
+      <c r="M69" s="228"/>
+      <c r="N69" s="228"/>
+      <c r="O69" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -7083,6 +7073,10 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7130,8 +7124,8 @@
         <v>54</v>
       </c>
       <c r="J5" s="114"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="273"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="204"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C6" s="117" t="s">
@@ -7147,43 +7141,43 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J6" s="114"/>
-      <c r="K6" s="272"/>
-      <c r="L6" s="273"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="204"/>
     </row>
     <row r="7" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="114"/>
-      <c r="K7" s="272"/>
-      <c r="L7" s="273"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="204"/>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="255" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="256"/>
-      <c r="E8" s="256"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
-      <c r="H8" s="256"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="272"/>
-      <c r="L8" s="273"/>
+      <c r="C8" s="265" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="266"/>
+      <c r="E8" s="266"/>
+      <c r="F8" s="266"/>
+      <c r="G8" s="266"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="204"/>
     </row>
     <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="258"/>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="259"/>
-      <c r="I9" s="259"/>
-      <c r="J9" s="260"/>
+      <c r="C9" s="268"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="270"/>
       <c r="K9" s="185"/>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.25">
@@ -7198,7 +7192,7 @@
         <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J12" s="114"/>
     </row>
@@ -7219,50 +7213,50 @@
         <v>93</v>
       </c>
       <c r="J13" s="114"/>
-      <c r="K13" s="273"/>
-      <c r="L13" s="273"/>
+      <c r="K13" s="204"/>
+      <c r="L13" s="204"/>
     </row>
     <row r="14" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J14" s="114"/>
-      <c r="K14" s="273"/>
-      <c r="L14" s="273"/>
+      <c r="K14" s="204"/>
+      <c r="L14" s="204"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="255" t="s">
-        <v>195</v>
-      </c>
-      <c r="D15" s="256"/>
-      <c r="E15" s="256"/>
-      <c r="F15" s="256"/>
-      <c r="G15" s="256"/>
-      <c r="H15" s="256"/>
-      <c r="I15" s="256"/>
-      <c r="J15" s="257"/>
-      <c r="K15" s="273"/>
-      <c r="L15" s="273"/>
+      <c r="C15" s="265" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="266"/>
+      <c r="E15" s="266"/>
+      <c r="F15" s="266"/>
+      <c r="G15" s="266"/>
+      <c r="H15" s="266"/>
+      <c r="I15" s="266"/>
+      <c r="J15" s="267"/>
+      <c r="K15" s="204"/>
+      <c r="L15" s="204"/>
     </row>
     <row r="16" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="258"/>
-      <c r="D16" s="259"/>
-      <c r="E16" s="259"/>
-      <c r="F16" s="259"/>
-      <c r="G16" s="259"/>
-      <c r="H16" s="259"/>
-      <c r="I16" s="259"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="273"/>
-      <c r="L16" s="273"/>
+      <c r="C16" s="268"/>
+      <c r="D16" s="269"/>
+      <c r="E16" s="269"/>
+      <c r="F16" s="269"/>
+      <c r="G16" s="269"/>
+      <c r="H16" s="269"/>
+      <c r="I16" s="269"/>
+      <c r="J16" s="270"/>
+      <c r="K16" s="204"/>
+      <c r="L16" s="204"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="K17" s="273"/>
-      <c r="L17" s="273"/>
+      <c r="K17" s="204"/>
+      <c r="L17" s="204"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="K18" s="273"/>
-      <c r="L18" s="273"/>
+      <c r="K18" s="204"/>
+      <c r="L18" s="204"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="198" t="s">
@@ -7276,8 +7270,8 @@
         <v>54</v>
       </c>
       <c r="J19" s="114"/>
-      <c r="K19" s="273"/>
-      <c r="L19" s="273"/>
+      <c r="K19" s="204"/>
+      <c r="L19" s="204"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="198" t="s">
@@ -7293,45 +7287,45 @@
         <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J20" s="114"/>
-      <c r="K20" s="273"/>
-      <c r="L20" s="273"/>
+      <c r="K20" s="204"/>
+      <c r="L20" s="204"/>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J21" s="114"/>
-      <c r="K21" s="273"/>
-      <c r="L21" s="273"/>
+      <c r="K21" s="204"/>
+      <c r="L21" s="204"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="255" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="256"/>
-      <c r="E22" s="256"/>
-      <c r="F22" s="256"/>
-      <c r="G22" s="256"/>
-      <c r="H22" s="256"/>
-      <c r="I22" s="256"/>
-      <c r="J22" s="257"/>
-      <c r="K22" s="273"/>
-      <c r="L22" s="273"/>
+      <c r="C22" s="265" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="266"/>
+      <c r="J22" s="267"/>
+      <c r="K22" s="204"/>
+      <c r="L22" s="204"/>
     </row>
     <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="258"/>
-      <c r="D23" s="259"/>
-      <c r="E23" s="259"/>
-      <c r="F23" s="259"/>
-      <c r="G23" s="259"/>
-      <c r="H23" s="259"/>
-      <c r="I23" s="259"/>
-      <c r="J23" s="260"/>
-      <c r="K23" s="273"/>
-      <c r="L23" s="273"/>
+      <c r="C23" s="268"/>
+      <c r="D23" s="269"/>
+      <c r="E23" s="269"/>
+      <c r="F23" s="269"/>
+      <c r="G23" s="269"/>
+      <c r="H23" s="269"/>
+      <c r="I23" s="269"/>
+      <c r="J23" s="270"/>
+      <c r="K23" s="204"/>
+      <c r="L23" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Agosto/Agosto ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D653A12-3EA2-492E-B1A7-84C66F4C1A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E09E82F-8B7C-4906-A15B-186497AC4FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -1856,18 +1856,36 @@
     <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1892,20 +1910,38 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1952,12 +1988,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1991,33 +2021,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2035,9 +2038,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2460,12 +2460,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="211" t="s">
+      <c r="B1" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="212"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="220"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2478,12 +2478,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="215" t="s">
+      <c r="B3" s="221" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="216"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="222"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2521,18 +2521,18 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="217" t="s">
+      <c r="B8" s="223" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="217"/>
+      <c r="C8" s="223"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
+      <c r="B9" s="223"/>
+      <c r="C9" s="223"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -2541,34 +2541,34 @@
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="218" t="s">
+      <c r="A13" s="224" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="218"/>
-      <c r="C13" s="218"/>
-      <c r="D13" s="218"/>
-      <c r="E13" s="218"/>
+      <c r="B13" s="224"/>
+      <c r="C13" s="224"/>
+      <c r="D13" s="224"/>
+      <c r="E13" s="224"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="218"/>
-      <c r="B14" s="218"/>
-      <c r="C14" s="218"/>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
+      <c r="A14" s="224"/>
+      <c r="B14" s="224"/>
+      <c r="C14" s="224"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="218"/>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
+      <c r="A15" s="224"/>
+      <c r="B15" s="224"/>
+      <c r="C15" s="224"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="224"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
-      <c r="B16" s="218"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
+      <c r="A16" s="224"/>
+      <c r="B16" s="224"/>
+      <c r="C16" s="224"/>
+      <c r="D16" s="224"/>
+      <c r="E16" s="224"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2594,10 +2594,10 @@
       <c r="E21" s="96"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="219" t="s">
+      <c r="A22" s="225" t="s">
         <v>223</v>
       </c>
-      <c r="B22" s="220"/>
+      <c r="B22" s="226"/>
       <c r="C22" s="19"/>
       <c r="D22" s="209">
         <v>1460357.72</v>
@@ -2606,10 +2606,10 @@
       <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="213" t="s">
+      <c r="A23" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="214"/>
+      <c r="B23" s="213"/>
       <c r="C23" s="150"/>
       <c r="D23" s="209">
         <v>-317627.71999999997</v>
@@ -2619,10 +2619,10 @@
       <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="213" t="s">
+      <c r="A24" s="212" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="214"/>
+      <c r="B24" s="213"/>
       <c r="C24" s="150"/>
       <c r="D24" s="194"/>
       <c r="E24" s="21"/>
@@ -2801,10 +2801,10 @@
       <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="221" t="s">
+      <c r="A39" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="222"/>
+      <c r="B39" s="228"/>
       <c r="C39" s="154"/>
       <c r="D39" s="195">
         <v>205033.71</v>
@@ -2815,10 +2815,10 @@
       <c r="F39" s="38"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="221" t="s">
+      <c r="A40" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="222"/>
+      <c r="B40" s="228"/>
       <c r="C40" s="154"/>
       <c r="D40" s="195">
         <v>0</v>
@@ -2897,10 +2897,10 @@
       <c r="F45" s="38"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="221" t="s">
+      <c r="A46" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="222"/>
+      <c r="B46" s="228"/>
       <c r="C46" s="33"/>
       <c r="D46" s="206">
         <v>542877.21</v>
@@ -2950,10 +2950,10 @@
       <c r="F49" s="38"/>
     </row>
     <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="213" t="s">
+      <c r="A50" s="212" t="s">
         <v>212</v>
       </c>
-      <c r="B50" s="214"/>
+      <c r="B50" s="213"/>
       <c r="C50" s="33"/>
       <c r="D50" s="206">
         <v>250600</v>
@@ -2964,10 +2964,10 @@
       <c r="F50" s="38"/>
     </row>
     <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="213" t="s">
+      <c r="A51" s="212" t="s">
         <v>215</v>
       </c>
-      <c r="B51" s="214"/>
+      <c r="B51" s="213"/>
       <c r="C51" s="33"/>
       <c r="D51" s="206">
         <v>298200</v>
@@ -2978,10 +2978,10 @@
       <c r="F51" s="38"/>
     </row>
     <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="221" t="s">
+      <c r="A52" s="227" t="s">
         <v>204</v>
       </c>
-      <c r="B52" s="222"/>
+      <c r="B52" s="228"/>
       <c r="C52" s="150"/>
       <c r="D52" s="206">
         <v>300000</v>
@@ -2992,10 +2992,10 @@
       <c r="F52" s="132"/>
     </row>
     <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="223" t="s">
+      <c r="A53" s="217" t="s">
         <v>205</v>
       </c>
-      <c r="B53" s="224"/>
+      <c r="B53" s="218"/>
       <c r="C53" s="150"/>
       <c r="D53" s="206">
         <v>150000</v>
@@ -3006,10 +3006,10 @@
       <c r="F53" s="132"/>
     </row>
     <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="223" t="s">
+      <c r="A54" s="217" t="s">
         <v>206</v>
       </c>
-      <c r="B54" s="224"/>
+      <c r="B54" s="218"/>
       <c r="C54" s="150"/>
       <c r="D54" s="206">
         <v>350000</v>
@@ -3034,10 +3034,10 @@
       <c r="F55" s="132"/>
     </row>
     <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="223" t="s">
+      <c r="A56" s="217" t="s">
         <v>201</v>
       </c>
-      <c r="B56" s="224"/>
+      <c r="B56" s="218"/>
       <c r="C56" s="150"/>
       <c r="D56" s="206">
         <v>202973</v>
@@ -3048,10 +3048,10 @@
       <c r="F56" s="132"/>
     </row>
     <row r="57" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="221" t="s">
+      <c r="A57" s="227" t="s">
         <v>200</v>
       </c>
-      <c r="B57" s="222"/>
+      <c r="B57" s="228"/>
       <c r="C57" s="150"/>
       <c r="D57" s="206">
         <v>180000</v>
@@ -3062,10 +3062,10 @@
       <c r="F57" s="38"/>
     </row>
     <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="213" t="s">
+      <c r="A58" s="212" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="214"/>
+      <c r="B58" s="213"/>
       <c r="C58" s="150"/>
       <c r="D58" s="206">
         <v>265200</v>
@@ -3127,10 +3127,10 @@
       <c r="F62" s="38"/>
     </row>
     <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="213" t="s">
+      <c r="A63" s="212" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="214"/>
+      <c r="B63" s="213"/>
       <c r="C63" s="150"/>
       <c r="D63" s="207">
         <v>210000</v>
@@ -3139,10 +3139,10 @@
       <c r="F63" s="38"/>
     </row>
     <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="213" t="s">
+      <c r="A64" s="212" t="s">
         <v>219</v>
       </c>
-      <c r="B64" s="214"/>
+      <c r="B64" s="213"/>
       <c r="C64" s="150"/>
       <c r="D64" s="208">
         <v>0</v>
@@ -3293,8 +3293,8 @@
       <c r="F77" s="38"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="226"/>
-      <c r="B78" s="227"/>
+      <c r="A78" s="215"/>
+      <c r="B78" s="216"/>
       <c r="C78" s="33"/>
       <c r="D78" s="172"/>
       <c r="E78" s="119"/>
@@ -3730,16 +3730,16 @@
     </row>
     <row r="119" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="225" t="s">
+      <c r="A120" s="214" t="s">
         <v>25</v>
       </c>
-      <c r="B120" s="225"/>
-      <c r="C120" s="225"/>
+      <c r="B120" s="214"/>
+      <c r="C120" s="214"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="225"/>
-      <c r="B121" s="225"/>
-      <c r="C121" s="225"/>
+      <c r="A121" s="214"/>
+      <c r="B121" s="214"/>
+      <c r="C121" s="214"/>
     </row>
     <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56"/>
@@ -3762,12 +3762,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A120:C121"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A63:B63"/>
@@ -3784,6 +3778,12 @@
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3825,19 +3825,19 @@
       <c r="G1" s="126"/>
       <c r="H1" s="126"/>
       <c r="I1" s="126"/>
-      <c r="J1" s="256" t="str">
+      <c r="J1" s="229" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="256"/>
-      <c r="L1" s="256"/>
-      <c r="M1" s="256"/>
-      <c r="N1" s="256"/>
-      <c r="O1" s="256"/>
-      <c r="P1" s="257"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="230"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3848,21 +3848,21 @@
         <f>D2-C4-C5</f>
         <v>5827100.4799999995</v>
       </c>
-      <c r="D2" s="271">
+      <c r="D2" s="211">
         <v>7736519.879999999</v>
       </c>
       <c r="E2" s="68"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="239"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="M2" s="258"/>
-      <c r="N2" s="258"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="232"/>
       <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3879,13 +3879,13 @@
       <c r="G3" s="131"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="258"/>
-      <c r="O3" s="258"/>
-      <c r="P3" s="259"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="231"/>
+      <c r="P3" s="232"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
@@ -3903,13 +3903,13 @@
       <c r="G4" s="131"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="M4" s="258"/>
-      <c r="N4" s="258"/>
-      <c r="O4" s="258"/>
-      <c r="P4" s="259"/>
+      <c r="J4" s="231"/>
+      <c r="K4" s="231"/>
+      <c r="L4" s="231"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="232"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
@@ -3927,201 +3927,201 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="M5" s="260"/>
-      <c r="N5" s="260"/>
-      <c r="O5" s="260"/>
-      <c r="P5" s="261"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="233"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="233"/>
+      <c r="P5" s="234"/>
       <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="241" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="232"/>
+      <c r="B6" s="242"/>
+      <c r="C6" s="243"/>
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="244"/>
       <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="233"/>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-      <c r="H7" s="234"/>
-      <c r="I7" s="234"/>
-      <c r="J7" s="234"/>
-      <c r="K7" s="234"/>
-      <c r="L7" s="234"/>
-      <c r="M7" s="234"/>
-      <c r="N7" s="234"/>
-      <c r="O7" s="234"/>
-      <c r="P7" s="235"/>
+      <c r="A7" s="245"/>
+      <c r="B7" s="246"/>
+      <c r="C7" s="246"/>
+      <c r="D7" s="246"/>
+      <c r="E7" s="246"/>
+      <c r="F7" s="246"/>
+      <c r="G7" s="246"/>
+      <c r="H7" s="246"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
+      <c r="M7" s="246"/>
+      <c r="N7" s="246"/>
+      <c r="O7" s="246"/>
+      <c r="P7" s="247"/>
       <c r="Q7" s="62"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="233"/>
-      <c r="B8" s="234"/>
-      <c r="C8" s="234"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="235"/>
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="246"/>
+      <c r="D8" s="246"/>
+      <c r="E8" s="246"/>
+      <c r="F8" s="246"/>
+      <c r="G8" s="246"/>
+      <c r="H8" s="246"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="246"/>
+      <c r="K8" s="246"/>
+      <c r="L8" s="246"/>
+      <c r="M8" s="246"/>
+      <c r="N8" s="246"/>
+      <c r="O8" s="246"/>
+      <c r="P8" s="247"/>
       <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="233"/>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="234"/>
-      <c r="P9" s="235"/>
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
+      <c r="M9" s="246"/>
+      <c r="N9" s="246"/>
+      <c r="O9" s="246"/>
+      <c r="P9" s="247"/>
       <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="236"/>
-      <c r="B10" s="237"/>
-      <c r="C10" s="237"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="237"/>
-      <c r="G10" s="237"/>
-      <c r="H10" s="237"/>
-      <c r="I10" s="237"/>
-      <c r="J10" s="237"/>
-      <c r="K10" s="237"/>
-      <c r="L10" s="237"/>
-      <c r="M10" s="237"/>
-      <c r="N10" s="237"/>
-      <c r="O10" s="237"/>
-      <c r="P10" s="238"/>
+      <c r="A10" s="248"/>
+      <c r="B10" s="249"/>
+      <c r="C10" s="249"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="249"/>
+      <c r="K10" s="249"/>
+      <c r="L10" s="249"/>
+      <c r="M10" s="249"/>
+      <c r="N10" s="249"/>
+      <c r="O10" s="249"/>
+      <c r="P10" s="250"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="249" t="s">
+      <c r="A11" s="259" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="250"/>
-      <c r="C11" s="250"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="250"/>
-      <c r="G11" s="250"/>
-      <c r="H11" s="250"/>
-      <c r="I11" s="250"/>
-      <c r="J11" s="250"/>
-      <c r="K11" s="250"/>
-      <c r="L11" s="250"/>
-      <c r="M11" s="250"/>
-      <c r="N11" s="250"/>
-      <c r="O11" s="250"/>
-      <c r="P11" s="251"/>
+      <c r="B11" s="260"/>
+      <c r="C11" s="260"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
+      <c r="M11" s="260"/>
+      <c r="N11" s="260"/>
+      <c r="O11" s="260"/>
+      <c r="P11" s="261"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="239" t="s">
+      <c r="A12" s="251" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="254" t="s">
+      <c r="B12" s="264" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="241" t="s">
+      <c r="C12" s="253" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="241" t="s">
+      <c r="D12" s="253" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="241" t="s">
+      <c r="E12" s="253" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="243" t="s">
+      <c r="F12" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="245" t="s">
+      <c r="G12" s="255" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="247" t="s">
+      <c r="H12" s="257" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="243" t="s">
+      <c r="I12" s="235" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="243" t="s">
+      <c r="J12" s="235" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="243" t="s">
+      <c r="K12" s="235" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="254" t="s">
+      <c r="L12" s="264" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="243" t="s">
+      <c r="M12" s="235" t="s">
         <v>167</v>
       </c>
-      <c r="N12" s="252" t="s">
+      <c r="N12" s="262" t="s">
         <v>182</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="262" t="s">
+      <c r="P12" s="237" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="240"/>
-      <c r="B13" s="255"/>
-      <c r="C13" s="242"/>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="255"/>
-      <c r="M13" s="244"/>
-      <c r="N13" s="253"/>
+      <c r="A13" s="252"/>
+      <c r="B13" s="265"/>
+      <c r="C13" s="254"/>
+      <c r="D13" s="254"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="256"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="265"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="263"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P13" s="263"/>
+      <c r="P13" s="238"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
@@ -6964,99 +6964,103 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="228" t="s">
+      <c r="C64" s="240" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="228"/>
-      <c r="E64" s="228"/>
-      <c r="F64" s="228"/>
-      <c r="G64" s="228"/>
-      <c r="H64" s="228"/>
-      <c r="I64" s="228"/>
-      <c r="J64" s="228"/>
-      <c r="K64" s="228"/>
-      <c r="L64" s="228"/>
-      <c r="M64" s="228"/>
-      <c r="N64" s="228"/>
-      <c r="O64" s="228"/>
+      <c r="D64" s="240"/>
+      <c r="E64" s="240"/>
+      <c r="F64" s="240"/>
+      <c r="G64" s="240"/>
+      <c r="H64" s="240"/>
+      <c r="I64" s="240"/>
+      <c r="J64" s="240"/>
+      <c r="K64" s="240"/>
+      <c r="L64" s="240"/>
+      <c r="M64" s="240"/>
+      <c r="N64" s="240"/>
+      <c r="O64" s="240"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="228"/>
-      <c r="D65" s="228"/>
-      <c r="E65" s="228"/>
-      <c r="F65" s="228"/>
-      <c r="G65" s="228"/>
-      <c r="H65" s="228"/>
-      <c r="I65" s="228"/>
-      <c r="J65" s="228"/>
-      <c r="K65" s="228"/>
-      <c r="L65" s="228"/>
-      <c r="M65" s="228"/>
-      <c r="N65" s="228"/>
-      <c r="O65" s="228"/>
+      <c r="C65" s="240"/>
+      <c r="D65" s="240"/>
+      <c r="E65" s="240"/>
+      <c r="F65" s="240"/>
+      <c r="G65" s="240"/>
+      <c r="H65" s="240"/>
+      <c r="I65" s="240"/>
+      <c r="J65" s="240"/>
+      <c r="K65" s="240"/>
+      <c r="L65" s="240"/>
+      <c r="M65" s="240"/>
+      <c r="N65" s="240"/>
+      <c r="O65" s="240"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="228"/>
-      <c r="D66" s="228"/>
-      <c r="E66" s="228"/>
-      <c r="F66" s="228"/>
-      <c r="G66" s="228"/>
-      <c r="H66" s="228"/>
-      <c r="I66" s="228"/>
-      <c r="J66" s="228"/>
-      <c r="K66" s="228"/>
-      <c r="L66" s="228"/>
-      <c r="M66" s="228"/>
-      <c r="N66" s="228"/>
-      <c r="O66" s="228"/>
+      <c r="C66" s="240"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
+      <c r="G66" s="240"/>
+      <c r="H66" s="240"/>
+      <c r="I66" s="240"/>
+      <c r="J66" s="240"/>
+      <c r="K66" s="240"/>
+      <c r="L66" s="240"/>
+      <c r="M66" s="240"/>
+      <c r="N66" s="240"/>
+      <c r="O66" s="240"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="228"/>
-      <c r="D67" s="228"/>
-      <c r="E67" s="228"/>
-      <c r="F67" s="228"/>
-      <c r="G67" s="228"/>
-      <c r="H67" s="228"/>
-      <c r="I67" s="228"/>
-      <c r="J67" s="228"/>
-      <c r="K67" s="228"/>
-      <c r="L67" s="228"/>
-      <c r="M67" s="228"/>
-      <c r="N67" s="228"/>
-      <c r="O67" s="228"/>
+      <c r="C67" s="240"/>
+      <c r="D67" s="240"/>
+      <c r="E67" s="240"/>
+      <c r="F67" s="240"/>
+      <c r="G67" s="240"/>
+      <c r="H67" s="240"/>
+      <c r="I67" s="240"/>
+      <c r="J67" s="240"/>
+      <c r="K67" s="240"/>
+      <c r="L67" s="240"/>
+      <c r="M67" s="240"/>
+      <c r="N67" s="240"/>
+      <c r="O67" s="240"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="228"/>
-      <c r="D68" s="228"/>
-      <c r="E68" s="228"/>
-      <c r="F68" s="228"/>
-      <c r="G68" s="228"/>
-      <c r="H68" s="228"/>
-      <c r="I68" s="228"/>
-      <c r="J68" s="228"/>
-      <c r="K68" s="228"/>
-      <c r="L68" s="228"/>
-      <c r="M68" s="228"/>
-      <c r="N68" s="228"/>
-      <c r="O68" s="228"/>
+      <c r="C68" s="240"/>
+      <c r="D68" s="240"/>
+      <c r="E68" s="240"/>
+      <c r="F68" s="240"/>
+      <c r="G68" s="240"/>
+      <c r="H68" s="240"/>
+      <c r="I68" s="240"/>
+      <c r="J68" s="240"/>
+      <c r="K68" s="240"/>
+      <c r="L68" s="240"/>
+      <c r="M68" s="240"/>
+      <c r="N68" s="240"/>
+      <c r="O68" s="240"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="228"/>
-      <c r="D69" s="228"/>
-      <c r="E69" s="228"/>
-      <c r="F69" s="228"/>
-      <c r="G69" s="228"/>
-      <c r="H69" s="228"/>
-      <c r="I69" s="228"/>
-      <c r="J69" s="228"/>
-      <c r="K69" s="228"/>
-      <c r="L69" s="228"/>
-      <c r="M69" s="228"/>
-      <c r="N69" s="228"/>
-      <c r="O69" s="228"/>
+      <c r="C69" s="240"/>
+      <c r="D69" s="240"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
+      <c r="G69" s="240"/>
+      <c r="H69" s="240"/>
+      <c r="I69" s="240"/>
+      <c r="J69" s="240"/>
+      <c r="K69" s="240"/>
+      <c r="L69" s="240"/>
+      <c r="M69" s="240"/>
+      <c r="N69" s="240"/>
+      <c r="O69" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -7073,10 +7077,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7156,28 +7156,28 @@
       <c r="L7" s="204"/>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="265" t="s">
+      <c r="C8" s="266" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
-      <c r="G8" s="266"/>
-      <c r="H8" s="266"/>
-      <c r="I8" s="266"/>
-      <c r="J8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="267"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="268"/>
       <c r="K8" s="203"/>
       <c r="L8" s="204"/>
     </row>
     <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="268"/>
-      <c r="D9" s="269"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="269"/>
-      <c r="G9" s="269"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="270"/>
+      <c r="C9" s="269"/>
+      <c r="D9" s="270"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
+      <c r="H9" s="270"/>
+      <c r="I9" s="270"/>
+      <c r="J9" s="271"/>
       <c r="K9" s="185"/>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.25">
@@ -7225,28 +7225,28 @@
       <c r="L14" s="204"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="265" t="s">
+      <c r="C15" s="266" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="266"/>
-      <c r="E15" s="266"/>
-      <c r="F15" s="266"/>
-      <c r="G15" s="266"/>
-      <c r="H15" s="266"/>
-      <c r="I15" s="266"/>
-      <c r="J15" s="267"/>
+      <c r="D15" s="267"/>
+      <c r="E15" s="267"/>
+      <c r="F15" s="267"/>
+      <c r="G15" s="267"/>
+      <c r="H15" s="267"/>
+      <c r="I15" s="267"/>
+      <c r="J15" s="268"/>
       <c r="K15" s="204"/>
       <c r="L15" s="204"/>
     </row>
     <row r="16" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="268"/>
-      <c r="D16" s="269"/>
-      <c r="E16" s="269"/>
-      <c r="F16" s="269"/>
-      <c r="G16" s="269"/>
-      <c r="H16" s="269"/>
-      <c r="I16" s="269"/>
-      <c r="J16" s="270"/>
+      <c r="C16" s="269"/>
+      <c r="D16" s="270"/>
+      <c r="E16" s="270"/>
+      <c r="F16" s="270"/>
+      <c r="G16" s="270"/>
+      <c r="H16" s="270"/>
+      <c r="I16" s="270"/>
+      <c r="J16" s="271"/>
       <c r="K16" s="204"/>
       <c r="L16" s="204"/>
     </row>
@@ -7302,28 +7302,28 @@
       <c r="L21" s="204"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="265" t="s">
+      <c r="C22" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="267"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="267"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="267"/>
+      <c r="J22" s="268"/>
       <c r="K22" s="204"/>
       <c r="L22" s="204"/>
     </row>
     <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="268"/>
-      <c r="D23" s="269"/>
-      <c r="E23" s="269"/>
-      <c r="F23" s="269"/>
-      <c r="G23" s="269"/>
-      <c r="H23" s="269"/>
-      <c r="I23" s="269"/>
-      <c r="J23" s="270"/>
+      <c r="C23" s="269"/>
+      <c r="D23" s="270"/>
+      <c r="E23" s="270"/>
+      <c r="F23" s="270"/>
+      <c r="G23" s="270"/>
+      <c r="H23" s="270"/>
+      <c r="I23" s="270"/>
+      <c r="J23" s="271"/>
       <c r="K23" s="204"/>
       <c r="L23" s="204"/>
     </row>
